--- a/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="193">
   <si>
     <t>group</t>
   </si>
@@ -136,450 +136,402 @@
     <t>0.640</t>
   </si>
   <si>
-    <t>HT4_HT6_Int</t>
-  </si>
-  <si>
-    <t>ROE + 5-HT4 + 5-HT6 + 5-HT4x5-HT6</t>
-  </si>
-  <si>
-    <t>3.1e-05</t>
-  </si>
-  <si>
-    <t>0.011</t>
-  </si>
-  <si>
-    <t>0.570</t>
-  </si>
-  <si>
-    <t>R_5HT4_x_5HT6</t>
-  </si>
-  <si>
-    <t>5-HT4 x 5-HT6</t>
-  </si>
-  <si>
-    <t>0.479</t>
-  </si>
-  <si>
-    <t>HT4_HT6_Cov</t>
-  </si>
-  <si>
-    <t>ROE + 5-HT4 + 5-HT6 + Sex + MQS non-opioid + log MME + SOWS + DOU</t>
-  </si>
-  <si>
-    <t>0.139</t>
-  </si>
-  <si>
-    <t>0.225</t>
-  </si>
-  <si>
-    <t>0.035</t>
+    <t>HT4_HT6_ROEint</t>
+  </si>
+  <si>
+    <t>ROE + 5-HT4 + 5-HT6 + ROEx5-HT4 + ROEx5-HT6</t>
+  </si>
+  <si>
+    <t>2.1e-04</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>0.846</t>
+  </si>
+  <si>
+    <t>0.894</t>
+  </si>
+  <si>
+    <t>R_5HT4_x_ROE</t>
+  </si>
+  <si>
+    <t>5-HT4 x log10 ROE</t>
+  </si>
+  <si>
+    <t>0.526</t>
+  </si>
+  <si>
+    <t>R_5HT6_x_ROE</t>
+  </si>
+  <si>
+    <t>5-HT6 x log10 ROE</t>
+  </si>
+  <si>
+    <t>0.871</t>
+  </si>
+  <si>
+    <t>HT4_HT6_ROEint_Cov</t>
+  </si>
+  <si>
+    <t>ROE + 5-HT4 + 5-HT6 + ROEx5-HT4 + ROEx5-HT6 + Sex + log MME + MQS non-opioid</t>
+  </si>
+  <si>
+    <t>0.540</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>0.218</t>
+  </si>
+  <si>
+    <t>0.411</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>0.503</t>
+  </si>
+  <si>
+    <t>sex_female</t>
+  </si>
+  <si>
+    <t>Sex (female)</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>log_MME</t>
+  </si>
+  <si>
+    <t>log10 MME</t>
+  </si>
+  <si>
+    <t>0.252</t>
+  </si>
+  <si>
+    <t>MQS_nonopioid</t>
+  </si>
+  <si>
+    <t>MQS non-opioid</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>Tramadol group</t>
+  </si>
+  <si>
+    <t>0.241</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>0.615</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>0.006</t>
+  </si>
+  <si>
+    <t>0.392</t>
+  </si>
+  <si>
+    <t>0.573</t>
+  </si>
+  <si>
+    <t>0.260</t>
+  </si>
+  <si>
+    <t>0.865</t>
+  </si>
+  <si>
+    <t>0.289</t>
+  </si>
+  <si>
+    <t>0.836</t>
+  </si>
+  <si>
+    <t>0.365</t>
+  </si>
+  <si>
+    <t>0.774</t>
+  </si>
+  <si>
+    <t>0.641</t>
+  </si>
+  <si>
+    <t>0.970</t>
+  </si>
+  <si>
+    <t>0.536</t>
+  </si>
+  <si>
+    <t>0.983</t>
+  </si>
+  <si>
+    <t>0.585</t>
+  </si>
+  <si>
+    <t>0.451</t>
+  </si>
+  <si>
+    <t>0.879</t>
+  </si>
+  <si>
+    <t>0.549</t>
+  </si>
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>adj_R2</t>
+  </si>
+  <si>
+    <t>F_stat</t>
+  </si>
+  <si>
+    <t>df1</t>
+  </si>
+  <si>
+    <t>df2</t>
+  </si>
+  <si>
+    <t>F_p</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>AIC</t>
+  </si>
+  <si>
+    <t>BIC</t>
+  </si>
+  <si>
+    <t>max_VIF</t>
+  </si>
+  <si>
+    <t>max_cooksD</t>
+  </si>
+  <si>
+    <t>shapiro_p</t>
+  </si>
+  <si>
+    <t>bp_p</t>
+  </si>
+  <si>
+    <t>F_p_fmt</t>
+  </si>
+  <si>
+    <t>nrs ~ log_ROE + R_5HT4</t>
+  </si>
+  <si>
+    <t>0.002</t>
+  </si>
+  <si>
+    <t>nrs ~ log_ROE + R_5HT6</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6</t>
+  </si>
+  <si>
+    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE</t>
+  </si>
+  <si>
+    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE +      sex_female + log_MME + MQS_nonopioid</t>
+  </si>
+  <si>
+    <t>0.167</t>
+  </si>
+  <si>
+    <t>0.012</t>
+  </si>
+  <si>
+    <t>0.222</t>
+  </si>
+  <si>
+    <t>reduced</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>added_term</t>
+  </si>
+  <si>
+    <t>added_lab</t>
+  </si>
+  <si>
+    <t>df_num</t>
+  </si>
+  <si>
+    <t>df_den</t>
+  </si>
+  <si>
+    <t>R2_reduced</t>
+  </si>
+  <si>
+    <t>R2_full</t>
+  </si>
+  <si>
+    <t>delta_R2</t>
+  </si>
+  <si>
+    <t>adjR2_reduced</t>
+  </si>
+  <si>
+    <t>adjR2_full</t>
+  </si>
+  <si>
+    <t>delta_adjR2</t>
+  </si>
+  <si>
+    <t>delta_AIC</t>
+  </si>
+  <si>
+    <t>R_5HT4_x_ROE + R_5HT6_x_ROE</t>
+  </si>
+  <si>
+    <t>5-HT4 x log10 ROE + 5-HT6 x log10 ROE</t>
+  </si>
+  <si>
+    <t>0.756</t>
+  </si>
+  <si>
+    <t>0.234</t>
+  </si>
+  <si>
+    <t>predictor</t>
+  </si>
+  <si>
+    <t>comparison</t>
+  </si>
+  <si>
+    <t>sig</t>
+  </si>
+  <si>
+    <t>.grpTramadol group:log_ROE</t>
+  </si>
+  <si>
+    <t>Tramadol group minus Hydrocodone group</t>
+  </si>
+  <si>
+    <t>.grpTramadol group:R_5HT4</t>
+  </si>
+  <si>
+    <t>0.205</t>
+  </si>
+  <si>
+    <t>5.8e-04</t>
+  </si>
+  <si>
+    <t>.grpTramadol group:R_5HT6</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>3.5e-04</t>
+  </si>
+  <si>
+    <t>0.018</t>
+  </si>
+  <si>
+    <t>0.015</t>
+  </si>
+  <si>
+    <t>0.137</t>
+  </si>
+  <si>
+    <t>0.881</t>
+  </si>
+  <si>
+    <t>.grpTramadol group:R_5HT4_x_ROE</t>
+  </si>
+  <si>
+    <t>0.766</t>
+  </si>
+  <si>
+    <t>.grpTramadol group:R_5HT6_x_ROE</t>
+  </si>
+  <si>
+    <t>0.366</t>
+  </si>
+  <si>
+    <t>0.502</t>
+  </si>
+  <si>
+    <t>0.979</t>
   </si>
   <si>
     <t>0.314</t>
   </si>
   <si>
-    <t>sex_female</t>
-  </si>
-  <si>
-    <t>Sex (female)</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>MQS_nonopioid</t>
-  </si>
-  <si>
-    <t>MQS non-opioid</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>log_MME</t>
-  </si>
-  <si>
-    <t>log10 MME</t>
-  </si>
-  <si>
-    <t>0.798</t>
-  </si>
-  <si>
-    <t>SOWS</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>DOU</t>
-  </si>
-  <si>
-    <t>DOU (yr)</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>HT4_HT6_Cov_noMME</t>
-  </si>
-  <si>
-    <t>ROE + 5-HT4 + 5-HT6 + Sex + MQS non-opioid + SOWS + DOU</t>
-  </si>
-  <si>
-    <t>0.003</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>0.013</t>
-  </si>
-  <si>
-    <t>0.277</t>
-  </si>
-  <si>
-    <t>0.060</t>
+    <t>0.847</t>
+  </si>
+  <si>
+    <t>0.368</t>
+  </si>
+  <si>
+    <t>.grpTramadol group:sex_female</t>
+  </si>
+  <si>
+    <t>0.868</t>
+  </si>
+  <si>
+    <t>.grpTramadol group:log_MME</t>
+  </si>
+  <si>
+    <t>0.791</t>
+  </si>
+  <si>
+    <t>.grpTramadol group:MQS_nonopioid</t>
+  </si>
+  <si>
+    <t>0.386</t>
   </si>
   <si>
     <t>0.007</t>
   </si>
   <si>
-    <t>0.006</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>Tramadol group</t>
-  </si>
-  <si>
-    <t>0.241</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>0.615</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>0.392</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>0.008</t>
-  </si>
-  <si>
-    <t>0.896</t>
+    <t>3.3e-04</t>
   </si>
   <si>
     <t>0.023</t>
   </si>
   <si>
-    <t>0.691</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>0.363</t>
-  </si>
-  <si>
-    <t>0.667</t>
-  </si>
-  <si>
-    <t>0.221</t>
-  </si>
-  <si>
-    <t>0.721</t>
-  </si>
-  <si>
-    <t>0.744</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>0.311</t>
-  </si>
-  <si>
-    <t>0.508</t>
-  </si>
-  <si>
-    <t>0.233</t>
-  </si>
-  <si>
-    <t>0.191</t>
-  </si>
-  <si>
-    <t>0.779</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>0.942</t>
-  </si>
-  <si>
-    <t>formula</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>adj_R2</t>
-  </si>
-  <si>
-    <t>F_stat</t>
-  </si>
-  <si>
-    <t>df1</t>
-  </si>
-  <si>
-    <t>df2</t>
-  </si>
-  <si>
-    <t>F_p</t>
-  </si>
-  <si>
-    <t>sigma</t>
-  </si>
-  <si>
-    <t>RMSE</t>
-  </si>
-  <si>
-    <t>AIC</t>
-  </si>
-  <si>
-    <t>BIC</t>
-  </si>
-  <si>
-    <t>max_VIF</t>
-  </si>
-  <si>
-    <t>max_cooksD</t>
-  </si>
-  <si>
-    <t>shapiro_p</t>
-  </si>
-  <si>
-    <t>bp_p</t>
-  </si>
-  <si>
-    <t>F_p_fmt</t>
-  </si>
-  <si>
-    <t>nrs ~ log_ROE + R_5HT4</t>
-  </si>
-  <si>
-    <t>0.002</t>
-  </si>
-  <si>
-    <t>nrs ~ log_ROE + R_5HT6</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6</t>
-  </si>
-  <si>
-    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_5HT6</t>
-  </si>
-  <si>
-    <t>0.014</t>
-  </si>
-  <si>
-    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6 + sex_female + MQS_nonopioid +      log_MME + SOWS + DOU</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
-    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6 + sex_female + MQS_nonopioid +      SOWS + DOU</t>
-  </si>
-  <si>
-    <t>9.7e-05</t>
-  </si>
-  <si>
-    <t>0.167</t>
-  </si>
-  <si>
-    <t>0.016</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>0.017</t>
-  </si>
-  <si>
-    <t>reduced</t>
-  </si>
-  <si>
-    <t>full</t>
-  </si>
-  <si>
-    <t>added_term</t>
-  </si>
-  <si>
-    <t>df_num</t>
-  </si>
-  <si>
-    <t>df_den</t>
-  </si>
-  <si>
-    <t>R2_reduced</t>
-  </si>
-  <si>
-    <t>R2_full</t>
-  </si>
-  <si>
-    <t>delta_R2</t>
-  </si>
-  <si>
-    <t>adjR2_reduced</t>
-  </si>
-  <si>
-    <t>adjR2_full</t>
-  </si>
-  <si>
-    <t>delta_adjR2</t>
-  </si>
-  <si>
-    <t>delta_AIC</t>
-  </si>
-  <si>
-    <t>sex_female + MQS_nonopioid + SOWS + DOU</t>
-  </si>
-  <si>
-    <t>0.194</t>
-  </si>
-  <si>
-    <t>predictor</t>
-  </si>
-  <si>
-    <t>comparison</t>
-  </si>
-  <si>
-    <t>sig</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:log_ROE</t>
-  </si>
-  <si>
-    <t>Tramadol group minus Hydrocodone group</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:R_5HT4</t>
-  </si>
-  <si>
-    <t>0.205</t>
-  </si>
-  <si>
-    <t>5.8e-04</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:R_5HT6</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>3.5e-04</t>
-  </si>
-  <si>
-    <t>0.018</t>
-  </si>
-  <si>
-    <t>0.015</t>
-  </si>
-  <si>
-    <t>4.5e-04</t>
-  </si>
-  <si>
-    <t>0.178</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:R_5HT4_x_5HT6</t>
-  </si>
-  <si>
-    <t>0.992</t>
-  </si>
-  <si>
-    <t>0.851</t>
-  </si>
-  <si>
-    <t>0.369</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:sex_female</t>
-  </si>
-  <si>
-    <t>0.513</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:MQS_nonopioid</t>
-  </si>
-  <si>
-    <t>0.541</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:log_MME</t>
-  </si>
-  <si>
-    <t>0.632</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:SOWS</t>
-  </si>
-  <si>
-    <t>0.110</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:DOU</t>
-  </si>
-  <si>
-    <t>0.529</t>
-  </si>
-  <si>
-    <t>0.573</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>0.482</t>
-  </si>
-  <si>
-    <t>0.415</t>
-  </si>
-  <si>
-    <t>0.184</t>
-  </si>
-  <si>
-    <t>0.338</t>
-  </si>
-  <si>
-    <t>3.3e-04</t>
-  </si>
-  <si>
     <t>setting</t>
   </si>
   <si>
@@ -604,13 +556,13 @@
     <t>models</t>
   </si>
   <si>
-    <t>HT4: nrs ~ log_ROE + R_5HT4  |  HT6: nrs ~ log_ROE + R_5HT6  |  HT4_HT6: nrs ~ log_ROE + R_5HT4 + R_5HT6  |  HT4_HT6_Int: nrs ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_5HT6  |  HT4_HT6_Cov: nrs ~ log_ROE + R_5HT4 + R_5HT6 + sex_female + MQS_nonopioid + log_MME + SOWS + DOU  |  HT4_HT6_Cov_noMME: nrs ~ log_ROE + R_5HT4 + R_5HT6 + sex_female + MQS_nonopioid + SOWS + DOU</t>
+    <t>HT4: nrs ~ log_ROE + R_5HT4  |  HT6: nrs ~ log_ROE + R_5HT6  |  HT4_HT6: nrs ~ log_ROE + R_5HT4 + R_5HT6  |  HT4_HT6_ROEint: nrs ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE  |  HT4_HT6_ROEint_Cov: nrs ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE + sex_female + log_MME + MQS_nonopioid</t>
   </si>
   <si>
     <t>interaction_raw</t>
   </si>
   <si>
-    <t>R_5HT4_x_5HT6 = R_5HT4 * R_5HT6  (HT4_HT6_Int)</t>
+    <t>R_5HT4_x_ROE = R_5HT4 * log_ROE and R_5HT6_x_ROE = R_5HT6 * log_ROE (M4, M5)</t>
   </si>
   <si>
     <t>sex_coding</t>
@@ -622,7 +574,7 @@
     <t>covariate_scales</t>
   </si>
   <si>
-    <t>MME entered as log10 (log_MME); DOU entered RAW in years; MQS_nonopioid and SOWS entered raw. HT4_HT6_Cov is fit on fewer rows than every other model because log_MME has missing values -- its R2/AIC are NOT comparable to the others; use HT4_HT6_Cov_noMME for that.</t>
+    <t>MME entered as log10 (log_MME); MQS_nonopioid entered raw. M5 (HT4_HT6_ROEint_Cov) is fit on fewer rows than M1-M4 because log_MME has missing values -- its R2/adj R2/AIC/RMSE are NOT comparable to theirs, and no nested F test into it is valid. Compare the n row first.</t>
   </si>
   <si>
     <t>min_n</t>
@@ -646,7 +598,7 @@
     <t>output_dir</t>
   </si>
   <si>
-    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/New_Outputs/multiple_regression_HT4_HT6</t>
+    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/nested-regression-models/New_Outputs/multiple_regression_HT4_HT6</t>
   </si>
 </sst>
 </file>
@@ -989,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1">
@@ -1484,28 +1436,28 @@
         <v>17</v>
       </c>
       <c r="F12">
-        <v>10.36816699649565</v>
+        <v>9.902340064556773</v>
       </c>
       <c r="G12">
-        <v>1.7183416258521</v>
+        <v>1.952111539446245</v>
       </c>
       <c r="H12">
-        <v>6.033821703733816</v>
+        <v>5.072630259316927</v>
       </c>
       <c r="I12">
-        <v>3.071151564084158E-05</v>
+        <v>0.0002137698813614068</v>
       </c>
       <c r="J12" t="s">
         <v>40</v>
       </c>
       <c r="K12">
-        <v>6.682690752073032</v>
+        <v>5.685059480817777</v>
       </c>
       <c r="L12">
-        <v>14.05364324091827</v>
+        <v>14.11962064829577</v>
       </c>
       <c r="M12">
-        <v>7.029374811014715E-17</v>
+        <v>5.368454873047635E-17</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1525,31 +1477,31 @@
         <v>20</v>
       </c>
       <c r="F13">
-        <v>1.48714211365276</v>
+        <v>1.278045426650765</v>
       </c>
       <c r="G13">
-        <v>0.6111412070659636</v>
+        <v>0.6780795506097234</v>
       </c>
       <c r="H13">
-        <v>2.433385437700072</v>
+        <v>1.884801606981891</v>
       </c>
       <c r="I13">
-        <v>0.02895405137713761</v>
+        <v>0.08200757702644451</v>
       </c>
       <c r="J13" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="K13">
-        <v>0.1763745882996632</v>
+        <v>-0.1868563810748567</v>
       </c>
       <c r="L13">
-        <v>2.797909639005857</v>
+        <v>2.742947234376387</v>
       </c>
       <c r="M13">
-        <v>0.4410205171601154</v>
+        <v>0.3790116962199406</v>
       </c>
       <c r="N13">
-        <v>1.058666812069294</v>
+        <v>1.217298576161407</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1569,31 +1521,31 @@
         <v>23</v>
       </c>
       <c r="F14">
-        <v>2.751825849112008</v>
+        <v>0.5866724405731458</v>
       </c>
       <c r="G14">
-        <v>0.93371683870735</v>
+        <v>2.969857851793622</v>
       </c>
       <c r="H14">
-        <v>2.947173848681654</v>
+        <v>0.1975422629129639</v>
       </c>
       <c r="I14">
-        <v>0.01060504642940412</v>
+        <v>0.8464584846887609</v>
       </c>
       <c r="J14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K14">
-        <v>0.7492024031677884</v>
+        <v>-5.829315376591715</v>
       </c>
       <c r="L14">
-        <v>4.754449295056228</v>
+        <v>7.002660257738007</v>
       </c>
       <c r="M14">
-        <v>0.6072250142810075</v>
+        <v>0.1294566591923903</v>
       </c>
       <c r="N14">
-        <v>1.368205454794085</v>
+        <v>12.92861246286382</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1613,31 +1565,31 @@
         <v>30</v>
       </c>
       <c r="F15">
-        <v>0.7566737752122188</v>
+        <v>-1.238207904083448</v>
       </c>
       <c r="G15">
-        <v>1.300861046282463</v>
+        <v>9.082348762412622</v>
       </c>
       <c r="H15">
-        <v>0.5816714839564182</v>
+        <v>-0.1363312438746883</v>
       </c>
       <c r="I15">
-        <v>0.5700360291310171</v>
+        <v>0.8936480221241607</v>
       </c>
       <c r="J15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K15">
-        <v>-2.033395679685233</v>
+        <v>-20.8594294974633</v>
       </c>
       <c r="L15">
-        <v>3.546743230109671</v>
+        <v>18.3830136892964</v>
       </c>
       <c r="M15">
-        <v>0.1097680155318406</v>
+        <v>-0.1796224858050113</v>
       </c>
       <c r="N15">
-        <v>1.147782499508406</v>
+        <v>52.25812053263659</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1651,37 +1603,37 @@
         <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F16">
-        <v>2.457273654398627</v>
+        <v>-0.834611263116579</v>
       </c>
       <c r="G16">
-        <v>3.375750691227966</v>
+        <v>1.279701386227992</v>
       </c>
       <c r="H16">
-        <v>0.7279191738844811</v>
+        <v>-0.6521922005387936</v>
       </c>
       <c r="I16">
-        <v>0.4786616139791064</v>
+        <v>0.525641540877594</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K16">
-        <v>-4.782991489876439</v>
+        <v>-3.599238027555519</v>
       </c>
       <c r="L16">
-        <v>9.697538798673694</v>
+        <v>1.930015501322361</v>
       </c>
       <c r="M16">
-        <v>0.1502376234928155</v>
+        <v>-0.4490746223254154</v>
       </c>
       <c r="N16">
-        <v>1.372949653581145</v>
+        <v>14.27279410864606</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1689,40 +1641,43 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
         <v>47</v>
       </c>
-      <c r="D17" t="s">
-        <v>17</v>
-      </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F17">
-        <v>4.266818973873088</v>
+        <v>-0.5088683148202404</v>
       </c>
       <c r="G17">
-        <v>2.627629335930207</v>
+        <v>3.070790525600985</v>
       </c>
       <c r="H17">
-        <v>1.623828336641169</v>
+        <v>-0.1657124804110986</v>
       </c>
       <c r="I17">
-        <v>0.1388597673074079</v>
+        <v>0.870932576241951</v>
       </c>
       <c r="J17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K17">
-        <v>-1.67729154958012</v>
+        <v>-7.142907916891511</v>
       </c>
       <c r="L17">
-        <v>10.2109294973263</v>
+        <v>6.12517128725103</v>
       </c>
       <c r="M17">
-        <v>7.978822167533627E-18</v>
+        <v>-0.2216653048878749</v>
+      </c>
+      <c r="N17">
+        <v>53.86518864767415</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1730,43 +1685,40 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>0.6814826880478821</v>
+        <v>1.828221291047192</v>
       </c>
       <c r="G18">
-        <v>0.5226515472833611</v>
+        <v>2.867846524034585</v>
       </c>
       <c r="H18">
-        <v>1.303894902043424</v>
+        <v>0.637489236514368</v>
       </c>
       <c r="I18">
-        <v>0.2246308372309903</v>
+        <v>0.5396831608311319</v>
       </c>
       <c r="J18" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K18">
-        <v>-0.5008372532867378</v>
+        <v>-4.659298265103578</v>
       </c>
       <c r="L18">
-        <v>1.863802629382502</v>
+        <v>8.315740847197961</v>
       </c>
       <c r="M18">
-        <v>0.2030851855980043</v>
-      </c>
-      <c r="N18">
-        <v>2.219748423244484</v>
+        <v>-1.748993587185722E-16</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1774,43 +1726,43 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>1.47995641292851</v>
+        <v>-0.05194554429486767</v>
       </c>
       <c r="G19">
-        <v>0.598359490812857</v>
+        <v>0.5701285613569899</v>
       </c>
       <c r="H19">
-        <v>2.473356628668202</v>
+        <v>-0.09111198388523042</v>
       </c>
       <c r="I19">
-        <v>0.03537492220825907</v>
+        <v>0.9293992600759664</v>
       </c>
       <c r="J19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K19">
-        <v>0.1263732048579189</v>
+        <v>-1.341665953084418</v>
       </c>
       <c r="L19">
-        <v>2.833539620999101</v>
+        <v>1.237774864494683</v>
       </c>
       <c r="M19">
-        <v>0.3222774408392703</v>
+        <v>-0.01548002713661297</v>
       </c>
       <c r="N19">
-        <v>1.553526883683434</v>
+        <v>2.147524359538006</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1818,43 +1770,43 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F20">
-        <v>-1.011739308864294</v>
+        <v>-2.79181759345162</v>
       </c>
       <c r="G20">
-        <v>0.9481714434240794</v>
+        <v>2.108240965572673</v>
       </c>
       <c r="H20">
-        <v>-1.067042585896339</v>
+        <v>-1.324240273783535</v>
       </c>
       <c r="I20">
-        <v>0.313737914312984</v>
+        <v>0.2180657591054126</v>
       </c>
       <c r="J20" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K20">
-        <v>-3.156652131166789</v>
+        <v>-7.560989994626445</v>
       </c>
       <c r="L20">
-        <v>1.1331735134382</v>
+        <v>1.977354807723205</v>
       </c>
       <c r="M20">
-        <v>-0.1417202613270651</v>
+        <v>-0.6079502216739275</v>
       </c>
       <c r="N20">
-        <v>1.614108878193461</v>
+        <v>15.68007473575603</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1862,43 +1814,43 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>1.033689122234634</v>
+        <v>-5.495507284001475</v>
       </c>
       <c r="G21">
-        <v>0.550702293695608</v>
+        <v>6.380967108170462</v>
       </c>
       <c r="H21">
-        <v>1.877037982351294</v>
+        <v>-0.861234228423587</v>
       </c>
       <c r="I21">
-        <v>0.09324600082859175</v>
+        <v>0.4114660252044843</v>
       </c>
       <c r="J21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K21">
-        <v>-0.2120860160182865</v>
+        <v>-19.93025773332903</v>
       </c>
       <c r="L21">
-        <v>2.279464260487554</v>
+        <v>8.939243165326083</v>
       </c>
       <c r="M21">
-        <v>0.2422173027814284</v>
+        <v>-0.7697879499094803</v>
       </c>
       <c r="N21">
-        <v>1.523690108973254</v>
+        <v>59.43541820810998</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1906,43 +1858,43 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22">
+        <v>-1.932213905458058</v>
+      </c>
+      <c r="G22">
+        <v>0.8733408625524705</v>
+      </c>
+      <c r="H22">
+        <v>-2.212439596391805</v>
+      </c>
+      <c r="I22">
+        <v>0.05422896907145851</v>
+      </c>
+      <c r="J22" t="s">
         <v>56</v>
       </c>
-      <c r="F22">
-        <v>0.051208491576968</v>
-      </c>
-      <c r="G22">
-        <v>0.02422980362536294</v>
-      </c>
-      <c r="H22">
-        <v>2.113450540860541</v>
-      </c>
-      <c r="I22">
-        <v>0.06371178142166012</v>
-      </c>
-      <c r="J22" t="s">
-        <v>57</v>
-      </c>
       <c r="K22">
-        <v>-0.003603132247340685</v>
+        <v>-3.907848193245492</v>
       </c>
       <c r="L22">
-        <v>0.1060201154012767</v>
+        <v>0.04342038232937506</v>
       </c>
       <c r="M22">
-        <v>0.3129279726401553</v>
+        <v>-1.017785101958202</v>
       </c>
       <c r="N22">
-        <v>2.00602821726018</v>
+        <v>15.74399719434322</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1950,43 +1902,43 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
         <v>47</v>
       </c>
-      <c r="D23" t="s">
-        <v>58</v>
-      </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F23">
-        <v>0.3137544248848685</v>
+        <v>-1.502017604888746</v>
       </c>
       <c r="G23">
-        <v>1.188681162123391</v>
+        <v>2.153554970164709</v>
       </c>
       <c r="H23">
-        <v>0.263951709577357</v>
+        <v>-0.6974596078101819</v>
       </c>
       <c r="I23">
-        <v>0.797761586337435</v>
+        <v>0.5031329126524713</v>
       </c>
       <c r="J23" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="K23">
-        <v>-2.375229180295855</v>
+        <v>-6.373697406126516</v>
       </c>
       <c r="L23">
-        <v>3.002738030065592</v>
+        <v>3.369662196349025</v>
       </c>
       <c r="M23">
-        <v>0.04993507152507754</v>
+        <v>-0.6319725722756425</v>
       </c>
       <c r="N23">
-        <v>3.274875819626642</v>
+        <v>61.08070029911875</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1994,43 +1946,43 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F24">
-        <v>0.09927049812751895</v>
+        <v>1.242107842466939</v>
       </c>
       <c r="G24">
-        <v>0.03774206670315421</v>
+        <v>0.6128722921647237</v>
       </c>
       <c r="H24">
-        <v>2.63023482281172</v>
+        <v>2.026699295019024</v>
       </c>
       <c r="I24">
-        <v>0.02734812172588747</v>
+        <v>0.07332438590515773</v>
       </c>
       <c r="J24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K24">
-        <v>0.01389201159617104</v>
+        <v>-0.1443056031340451</v>
       </c>
       <c r="L24">
-        <v>0.1846489846588669</v>
+        <v>2.628521288067923</v>
       </c>
       <c r="M24">
-        <v>0.4747045229377569</v>
+        <v>0.2910546361517289</v>
       </c>
       <c r="N24">
-        <v>2.980506924762329</v>
+        <v>1.534320472076546</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -2038,43 +1990,43 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25">
+        <v>1.484329999294819</v>
+      </c>
+      <c r="G25">
+        <v>1.211537304524129</v>
+      </c>
+      <c r="H25">
+        <v>1.225162439284392</v>
+      </c>
+      <c r="I25">
+        <v>0.2516095807119866</v>
+      </c>
+      <c r="J25" t="s">
         <v>63</v>
       </c>
-      <c r="E25" t="s">
-        <v>64</v>
-      </c>
-      <c r="F25">
-        <v>0.09106679312310491</v>
-      </c>
-      <c r="G25">
-        <v>0.04355916580114648</v>
-      </c>
-      <c r="H25">
-        <v>2.090645939796855</v>
-      </c>
-      <c r="I25">
-        <v>0.06611403794901438</v>
-      </c>
-      <c r="J25" t="s">
-        <v>65</v>
-      </c>
       <c r="K25">
-        <v>-0.007470885799473206</v>
+        <v>-1.256357792131669</v>
       </c>
       <c r="L25">
-        <v>0.189604472045683</v>
+        <v>4.225017790721308</v>
       </c>
       <c r="M25">
-        <v>0.2741570827730281</v>
+        <v>0.2362361095267534</v>
       </c>
       <c r="N25">
-        <v>1.573513249786552</v>
+        <v>2.765991782932822</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -2082,488 +2034,485 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26">
+        <v>0.09640589246893831</v>
+      </c>
+      <c r="G26">
+        <v>0.02924678992963755</v>
+      </c>
+      <c r="H26">
+        <v>3.296289702250172</v>
+      </c>
+      <c r="I26">
+        <v>0.009284696343749841</v>
+      </c>
+      <c r="J26" t="s">
         <v>66</v>
       </c>
-      <c r="C26" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26">
-        <v>4.934877122396522</v>
-      </c>
-      <c r="G26">
-        <v>1.290196632522029</v>
-      </c>
-      <c r="H26">
-        <v>3.82490311786817</v>
-      </c>
-      <c r="I26">
-        <v>0.002819135041753742</v>
-      </c>
-      <c r="J26" t="s">
-        <v>68</v>
-      </c>
       <c r="K26">
-        <v>2.095173480615331</v>
+        <v>0.03024505714075432</v>
       </c>
       <c r="L26">
-        <v>7.774580764177713</v>
+        <v>0.1625667277971223</v>
       </c>
       <c r="M26">
-        <v>-1.386777010808419E-17</v>
+        <v>0.5891230058109815</v>
+      </c>
+      <c r="N26">
+        <v>2.376330748734058</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F27">
-        <v>0.7844685263412402</v>
+        <v>-8.618603698098783</v>
       </c>
       <c r="G27">
-        <v>0.3638471439456284</v>
+        <v>7.042351060199127</v>
       </c>
       <c r="H27">
-        <v>2.156038708547531</v>
+        <v>-1.223824774485907</v>
       </c>
       <c r="I27">
-        <v>0.05407583990041737</v>
+        <v>0.2412163428046945</v>
       </c>
       <c r="J27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K27">
-        <v>-0.01635363802481438</v>
+        <v>-23.7229445036577</v>
       </c>
       <c r="L27">
-        <v>1.585290690707295</v>
+        <v>6.485737107460135</v>
       </c>
       <c r="M27">
-        <v>0.2326386375630732</v>
-      </c>
-      <c r="N27">
-        <v>1.304595146808368</v>
+        <v>2.549396886789191E-16</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>1.520645194869581</v>
+        <v>-3.511290391677422</v>
       </c>
       <c r="G28">
-        <v>0.5114997136681834</v>
+        <v>1.751985142324548</v>
       </c>
       <c r="H28">
-        <v>2.972915046157863</v>
+        <v>-2.00417817871367</v>
       </c>
       <c r="I28">
-        <v>0.01267909727810817</v>
+        <v>0.06479240799018404</v>
       </c>
       <c r="J28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K28">
-        <v>0.3948419156947871</v>
+        <v>-7.26892480236489</v>
       </c>
       <c r="L28">
-        <v>2.646448474044375</v>
+        <v>0.2463440190100465</v>
       </c>
       <c r="M28">
-        <v>0.3355495045113385</v>
+        <v>-0.4754847166404753</v>
       </c>
       <c r="N28">
-        <v>1.427491004498004</v>
+        <v>1.017681660032122</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F29">
-        <v>-0.9318124714118717</v>
+        <v>0.6805961087246314</v>
       </c>
       <c r="G29">
-        <v>0.8154672853588478</v>
+        <v>1.322614030297522</v>
       </c>
       <c r="H29">
-        <v>-1.142673027038511</v>
+        <v>0.514584068468963</v>
       </c>
       <c r="I29">
-        <v>0.2774357148236511</v>
+        <v>0.6148709436016764</v>
       </c>
       <c r="J29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K29">
-        <v>-2.726643865026909</v>
+        <v>-2.15612885671081</v>
       </c>
       <c r="L29">
-        <v>0.863018922203166</v>
+        <v>3.517321074160073</v>
       </c>
       <c r="M29">
-        <v>-0.1351747730466991</v>
+        <v>0.1220833868876404</v>
       </c>
       <c r="N29">
-        <v>1.568095544415512</v>
+        <v>1.017681660032122</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="F30">
-        <v>0.9867245696950405</v>
+        <v>-10.6127934040996</v>
       </c>
       <c r="G30">
-        <v>0.4699494710336582</v>
+        <v>5.175514159846477</v>
       </c>
       <c r="H30">
-        <v>2.099639707061976</v>
+        <v>-2.050577599890946</v>
       </c>
       <c r="I30">
-        <v>0.05963750798020791</v>
+        <v>0.05951621020672625</v>
       </c>
       <c r="J30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K30">
-        <v>-0.04762724204295654</v>
+        <v>-21.71316727726842</v>
       </c>
       <c r="L30">
-        <v>2.021076381433037</v>
+        <v>0.4875804690692256</v>
       </c>
       <c r="M30">
-        <v>0.2371556470963132</v>
-      </c>
-      <c r="N30">
-        <v>1.429560569335166</v>
+        <v>2.705530520589896E-16</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="F31">
-        <v>0.04877290991791785</v>
+        <v>-4.411999436516661</v>
       </c>
       <c r="G31">
-        <v>0.01471203163979136</v>
+        <v>1.309432873444871</v>
       </c>
       <c r="H31">
-        <v>3.315171630409131</v>
+        <v>-3.369397184072156</v>
       </c>
       <c r="I31">
-        <v>0.006890036529532064</v>
+        <v>0.004583616726171178</v>
       </c>
       <c r="J31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K31">
-        <v>0.0163919466039384</v>
+        <v>-7.22045363220318</v>
       </c>
       <c r="L31">
-        <v>0.08115387323189729</v>
+        <v>-1.603545240830142</v>
       </c>
       <c r="M31">
-        <v>0.35367424158886</v>
+        <v>-0.597455085703657</v>
       </c>
       <c r="N31">
-        <v>1.275322441065481</v>
+        <v>1.051471993332928</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="D32" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="F32">
-        <v>0.1039147134489807</v>
+        <v>5.448492357166543</v>
       </c>
       <c r="G32">
-        <v>0.03051255469370785</v>
+        <v>1.5482478081329</v>
       </c>
       <c r="H32">
-        <v>3.405637924850962</v>
+        <v>3.519134552327976</v>
       </c>
       <c r="I32">
-        <v>0.005870318770985708</v>
+        <v>0.00340331696787525</v>
       </c>
       <c r="J32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K32">
-        <v>0.03675703337164522</v>
+        <v>2.127831068685181</v>
       </c>
       <c r="L32">
-        <v>0.1710723935263161</v>
+        <v>8.769153645647906</v>
       </c>
       <c r="M32">
-        <v>0.5037108654893194</v>
+        <v>0.6240062304031372</v>
       </c>
       <c r="N32">
-        <v>2.451268394797905</v>
+        <v>1.051471993332927</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="E33" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F33">
-        <v>0.09609551223353392</v>
+        <v>-10.19144750992142</v>
       </c>
       <c r="G33">
-        <v>0.0368750849263641</v>
+        <v>5.237262160554294</v>
       </c>
       <c r="H33">
-        <v>2.605973990986791</v>
+        <v>-1.945949467009839</v>
       </c>
       <c r="I33">
-        <v>0.02443231642067811</v>
+        <v>0.07360487493619533</v>
       </c>
       <c r="J33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K33">
-        <v>0.01493399753348766</v>
+        <v>-21.50586452726152</v>
       </c>
       <c r="L33">
-        <v>0.1772570269335802</v>
+        <v>1.122969507418674</v>
       </c>
       <c r="M33">
-        <v>0.2877308923613218</v>
-      </c>
-      <c r="N33">
-        <v>1.366022981771411</v>
+        <v>2.625400713087132E-16</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F34">
-        <v>-8.618603698098783</v>
+        <v>-4.366789316193658</v>
       </c>
       <c r="G34">
-        <v>7.042351060199127</v>
+        <v>1.320570139566511</v>
       </c>
       <c r="H34">
-        <v>-1.223824774485907</v>
+        <v>-3.30674546194653</v>
       </c>
       <c r="I34">
-        <v>0.2412163428046945</v>
+        <v>0.005673610803694174</v>
       </c>
       <c r="J34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K34">
-        <v>-23.7229445036577</v>
+        <v>-7.219707654373844</v>
       </c>
       <c r="L34">
-        <v>6.485737107460135</v>
+        <v>-1.513870978013472</v>
       </c>
       <c r="M34">
-        <v>2.549396886789191E-16</v>
+        <v>-0.591332914406741</v>
+      </c>
+      <c r="N34">
+        <v>1.053043406545435</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35">
+        <v>-0.9611352860384266</v>
+      </c>
+      <c r="G35">
+        <v>1.084507089405542</v>
+      </c>
+      <c r="H35">
+        <v>-0.8862415888542138</v>
+      </c>
+      <c r="I35">
+        <v>0.3915870564538799</v>
+      </c>
+      <c r="J35" t="s">
         <v>76</v>
       </c>
-      <c r="B35" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" t="s">
-        <v>20</v>
-      </c>
-      <c r="F35">
-        <v>-3.511290391677422</v>
-      </c>
-      <c r="G35">
-        <v>1.751985142324548</v>
-      </c>
-      <c r="H35">
-        <v>-2.00417817871367</v>
-      </c>
-      <c r="I35">
-        <v>0.06479240799018404</v>
-      </c>
-      <c r="J35" t="s">
-        <v>78</v>
-      </c>
       <c r="K35">
-        <v>-7.26892480236489</v>
+        <v>-3.304070409701851</v>
       </c>
       <c r="L35">
-        <v>0.2463440190100465</v>
+        <v>1.381799837624998</v>
       </c>
       <c r="M35">
-        <v>-0.4754847166404753</v>
+        <v>-0.17240570357752</v>
       </c>
       <c r="N35">
-        <v>1.017681660032122</v>
+        <v>1.246185532354503</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F36">
-        <v>0.6805961087246314</v>
+        <v>6.103712680342809</v>
       </c>
       <c r="G36">
-        <v>1.322614030297522</v>
+        <v>1.726552559379775</v>
       </c>
       <c r="H36">
-        <v>0.514584068468963</v>
+        <v>3.535202358702262</v>
       </c>
       <c r="I36">
-        <v>0.6148709436016764</v>
+        <v>0.003658663645030331</v>
       </c>
       <c r="J36" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="K36">
-        <v>-2.15612885671081</v>
+        <v>2.37372264732313</v>
       </c>
       <c r="L36">
-        <v>3.517321074160073</v>
+        <v>9.83370271336249</v>
       </c>
       <c r="M36">
-        <v>0.1220833868876404</v>
+        <v>0.6990474596362041</v>
       </c>
       <c r="N36">
-        <v>1.017681660032122</v>
+        <v>1.287562935668985</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -2572,39 +2521,39 @@
         <v>17</v>
       </c>
       <c r="F37">
-        <v>-10.6127934040996</v>
+        <v>-7.025807352399712</v>
       </c>
       <c r="G37">
-        <v>5.175514159846477</v>
+        <v>12.10172011153177</v>
       </c>
       <c r="H37">
-        <v>-2.050577599890946</v>
+        <v>-0.5805627041154916</v>
       </c>
       <c r="I37">
-        <v>0.05951621020672625</v>
+        <v>0.5732365592471065</v>
       </c>
       <c r="J37" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K37">
-        <v>-21.71316727726842</v>
+        <v>-33.66151372946366</v>
       </c>
       <c r="L37">
-        <v>0.4875804690692256</v>
+        <v>19.60989902466424</v>
       </c>
       <c r="M37">
-        <v>2.705530520589896E-16</v>
+        <v>-5.082782219216875E-16</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D38" t="s">
         <v>19</v>
@@ -2613,1207 +2562,600 @@
         <v>20</v>
       </c>
       <c r="F38">
-        <v>-4.411999436516661</v>
+        <v>-3.532744279421006</v>
       </c>
       <c r="G38">
-        <v>1.309432873444871</v>
+        <v>2.977497728821761</v>
       </c>
       <c r="H38">
-        <v>-3.369397184072156</v>
+        <v>-1.186480931697961</v>
       </c>
       <c r="I38">
-        <v>0.004583616726171178</v>
+        <v>0.260426198282804</v>
       </c>
       <c r="J38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K38">
-        <v>-7.22045363220318</v>
+        <v>-10.08617259476426</v>
       </c>
       <c r="L38">
-        <v>-1.603545240830142</v>
+        <v>3.020684035922248</v>
       </c>
       <c r="M38">
-        <v>-0.597455085703657</v>
+        <v>-0.4783899151848027</v>
       </c>
       <c r="N38">
-        <v>1.051471993332928</v>
+        <v>5.89942369691529</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D39" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F39">
-        <v>5.448492357166543</v>
+        <v>5.833484528910711</v>
       </c>
       <c r="G39">
-        <v>1.5482478081329</v>
+        <v>33.62541035817681</v>
       </c>
       <c r="H39">
-        <v>3.519134552327976</v>
+        <v>0.1734844115439074</v>
       </c>
       <c r="I39">
-        <v>0.00340331696787525</v>
+        <v>0.865421941006731</v>
       </c>
       <c r="J39" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="K39">
-        <v>2.127831068685181</v>
+        <v>-68.17554467142811</v>
       </c>
       <c r="L39">
-        <v>8.769153645647906</v>
+        <v>79.84251372924955</v>
       </c>
       <c r="M39">
-        <v>0.6240062304031372</v>
+        <v>1.046393800253498</v>
       </c>
       <c r="N39">
-        <v>1.051471993332927</v>
+        <v>1320.190136266348</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F40">
-        <v>-10.19144750992142</v>
+        <v>35.69942855371251</v>
       </c>
       <c r="G40">
-        <v>5.237262160554294</v>
+        <v>32.06615363008937</v>
       </c>
       <c r="H40">
-        <v>-1.945949467009839</v>
+        <v>1.113305604580334</v>
       </c>
       <c r="I40">
-        <v>0.07360487493619533</v>
+        <v>0.2893137205361322</v>
       </c>
       <c r="J40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K40">
-        <v>-21.50586452726152</v>
+        <v>-34.87769972733284</v>
       </c>
       <c r="L40">
-        <v>1.122969507418674</v>
+        <v>106.2765568347579</v>
       </c>
       <c r="M40">
-        <v>2.625400713087132E-16</v>
+        <v>4.088592656287188</v>
+      </c>
+      <c r="N40">
+        <v>489.4248092751843</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E41" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F41">
-        <v>-4.366789316193658</v>
+        <v>1.763626570521479</v>
       </c>
       <c r="G41">
-        <v>1.320570139566511</v>
+        <v>8.33421038896889</v>
       </c>
       <c r="H41">
-        <v>-3.30674546194653</v>
+        <v>0.2116129169064179</v>
       </c>
       <c r="I41">
-        <v>0.005673610803694174</v>
+        <v>0.8362786983247414</v>
       </c>
       <c r="J41" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="K41">
-        <v>-7.219707654373844</v>
+        <v>-16.57984681668061</v>
       </c>
       <c r="L41">
-        <v>-1.513870978013472</v>
+        <v>20.10709995772357</v>
       </c>
       <c r="M41">
-        <v>-0.591332914406741</v>
+        <v>1.256225479341864</v>
       </c>
       <c r="N41">
-        <v>1.053043406545435</v>
+        <v>1278.845061605036</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C42" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="E42" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="F42">
-        <v>-0.9611352860384266</v>
+        <v>7.413311777533256</v>
       </c>
       <c r="G42">
-        <v>1.084507089405542</v>
+        <v>7.850372629092067</v>
       </c>
       <c r="H42">
-        <v>-0.8862415888542138</v>
+        <v>0.9443261011663137</v>
       </c>
       <c r="I42">
-        <v>0.3915870564538799</v>
+        <v>0.3652831392486496</v>
       </c>
       <c r="J42" t="s">
         <v>82</v>
       </c>
       <c r="K42">
-        <v>-3.304070409701851</v>
+        <v>-9.865241880287968</v>
       </c>
       <c r="L42">
-        <v>1.381799837624998</v>
+        <v>24.69186543535448</v>
       </c>
       <c r="M42">
-        <v>-0.17240570357752</v>
+        <v>3.432787595952272</v>
       </c>
       <c r="N42">
-        <v>1.246185532354503</v>
+        <v>479.5312997909448</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D43" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F43">
-        <v>6.103712680342809</v>
+        <v>-8.565392342781157</v>
       </c>
       <c r="G43">
-        <v>1.726552559379775</v>
+        <v>27.82231610331168</v>
       </c>
       <c r="H43">
-        <v>3.535202358702262</v>
+        <v>-0.3078605070467739</v>
       </c>
       <c r="I43">
-        <v>0.003658663645030331</v>
+        <v>0.7735531303060883</v>
       </c>
       <c r="J43" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="K43">
-        <v>2.37372264732313</v>
+        <v>-85.81252570308662</v>
       </c>
       <c r="L43">
-        <v>9.83370271336249</v>
+        <v>68.68174101752432</v>
       </c>
       <c r="M43">
-        <v>0.6990474596362041</v>
-      </c>
-      <c r="N43">
-        <v>1.287562935668985</v>
+        <v>-3.479997159803594E-16</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F44">
-        <v>-10.96196978127127</v>
+        <v>-3.28623266226647</v>
       </c>
       <c r="G44">
-        <v>5.734580473718911</v>
+        <v>6.517868070138991</v>
       </c>
       <c r="H44">
-        <v>-1.911555663314699</v>
+        <v>-0.5041882755071464</v>
       </c>
       <c r="I44">
-        <v>0.08010512883973041</v>
+        <v>0.6406338509391254</v>
       </c>
       <c r="J44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K44">
-        <v>-23.4565472901692</v>
+        <v>-21.38273556192886</v>
       </c>
       <c r="L44">
-        <v>1.532607727626663</v>
+        <v>14.81027023739592</v>
       </c>
       <c r="M44">
-        <v>2.873883725421411E-16</v>
+        <v>-0.335075842545724</v>
+      </c>
+      <c r="N44">
+        <v>9.83669863928314</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F45">
-        <v>-4.495171905987651</v>
+        <v>-1.886091124073796</v>
       </c>
       <c r="G45">
-        <v>1.40097551703797</v>
+        <v>47.80442939832684</v>
       </c>
       <c r="H45">
-        <v>-3.20860132908791</v>
+        <v>-0.03945431726332475</v>
       </c>
       <c r="I45">
-        <v>0.007511679238218578</v>
+        <v>0.9704188544286534</v>
       </c>
       <c r="J45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K45">
-        <v>-7.547635336559658</v>
+        <v>-134.6124651338318</v>
       </c>
       <c r="L45">
-        <v>-1.442708475415644</v>
+        <v>130.8402828856842</v>
       </c>
       <c r="M45">
-        <v>-0.6087179644938699</v>
+        <v>-0.3248691183222625</v>
       </c>
       <c r="N45">
-        <v>1.109147684013403</v>
+        <v>1509.998127926904</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D46" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E46" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F46">
-        <v>-0.2718809205545135</v>
+        <v>47.74848681303564</v>
       </c>
       <c r="G46">
-        <v>2.029388629905962</v>
+        <v>70.70238063213495</v>
       </c>
       <c r="H46">
-        <v>-0.1339718359253406</v>
+        <v>0.6753448241222796</v>
       </c>
       <c r="I46">
-        <v>0.8956454974518373</v>
+        <v>0.5364845963625324</v>
       </c>
       <c r="J46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K46">
-        <v>-4.693538903774424</v>
+        <v>-148.5527918188867</v>
       </c>
       <c r="L46">
-        <v>4.149777062665396</v>
+        <v>244.049765444958</v>
       </c>
       <c r="M46">
-        <v>-0.04876922331164</v>
+        <v>4.662763691735115</v>
       </c>
       <c r="N46">
-        <v>4.083695181374016</v>
+        <v>1061.657115641728</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D47" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E47" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F47">
-        <v>5.615013523159514</v>
+        <v>-0.2656776392476792</v>
       </c>
       <c r="G47">
-        <v>2.150331785339641</v>
+        <v>11.86093317114378</v>
       </c>
       <c r="H47">
-        <v>2.611231234845293</v>
+        <v>-0.02239938758731403</v>
       </c>
       <c r="I47">
-        <v>0.022749906973555</v>
+        <v>0.9832022150942343</v>
       </c>
       <c r="J47" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K47">
-        <v>0.9298430412202663</v>
+        <v>-33.19690748534797</v>
       </c>
       <c r="L47">
-        <v>10.30018400509876</v>
+        <v>32.66555220685262</v>
       </c>
       <c r="M47">
-        <v>0.6430776061639811</v>
+        <v>-0.183286808004701</v>
       </c>
       <c r="N47">
-        <v>1.869066553601106</v>
+        <v>1491.20977191473</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D48" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E48" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F48">
-        <v>2.39211618095861</v>
+        <v>10.19545284992796</v>
       </c>
       <c r="G48">
-        <v>5.87097161727069</v>
+        <v>17.20902092055179</v>
       </c>
       <c r="H48">
-        <v>0.4074480915427525</v>
+        <v>0.5924481640760915</v>
       </c>
       <c r="I48">
-        <v>0.6908536520968989</v>
+        <v>0.5854191223842596</v>
       </c>
       <c r="J48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K48">
-        <v>-10.39963210136293</v>
+        <v>-37.58444905018449</v>
       </c>
       <c r="L48">
-        <v>15.18386446328015</v>
+        <v>57.9753547500404</v>
       </c>
       <c r="M48">
-        <v>0.133563588483288</v>
+        <v>4.088973628664985</v>
       </c>
       <c r="N48">
-        <v>3.311465531455321</v>
+        <v>1060.905052376005</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C49" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D49" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="F49">
-        <v>-18.72741983290402</v>
+        <v>1.498309202610451</v>
       </c>
       <c r="G49">
-        <v>7.269376857488876</v>
+        <v>1.797450544274193</v>
       </c>
       <c r="H49">
-        <v>-2.576207039481124</v>
+        <v>0.8335746468148116</v>
       </c>
       <c r="I49">
-        <v>0.06157355750543729</v>
+        <v>0.4514035274989894</v>
       </c>
       <c r="J49" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K49">
-        <v>-38.91044562671712</v>
+        <v>-3.492213562874741</v>
       </c>
       <c r="L49">
-        <v>1.455605960909089</v>
+        <v>6.488831968095644</v>
       </c>
       <c r="M49">
-        <v>4.012689049409911E-16</v>
+        <v>0.2098052536131294</v>
+      </c>
+      <c r="N49">
+        <v>1.410887344908986</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="E50" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F50">
-        <v>-4.966980456214547</v>
+        <v>0.6257416865540727</v>
       </c>
       <c r="G50">
-        <v>1.677229783569794</v>
+        <v>3.84361133467724</v>
       </c>
       <c r="H50">
-        <v>-2.961419183507994</v>
+        <v>0.1628004582327568</v>
       </c>
       <c r="I50">
-        <v>0.04149593869306766</v>
+        <v>0.8785691959241584</v>
       </c>
       <c r="J50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K50">
-        <v>-9.623716879098854</v>
+        <v>-10.04583418989331</v>
       </c>
       <c r="L50">
-        <v>-0.3102440333302399</v>
+        <v>11.29731756300145</v>
       </c>
       <c r="M50">
-        <v>-0.5064508001470377</v>
+        <v>0.0381518160393763</v>
       </c>
       <c r="N50">
-        <v>1.425851276415599</v>
+        <v>1.223116427490704</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D51" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E51" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F51">
-        <v>1.249842556859027</v>
+        <v>0.04228262003223595</v>
       </c>
       <c r="G51">
-        <v>1.217447443340111</v>
+        <v>0.06472401480274068</v>
       </c>
       <c r="H51">
-        <v>1.026609044765037</v>
+        <v>0.653275606605997</v>
       </c>
       <c r="I51">
-        <v>0.3626284726559762</v>
+        <v>0.5492260186729562</v>
       </c>
       <c r="J51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K51">
-        <v>-2.130333438038192</v>
+        <v>-0.1374200540555829</v>
       </c>
       <c r="L51">
-        <v>4.630018551756246</v>
+        <v>0.2219852941200548</v>
       </c>
       <c r="M51">
-        <v>0.2152787022355498</v>
+        <v>0.1496423847524685</v>
       </c>
       <c r="N51">
-        <v>2.143835396236969</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
-      <c r="A52" t="s">
-        <v>76</v>
-      </c>
-      <c r="B52" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52" t="s">
-        <v>47</v>
-      </c>
-      <c r="D52" t="s">
-        <v>29</v>
-      </c>
-      <c r="E52" t="s">
-        <v>30</v>
-      </c>
-      <c r="F52">
-        <v>1.243798567917556</v>
-      </c>
-      <c r="G52">
-        <v>2.679141479653663</v>
-      </c>
-      <c r="H52">
-        <v>0.4642526635354636</v>
-      </c>
-      <c r="I52">
-        <v>0.6666087102163512</v>
-      </c>
-      <c r="J52" t="s">
-        <v>91</v>
-      </c>
-      <c r="K52">
-        <v>-6.19469067939923</v>
-      </c>
-      <c r="L52">
-        <v>8.682287815234343</v>
-      </c>
-      <c r="M52">
-        <v>0.1214601590418344</v>
-      </c>
-      <c r="N52">
-        <v>3.337016537646436</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
-      <c r="A53" t="s">
-        <v>76</v>
-      </c>
-      <c r="B53" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" t="s">
-        <v>47</v>
-      </c>
-      <c r="D53" t="s">
-        <v>52</v>
-      </c>
-      <c r="E53" t="s">
-        <v>53</v>
-      </c>
-      <c r="F53">
-        <v>1.847457872168211</v>
-      </c>
-      <c r="G53">
-        <v>1.275719562466676</v>
-      </c>
-      <c r="H53">
-        <v>1.448169273657642</v>
-      </c>
-      <c r="I53">
-        <v>0.221141005095729</v>
-      </c>
-      <c r="J53" t="s">
-        <v>92</v>
-      </c>
-      <c r="K53">
-        <v>-1.694507462647461</v>
-      </c>
-      <c r="L53">
-        <v>5.389423206983883</v>
-      </c>
-      <c r="M53">
-        <v>0.258695846447791</v>
-      </c>
-      <c r="N53">
-        <v>1.555749716722623</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
-      <c r="A54" t="s">
-        <v>76</v>
-      </c>
-      <c r="B54" t="s">
-        <v>46</v>
-      </c>
-      <c r="C54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D54" t="s">
-        <v>55</v>
-      </c>
-      <c r="E54" t="s">
-        <v>56</v>
-      </c>
-      <c r="F54">
-        <v>0.01975895031218683</v>
-      </c>
-      <c r="G54">
-        <v>0.0516323996092311</v>
-      </c>
-      <c r="H54">
-        <v>0.3826851058972326</v>
-      </c>
-      <c r="I54">
-        <v>0.7214190301039676</v>
-      </c>
-      <c r="J54" t="s">
-        <v>93</v>
-      </c>
-      <c r="K54">
-        <v>-0.1235955728524793</v>
-      </c>
-      <c r="L54">
-        <v>0.163113473476853</v>
-      </c>
-      <c r="M54">
-        <v>0.0699288843185909</v>
-      </c>
-      <c r="N54">
-        <v>1.627906867265828</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="A55" t="s">
-        <v>76</v>
-      </c>
-      <c r="B55" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" t="s">
-        <v>47</v>
-      </c>
-      <c r="D55" t="s">
-        <v>58</v>
-      </c>
-      <c r="E55" t="s">
-        <v>59</v>
-      </c>
-      <c r="F55">
-        <v>-1.025782749973404</v>
-      </c>
-      <c r="G55">
-        <v>2.933548323550968</v>
-      </c>
-      <c r="H55">
-        <v>-0.3496730364856328</v>
-      </c>
-      <c r="I55">
-        <v>0.7442180667406819</v>
-      </c>
-      <c r="J55" t="s">
-        <v>94</v>
-      </c>
-      <c r="K55">
-        <v>-9.170618633757682</v>
-      </c>
-      <c r="L55">
-        <v>7.119053133810874</v>
-      </c>
-      <c r="M55">
-        <v>-0.06254254049920883</v>
-      </c>
-      <c r="N55">
-        <v>1.559646673766648</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
-      <c r="A56" t="s">
-        <v>76</v>
-      </c>
-      <c r="B56" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" t="s">
-        <v>47</v>
-      </c>
-      <c r="D56" t="s">
-        <v>61</v>
-      </c>
-      <c r="E56" t="s">
-        <v>61</v>
-      </c>
-      <c r="F56">
-        <v>0.2798741018750939</v>
-      </c>
-      <c r="G56">
-        <v>0.1189600474418274</v>
-      </c>
-      <c r="H56">
-        <v>2.352673085574845</v>
-      </c>
-      <c r="I56">
-        <v>0.07828645397077533</v>
-      </c>
-      <c r="J56" t="s">
-        <v>95</v>
-      </c>
-      <c r="K56">
-        <v>-0.05041193955886503</v>
-      </c>
-      <c r="L56">
-        <v>0.6101601433090529</v>
-      </c>
-      <c r="M56">
-        <v>0.6480674339436279</v>
-      </c>
-      <c r="N56">
-        <v>3.699275739211368</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
-      <c r="A57" t="s">
-        <v>76</v>
-      </c>
-      <c r="B57" t="s">
-        <v>46</v>
-      </c>
-      <c r="C57" t="s">
-        <v>47</v>
-      </c>
-      <c r="D57" t="s">
-        <v>63</v>
-      </c>
-      <c r="E57" t="s">
-        <v>64</v>
-      </c>
-      <c r="F57">
-        <v>0.1773886497551378</v>
-      </c>
-      <c r="G57">
-        <v>0.1530989476918103</v>
-      </c>
-      <c r="H57">
-        <v>1.158653618653362</v>
-      </c>
-      <c r="I57">
-        <v>0.3110588120831378</v>
-      </c>
-      <c r="J57" t="s">
-        <v>96</v>
-      </c>
-      <c r="K57">
-        <v>-0.2476821741747219</v>
-      </c>
-      <c r="L57">
-        <v>0.6024594736849975</v>
-      </c>
-      <c r="M57">
-        <v>0.2405936971950969</v>
-      </c>
-      <c r="N57">
-        <v>2.102135582397388</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
-      <c r="A58" t="s">
-        <v>76</v>
-      </c>
-      <c r="B58" t="s">
-        <v>66</v>
-      </c>
-      <c r="C58" t="s">
-        <v>67</v>
-      </c>
-      <c r="D58" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58">
-        <v>-11.31473731403601</v>
-      </c>
-      <c r="G58">
-        <v>5.251139173824305</v>
-      </c>
-      <c r="H58">
-        <v>-2.154720516728507</v>
-      </c>
-      <c r="I58">
-        <v>0.05957723707023269</v>
-      </c>
-      <c r="J58" t="s">
-        <v>72</v>
-      </c>
-      <c r="K58">
-        <v>-23.19363940895291</v>
-      </c>
-      <c r="L58">
-        <v>0.564164780880887</v>
-      </c>
-      <c r="M58">
-        <v>1.943862769726028E-16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
-      <c r="A59" t="s">
-        <v>76</v>
-      </c>
-      <c r="B59" t="s">
-        <v>66</v>
-      </c>
-      <c r="C59" t="s">
-        <v>67</v>
-      </c>
-      <c r="D59" t="s">
-        <v>19</v>
-      </c>
-      <c r="E59" t="s">
-        <v>20</v>
-      </c>
-      <c r="F59">
-        <v>-3.431848801428043</v>
-      </c>
-      <c r="G59">
-        <v>1.347143923204537</v>
-      </c>
-      <c r="H59">
-        <v>-2.547499745435131</v>
-      </c>
-      <c r="I59">
-        <v>0.03132297314190588</v>
-      </c>
-      <c r="J59" t="s">
-        <v>35</v>
-      </c>
-      <c r="K59">
-        <v>-6.479300076625263</v>
-      </c>
-      <c r="L59">
-        <v>-0.3843975262308237</v>
-      </c>
-      <c r="M59">
-        <v>-0.4647270583964503</v>
-      </c>
-      <c r="N59">
-        <v>1.401608079879456</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
-      <c r="A60" t="s">
-        <v>76</v>
-      </c>
-      <c r="B60" t="s">
-        <v>66</v>
-      </c>
-      <c r="C60" t="s">
-        <v>67</v>
-      </c>
-      <c r="D60" t="s">
-        <v>22</v>
-      </c>
-      <c r="E60" t="s">
-        <v>23</v>
-      </c>
-      <c r="F60">
-        <v>0.8354622508837038</v>
-      </c>
-      <c r="G60">
-        <v>1.212757763873726</v>
-      </c>
-      <c r="H60">
-        <v>0.6888945804107778</v>
-      </c>
-      <c r="I60">
-        <v>0.5082578268576731</v>
-      </c>
-      <c r="J60" t="s">
-        <v>97</v>
-      </c>
-      <c r="K60">
-        <v>-1.90798641140238</v>
-      </c>
-      <c r="L60">
-        <v>3.578910913169788</v>
-      </c>
-      <c r="M60">
-        <v>0.1498628333267797</v>
-      </c>
-      <c r="N60">
-        <v>1.99315610249821</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
-      <c r="A61" t="s">
-        <v>76</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61" t="s">
-        <v>67</v>
-      </c>
-      <c r="D61" t="s">
-        <v>29</v>
-      </c>
-      <c r="E61" t="s">
-        <v>30</v>
-      </c>
-      <c r="F61">
-        <v>2.564770938900524</v>
-      </c>
-      <c r="G61">
-        <v>2.005639917102749</v>
-      </c>
-      <c r="H61">
-        <v>1.278779364645609</v>
-      </c>
-      <c r="I61">
-        <v>0.2329626869388863</v>
-      </c>
-      <c r="J61" t="s">
-        <v>98</v>
-      </c>
-      <c r="K61">
-        <v>-1.972301765567457</v>
-      </c>
-      <c r="L61">
-        <v>7.101843643368506</v>
-      </c>
-      <c r="M61">
-        <v>0.2937386969673805</v>
-      </c>
-      <c r="N61">
-        <v>2.222235394349132</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14">
-      <c r="A62" t="s">
-        <v>76</v>
-      </c>
-      <c r="B62" t="s">
-        <v>66</v>
-      </c>
-      <c r="C62" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" t="s">
-        <v>52</v>
-      </c>
-      <c r="E62" t="s">
-        <v>53</v>
-      </c>
-      <c r="F62">
-        <v>1.872727546408498</v>
-      </c>
-      <c r="G62">
-        <v>1.325133927693838</v>
-      </c>
-      <c r="H62">
-        <v>1.413236433895894</v>
-      </c>
-      <c r="I62">
-        <v>0.1912253282123781</v>
-      </c>
-      <c r="J62" t="s">
-        <v>99</v>
-      </c>
-      <c r="K62">
-        <v>-1.124933659791035</v>
-      </c>
-      <c r="L62">
-        <v>4.870388752608032</v>
-      </c>
-      <c r="M62">
-        <v>0.2618921893348972</v>
-      </c>
-      <c r="N62">
-        <v>1.446353375905712</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-      <c r="B63" t="s">
-        <v>66</v>
-      </c>
-      <c r="C63" t="s">
-        <v>67</v>
-      </c>
-      <c r="D63" t="s">
-        <v>55</v>
-      </c>
-      <c r="E63" t="s">
-        <v>56</v>
-      </c>
-      <c r="F63">
-        <v>0.01349571147609272</v>
-      </c>
-      <c r="G63">
-        <v>0.04665875531089527</v>
-      </c>
-      <c r="H63">
-        <v>0.2892428524114818</v>
-      </c>
-      <c r="I63">
-        <v>0.7789477732973502</v>
-      </c>
-      <c r="J63" t="s">
-        <v>100</v>
-      </c>
-      <c r="K63">
-        <v>-0.09205372605769779</v>
-      </c>
-      <c r="L63">
-        <v>0.1190451490098832</v>
-      </c>
-      <c r="M63">
-        <v>0.05375072472702178</v>
-      </c>
-      <c r="N63">
-        <v>1.454461897852155</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
-      <c r="A64" t="s">
-        <v>76</v>
-      </c>
-      <c r="B64" t="s">
-        <v>66</v>
-      </c>
-      <c r="C64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D64" t="s">
-        <v>61</v>
-      </c>
-      <c r="E64" t="s">
-        <v>61</v>
-      </c>
-      <c r="F64">
-        <v>0.2200514808169769</v>
-      </c>
-      <c r="G64">
-        <v>0.09188281813026206</v>
-      </c>
-      <c r="H64">
-        <v>2.394914362607059</v>
-      </c>
-      <c r="I64">
-        <v>0.04023194596771432</v>
-      </c>
-      <c r="J64" t="s">
-        <v>101</v>
-      </c>
-      <c r="K64">
-        <v>0.01219810564551979</v>
-      </c>
-      <c r="L64">
-        <v>0.427904855988434</v>
-      </c>
-      <c r="M64">
-        <v>0.5143816223835602</v>
-      </c>
-      <c r="N64">
-        <v>1.942897468199728</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
-      <c r="A65" t="s">
-        <v>76</v>
-      </c>
-      <c r="B65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C65" t="s">
-        <v>67</v>
-      </c>
-      <c r="D65" t="s">
-        <v>63</v>
-      </c>
-      <c r="E65" t="s">
-        <v>64</v>
-      </c>
-      <c r="F65">
-        <v>0.007100275402761196</v>
-      </c>
-      <c r="G65">
-        <v>0.09446957910510312</v>
-      </c>
-      <c r="H65">
-        <v>0.07515938432266868</v>
-      </c>
-      <c r="I65">
-        <v>0.941732019260235</v>
-      </c>
-      <c r="J65" t="s">
-        <v>102</v>
-      </c>
-      <c r="K65">
-        <v>-0.2066047596363794</v>
-      </c>
-      <c r="L65">
-        <v>0.2208053104419019</v>
-      </c>
-      <c r="M65">
-        <v>0.01464264356077172</v>
-      </c>
-      <c r="N65">
-        <v>1.598569509677345</v>
+        <v>1.168597551198277</v>
       </c>
     </row>
   </sheetData>
@@ -3823,7 +3165,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1">
@@ -3834,61 +3176,61 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -3899,7 +3241,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D2">
         <v>19</v>
@@ -3953,7 +3295,7 @@
         <v>16</v>
       </c>
       <c r="U2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -3964,7 +3306,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D3">
         <v>19</v>
@@ -4018,7 +3360,7 @@
         <v>26</v>
       </c>
       <c r="U3" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -4029,7 +3371,7 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D4">
         <v>19</v>
@@ -4083,7 +3425,7 @@
         <v>33</v>
       </c>
       <c r="U4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -4094,61 +3436,61 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D5">
         <v>19</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0.5656253061014269</v>
+        <v>0.5681626756787765</v>
       </c>
       <c r="G5">
-        <v>0.4415182507018346</v>
+        <v>0.4020713970936907</v>
       </c>
       <c r="H5">
-        <v>4.557559634947918</v>
+        <v>3.420785730105122</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K5">
-        <v>0.0144703403908267</v>
+        <v>0.03427369420482255</v>
       </c>
       <c r="L5">
-        <v>1.595053176446366</v>
+        <v>1.650423269587353</v>
       </c>
       <c r="M5">
-        <v>1.36918579146961</v>
+        <v>1.365180932568826</v>
       </c>
       <c r="N5">
-        <v>77.85988177584804</v>
+        <v>79.74856916681688</v>
       </c>
       <c r="O5">
-        <v>83.52651565084668</v>
+        <v>86.35964202098197</v>
       </c>
       <c r="P5">
-        <v>1.372949653581145</v>
+        <v>53.86518864767415</v>
       </c>
       <c r="Q5">
-        <v>0.3219138496843572</v>
+        <v>0.5681977399499447</v>
       </c>
       <c r="R5">
-        <v>0.2229713177310755</v>
+        <v>0.2598850523000154</v>
       </c>
       <c r="S5">
-        <v>0.969416775756163</v>
+        <v>0.8794975187458534</v>
       </c>
       <c r="T5" t="s">
         <v>39</v>
       </c>
       <c r="U5" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -4156,10 +3498,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D6">
         <v>18</v>
@@ -4168,13 +3510,13 @@
         <v>8</v>
       </c>
       <c r="F6">
-        <v>0.9016419144511226</v>
+        <v>0.8790246632349847</v>
       </c>
       <c r="G6">
-        <v>0.8142125050743427</v>
+        <v>0.7714910305549711</v>
       </c>
       <c r="H6">
-        <v>10.31279887257922</v>
+        <v>8.174416146162267</v>
       </c>
       <c r="I6">
         <v>8</v>
@@ -4183,113 +3525,113 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>0.001020623048399414</v>
+        <v>0.002438185066128097</v>
       </c>
       <c r="L6">
-        <v>0.9405400689304357</v>
+        <v>1.04308737387962</v>
       </c>
       <c r="M6">
-        <v>0.6650622607183739</v>
+        <v>0.7375741554403465</v>
       </c>
       <c r="N6">
-        <v>56.39830096290471</v>
+        <v>60.12379593672846</v>
       </c>
       <c r="O6">
-        <v>65.30201854186636</v>
+        <v>69.0275135156901</v>
       </c>
       <c r="P6">
-        <v>3.274875819626642</v>
+        <v>61.08070029911875</v>
       </c>
       <c r="Q6">
-        <v>0.9564107679877191</v>
+        <v>0.4788638921806911</v>
       </c>
       <c r="R6">
-        <v>0.5997922517603256</v>
+        <v>0.9254893726900082</v>
       </c>
       <c r="S6">
-        <v>0.318606727007158</v>
+        <v>0.9793989291894669</v>
       </c>
       <c r="T6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="U6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>0.2256869953733925</v>
+      </c>
+      <c r="G7">
+        <v>0.1150708518553056</v>
+      </c>
+      <c r="H7">
+        <v>2.040271774042552</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>0.901832549824004</v>
-      </c>
-      <c r="G7">
-        <v>0.839362354257461</v>
-      </c>
-      <c r="H7">
-        <v>14.43620500376657</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>11</v>
-      </c>
       <c r="K7">
-        <v>9.695166233080134E-05</v>
+        <v>0.1668844505736521</v>
       </c>
       <c r="L7">
-        <v>0.8554494254447713</v>
+        <v>2.233996446339432</v>
       </c>
       <c r="M7">
-        <v>0.6508994147546787</v>
+        <v>2.027318740887332</v>
       </c>
       <c r="N7">
-        <v>55.60245827538432</v>
+        <v>80.2721896210583</v>
       </c>
       <c r="O7">
-        <v>64.10240908788228</v>
+        <v>83.60504299728316</v>
       </c>
       <c r="P7">
-        <v>2.451268394797905</v>
+        <v>1.017681660032122</v>
       </c>
       <c r="Q7">
-        <v>1.170373500273494</v>
+        <v>0.5018431757227956</v>
       </c>
       <c r="R7">
-        <v>0.7528928869508489</v>
+        <v>0.4220077889086216</v>
       </c>
       <c r="S7">
-        <v>0.3885499414135918</v>
+        <v>0.7979069126061417</v>
       </c>
       <c r="T7" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="U7" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D8">
         <v>17</v>
@@ -4298,13 +3640,13 @@
         <v>2</v>
       </c>
       <c r="F8">
-        <v>0.2256869953733925</v>
+        <v>0.581364133429465</v>
       </c>
       <c r="G8">
-        <v>0.1150708518553056</v>
+        <v>0.5215590096336744</v>
       </c>
       <c r="H8">
-        <v>2.040271774042552</v>
+        <v>9.720975336738347</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -4313,362 +3655,232 @@
         <v>14</v>
       </c>
       <c r="K8">
-        <v>0.1668844505736521</v>
+        <v>0.002253486890922358</v>
       </c>
       <c r="L8">
-        <v>2.233996446339432</v>
+        <v>1.642640090746519</v>
       </c>
       <c r="M8">
-        <v>2.027318740887332</v>
+        <v>1.490671592589143</v>
       </c>
       <c r="N8">
-        <v>80.2721896210583</v>
+        <v>69.81761968638281</v>
       </c>
       <c r="O8">
-        <v>83.60504299728316</v>
+        <v>73.15047306260767</v>
       </c>
       <c r="P8">
-        <v>1.017681660032122</v>
+        <v>1.051471993332928</v>
       </c>
       <c r="Q8">
-        <v>0.5018431757227956</v>
+        <v>0.3119360618233111</v>
       </c>
       <c r="R8">
-        <v>0.4220077889086216</v>
+        <v>0.9476168913915635</v>
       </c>
       <c r="S8">
-        <v>0.7979069126061417</v>
+        <v>0.3919919610818148</v>
       </c>
       <c r="T8" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="U8" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D9">
         <v>17</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>0.581364133429465</v>
+        <v>0.6052159001643111</v>
       </c>
       <c r="G9">
-        <v>0.5215590096336744</v>
+        <v>0.5141118771253059</v>
       </c>
       <c r="H9">
-        <v>9.720975336738347</v>
+        <v>6.643130346781668</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K9">
-        <v>0.002253486890922358</v>
+        <v>0.005860031563866003</v>
       </c>
       <c r="L9">
-        <v>1.642640090746519</v>
+        <v>1.655374913650029</v>
       </c>
       <c r="M9">
-        <v>1.490671592589143</v>
+        <v>1.44758336875928</v>
       </c>
       <c r="N9">
-        <v>69.81761968638281</v>
+        <v>70.82035793830373</v>
       </c>
       <c r="O9">
-        <v>73.15047306260767</v>
+        <v>74.98642465858481</v>
       </c>
       <c r="P9">
-        <v>1.051471993332928</v>
+        <v>1.287562935668985</v>
       </c>
       <c r="Q9">
-        <v>0.3119360618233111</v>
+        <v>0.2867174620062506</v>
       </c>
       <c r="R9">
-        <v>0.9476168913915635</v>
+        <v>0.9537540652610096</v>
       </c>
       <c r="S9">
-        <v>0.3919919610818148</v>
+        <v>0.4973830488955234</v>
       </c>
       <c r="T9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="U9" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D10">
         <v>17</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>0.6052159001643111</v>
+        <v>0.696872315126521</v>
       </c>
       <c r="G10">
-        <v>0.5141118771253059</v>
+        <v>0.5590870038203942</v>
       </c>
       <c r="H10">
-        <v>6.643130346781668</v>
+        <v>5.057667675317242</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K10">
-        <v>0.005860031563866003</v>
+        <v>0.01190990646581135</v>
       </c>
       <c r="L10">
-        <v>1.655374913650029</v>
+        <v>1.576901905053064</v>
       </c>
       <c r="M10">
-        <v>1.44758336875928</v>
+        <v>1.268459366590729</v>
       </c>
       <c r="N10">
-        <v>70.82035793830373</v>
+        <v>70.32921440355418</v>
       </c>
       <c r="O10">
-        <v>74.98642465858481</v>
+        <v>76.16170781194769</v>
       </c>
       <c r="P10">
-        <v>1.287562935668985</v>
+        <v>1320.190136266348</v>
       </c>
       <c r="Q10">
-        <v>0.2867174620062506</v>
+        <v>1.045986551806551</v>
       </c>
       <c r="R10">
-        <v>0.9537540652610096</v>
+        <v>0.912222834844275</v>
       </c>
       <c r="S10">
-        <v>0.4973830488955234</v>
+        <v>0.5275374953958908</v>
       </c>
       <c r="T10" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="U10" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>0.8203979138143715</v>
+      </c>
+      <c r="G11">
+        <v>0.4611937414431146</v>
+      </c>
+      <c r="H11">
+        <v>2.283932027845283</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11">
         <v>4</v>
       </c>
-      <c r="F11">
-        <v>0.610603011097244</v>
-      </c>
-      <c r="G11">
-        <v>0.4808040147963254</v>
-      </c>
-      <c r="H11">
-        <v>4.704219820634488</v>
-      </c>
-      <c r="I11">
-        <v>4</v>
-      </c>
-      <c r="J11">
-        <v>12</v>
-      </c>
       <c r="K11">
-        <v>0.01625842640885235</v>
+        <v>0.2215610425643967</v>
       </c>
       <c r="L11">
-        <v>1.711172887772359</v>
+        <v>1.968568108570851</v>
       </c>
       <c r="M11">
-        <v>1.437672789045799</v>
+        <v>1.091965116106979</v>
       </c>
       <c r="N11">
-        <v>72.58678350535749</v>
+        <v>59.17985409156405</v>
       </c>
       <c r="O11">
-        <v>77.5860635696948</v>
+        <v>64.82934766617942</v>
       </c>
       <c r="P11">
-        <v>4.083695181374016</v>
+        <v>1509.998127926904</v>
       </c>
       <c r="Q11">
-        <v>0.7336674483744495</v>
+        <v>2.834843051323265</v>
       </c>
       <c r="R11">
-        <v>0.7900021679569911</v>
+        <v>0.5945294488259011</v>
       </c>
       <c r="S11">
-        <v>0.5366288571540381</v>
+        <v>0.4051937054050931</v>
       </c>
       <c r="T11" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="U11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12">
-        <v>13</v>
-      </c>
-      <c r="E12">
-        <v>8</v>
-      </c>
-      <c r="F12">
-        <v>0.9179534138873856</v>
-      </c>
-      <c r="G12">
-        <v>0.7538602416621568</v>
-      </c>
-      <c r="H12">
-        <v>5.594098775952932</v>
-      </c>
-      <c r="I12">
-        <v>8</v>
-      </c>
-      <c r="J12">
-        <v>4</v>
-      </c>
-      <c r="K12">
-        <v>0.0569351108988928</v>
-      </c>
-      <c r="L12">
-        <v>1.330531050850008</v>
-      </c>
-      <c r="M12">
-        <v>0.7380458349902594</v>
-      </c>
-      <c r="N12">
-        <v>48.99491878211028</v>
-      </c>
-      <c r="O12">
-        <v>54.64441235672564</v>
-      </c>
-      <c r="P12">
-        <v>3.699275739211368</v>
-      </c>
-      <c r="Q12">
-        <v>26.82051809587888</v>
-      </c>
-      <c r="R12">
-        <v>0.9352860912391692</v>
-      </c>
-      <c r="S12">
-        <v>0.6480350161090446</v>
-      </c>
-      <c r="T12" t="s">
-        <v>47</v>
-      </c>
-      <c r="U12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="s">
-        <v>130</v>
-      </c>
-      <c r="D13">
-        <v>17</v>
-      </c>
-      <c r="E13">
-        <v>7</v>
-      </c>
-      <c r="F13">
-        <v>0.786310325341253</v>
-      </c>
-      <c r="G13">
-        <v>0.6201072450511165</v>
-      </c>
-      <c r="H13">
-        <v>4.731021374384942</v>
-      </c>
-      <c r="I13">
-        <v>7</v>
-      </c>
-      <c r="J13">
-        <v>9</v>
-      </c>
-      <c r="K13">
-        <v>0.01732326849299174</v>
-      </c>
-      <c r="L13">
-        <v>1.463722447989537</v>
-      </c>
-      <c r="M13">
-        <v>1.065014516408562</v>
-      </c>
-      <c r="N13">
-        <v>68.38551673192723</v>
-      </c>
-      <c r="O13">
-        <v>75.88443682843317</v>
-      </c>
-      <c r="P13">
-        <v>2.222235394349132</v>
-      </c>
-      <c r="Q13">
-        <v>0.926586624665542</v>
-      </c>
-      <c r="R13">
-        <v>0.7253227341197865</v>
-      </c>
-      <c r="S13">
-        <v>0.3874372043244655</v>
-      </c>
-      <c r="T13" t="s">
-        <v>67</v>
-      </c>
-      <c r="U13" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4678,63 +3890,66 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1">
+    <row r="1" spans="1:18" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -4747,47 +3962,50 @@
       <c r="D2" t="s">
         <v>29</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2">
         <v>19</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>15</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.2272901725807632</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.6404113864560872</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.5423542182666674</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.5491852688037044</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.006831050537037031</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.4851484955500008</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0.4590223225644453</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>-0.02612617298555553</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>1.714258562507808</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -4800,47 +4018,50 @@
       <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
         <v>19</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>15</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>8.765795238486142</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.009719532889465282</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.2857352938597114</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.5491852688037044</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.263449974943993</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.1964522055921754</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.4590223225644453</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.26257011697227</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>-6.743746248911961</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -4851,311 +4072,217 @@
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4">
+        <v>133</v>
+      </c>
+      <c r="E4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4">
         <v>19</v>
       </c>
-      <c r="F4">
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>13</v>
+      </c>
+      <c r="I4">
+        <v>0.285647251269581</v>
+      </c>
+      <c r="J4">
+        <v>0.756124834990865</v>
+      </c>
+      <c r="K4">
+        <v>0.5491852688037044</v>
+      </c>
+      <c r="L4">
+        <v>0.5681626756787765</v>
+      </c>
+      <c r="M4">
+        <v>0.0189774068750721</v>
+      </c>
+      <c r="N4">
+        <v>0.4590223225644453</v>
+      </c>
+      <c r="O4">
+        <v>0.4020713970936907</v>
+      </c>
+      <c r="P4">
+        <v>-0.05695092547075464</v>
+      </c>
+      <c r="Q4">
+        <v>3.182857380782167</v>
+      </c>
+      <c r="R4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>17</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="G4">
-        <v>14</v>
-      </c>
-      <c r="H4">
-        <v>0.5298663237086654</v>
-      </c>
-      <c r="I4">
-        <v>0.4786616139791066</v>
-      </c>
-      <c r="J4">
-        <v>0.5491852688037044</v>
-      </c>
-      <c r="K4">
-        <v>0.5656253061014269</v>
-      </c>
-      <c r="L4">
-        <v>0.01644003729772248</v>
-      </c>
-      <c r="M4">
-        <v>0.4590223225644453</v>
-      </c>
-      <c r="N4">
-        <v>0.4415182507018346</v>
-      </c>
-      <c r="O4">
-        <v>-0.01750407186261072</v>
-      </c>
-      <c r="P4">
-        <v>1.294169989813327</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E5">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
       <c r="H5">
-        <v>9.878834797758181</v>
+        <v>13</v>
       </c>
       <c r="I5">
-        <v>0.001211433733657446</v>
+        <v>12.49765571697403</v>
       </c>
       <c r="J5">
-        <v>0.5491852688037044</v>
+        <v>0.003658663645030331</v>
       </c>
       <c r="K5">
-        <v>0.901832549824004</v>
+        <v>0.2256869953733925</v>
       </c>
       <c r="L5">
-        <v>0.3526472810202995</v>
+        <v>0.6052159001643111</v>
       </c>
       <c r="M5">
-        <v>0.4590223225644453</v>
+        <v>0.3795289047909187</v>
       </c>
       <c r="N5">
-        <v>0.839362354257461</v>
+        <v>0.1150708518553056</v>
       </c>
       <c r="O5">
-        <v>0.3803400316930157</v>
+        <v>0.5141118771253059</v>
       </c>
       <c r="P5">
-        <v>-20.96325351065039</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+        <v>0.3990410252700003</v>
+      </c>
+      <c r="Q5">
+        <v>-9.451831682754573</v>
+      </c>
+      <c r="R5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6">
         <v>17</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>13</v>
       </c>
-      <c r="H6">
-        <v>12.49765571697403</v>
-      </c>
       <c r="I6">
-        <v>0.003658663645030331</v>
+        <v>0.7854241538148399</v>
       </c>
       <c r="J6">
-        <v>0.2256869953733925</v>
+        <v>0.3915870564538804</v>
       </c>
       <c r="K6">
+        <v>0.581364133429465</v>
+      </c>
+      <c r="L6">
         <v>0.6052159001643111</v>
       </c>
-      <c r="L6">
-        <v>0.3795289047909187</v>
-      </c>
       <c r="M6">
-        <v>0.1150708518553056</v>
+        <v>0.02385176673484612</v>
       </c>
       <c r="N6">
+        <v>0.5215590096336744</v>
+      </c>
+      <c r="O6">
         <v>0.5141118771253059</v>
       </c>
-      <c r="O6">
-        <v>0.3990410252700003</v>
-      </c>
       <c r="P6">
-        <v>-9.451831682754573</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
+        <v>-0.007447132508368481</v>
+      </c>
+      <c r="Q6">
+        <v>1.002738251920917</v>
+      </c>
+      <c r="R6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7">
+        <v>133</v>
+      </c>
+      <c r="E7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7">
         <v>17</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
       <c r="G7">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0.7854241538148399</v>
+        <v>11</v>
       </c>
       <c r="I7">
-        <v>0.3915870564538804</v>
+        <v>1.663029500266734</v>
       </c>
       <c r="J7">
-        <v>0.581364133429465</v>
+        <v>0.2338636499567078</v>
       </c>
       <c r="K7">
         <v>0.6052159001643111</v>
       </c>
       <c r="L7">
-        <v>0.02385176673484612</v>
+        <v>0.696872315126521</v>
       </c>
       <c r="M7">
-        <v>0.5215590096336744</v>
+        <v>0.09165641496220989</v>
       </c>
       <c r="N7">
         <v>0.5141118771253059</v>
       </c>
       <c r="O7">
-        <v>-0.007447132508368481</v>
+        <v>0.5590870038203942</v>
       </c>
       <c r="P7">
-        <v>1.002738251920917</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8">
-        <v>17</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>12</v>
-      </c>
-      <c r="H8">
-        <v>0.1660139473018341</v>
-      </c>
-      <c r="I8">
-        <v>0.6908536520968962</v>
-      </c>
-      <c r="J8">
-        <v>0.6052159001643111</v>
-      </c>
-      <c r="K8">
-        <v>0.610603011097244</v>
-      </c>
-      <c r="L8">
-        <v>0.00538711093293287</v>
-      </c>
-      <c r="M8">
-        <v>0.5141118771253059</v>
-      </c>
-      <c r="N8">
-        <v>0.4808040147963254</v>
-      </c>
-      <c r="O8">
-        <v>-0.03330786232898053</v>
-      </c>
-      <c r="P8">
-        <v>1.766425567053759</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9">
-        <v>17</v>
-      </c>
-      <c r="F9">
-        <v>4</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>1.906795250162734</v>
-      </c>
-      <c r="I9">
-        <v>0.1935212880371108</v>
-      </c>
-      <c r="J9">
-        <v>0.6052159001643111</v>
-      </c>
-      <c r="K9">
-        <v>0.786310325341253</v>
-      </c>
-      <c r="L9">
-        <v>0.1810944251769419</v>
-      </c>
-      <c r="M9">
-        <v>0.5141118771253059</v>
-      </c>
-      <c r="N9">
-        <v>0.6201072450511165</v>
-      </c>
-      <c r="O9">
-        <v>0.1059953679258105</v>
-      </c>
-      <c r="P9">
-        <v>-2.434841206376504</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>149</v>
+        <v>0.0449751266950883</v>
+      </c>
+      <c r="Q7">
+        <v>-0.4911435347495541</v>
+      </c>
+      <c r="R7" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -5165,7 +4292,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1">
@@ -5176,13 +4303,13 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -5209,7 +4336,7 @@
         <v>4</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>9</v>
@@ -5220,13 +4347,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E2">
         <v>36</v>
@@ -5259,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -5267,13 +4394,13 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E3">
         <v>36</v>
@@ -5306,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -5314,13 +4441,13 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E4">
         <v>36</v>
@@ -5353,7 +4480,7 @@
         <v>1</v>
       </c>
       <c r="O4" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -5361,13 +4488,13 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E5">
         <v>36</v>
@@ -5400,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -5408,13 +4535,13 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E6">
         <v>36</v>
@@ -5447,7 +4574,7 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -5455,13 +4582,13 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E7">
         <v>36</v>
@@ -5494,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -5502,13 +4629,13 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C8" t="s">
         <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E8">
         <v>36</v>
@@ -5541,7 +4668,7 @@
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -5549,34 +4676,34 @@
         <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E9">
         <v>36</v>
       </c>
       <c r="F9">
-        <v>-5.982314019640406</v>
+        <v>-4.810789706071763</v>
       </c>
       <c r="G9">
-        <v>1.491197227206835</v>
+        <v>3.124924900168364</v>
       </c>
       <c r="H9">
-        <v>-4.011752376207066</v>
+        <v>-1.539489702876561</v>
       </c>
       <c r="I9">
-        <v>0.0004533921376941398</v>
+        <v>0.1367668029302571</v>
       </c>
       <c r="J9">
-        <v>-9.04751381898668</v>
+        <v>-11.26031771272485</v>
       </c>
       <c r="K9">
-        <v>-2.917114220294133</v>
+        <v>1.638738300581324</v>
       </c>
       <c r="L9" t="s">
         <v>39</v>
@@ -5585,10 +4712,10 @@
         <v>20</v>
       </c>
       <c r="N9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -5596,34 +4723,34 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C10" t="s">
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E10">
         <v>36</v>
       </c>
       <c r="F10">
-        <v>-3.023706769666526</v>
+        <v>5.246812088337475</v>
       </c>
       <c r="G10">
-        <v>2.181789130201207</v>
+        <v>34.60602080118172</v>
       </c>
       <c r="H10">
-        <v>-1.385884056259679</v>
+        <v>0.1516155850012755</v>
       </c>
       <c r="I10">
-        <v>0.1775552783718117</v>
+        <v>0.8807574184531457</v>
       </c>
       <c r="J10">
-        <v>-7.508438555706135</v>
+        <v>-66.176504466891</v>
       </c>
       <c r="K10">
-        <v>1.461025016373082</v>
+        <v>76.67012864356596</v>
       </c>
       <c r="L10" t="s">
         <v>39</v>
@@ -5635,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -5643,34 +4770,34 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s">
         <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E11">
         <v>36</v>
       </c>
       <c r="F11">
-        <v>4.858339747947298</v>
+        <v>36.93763645779599</v>
       </c>
       <c r="G11">
-        <v>2.471350677183939</v>
+        <v>34.06728847980239</v>
       </c>
       <c r="H11">
-        <v>1.965864170067233</v>
+        <v>1.084255252063731</v>
       </c>
       <c r="I11">
-        <v>0.06007844681037599</v>
+        <v>0.2890240288797525</v>
       </c>
       <c r="J11">
-        <v>-0.2215943222142869</v>
+        <v>-33.37379123423516</v>
       </c>
       <c r="K11">
-        <v>9.938273818108883</v>
+        <v>107.2490641498271</v>
       </c>
       <c r="L11" t="s">
         <v>39</v>
@@ -5682,7 +4809,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -5690,751 +4817,469 @@
         <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E12">
         <v>36</v>
       </c>
       <c r="F12">
-        <v>-0.06515747344003796</v>
+        <v>2.598237833638032</v>
       </c>
       <c r="G12">
-        <v>6.650127684302199</v>
+        <v>8.638369475890512</v>
       </c>
       <c r="H12">
-        <v>-0.009797928180212823</v>
+        <v>0.3007787338675028</v>
       </c>
       <c r="I12">
-        <v>0.9922573038464295</v>
+        <v>0.7661734859586893</v>
       </c>
       <c r="J12">
-        <v>-13.73469069925716</v>
+        <v>-15.23048050246384</v>
       </c>
       <c r="K12">
-        <v>13.60437575237709</v>
+        <v>20.4269561697399</v>
       </c>
       <c r="L12" t="s">
         <v>39</v>
       </c>
       <c r="M12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E13">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>-5.648463144262429</v>
+        <v>7.922180092353511</v>
       </c>
       <c r="G13">
-        <v>1.481910106017257</v>
+        <v>8.5945906159867</v>
       </c>
       <c r="H13">
-        <v>-3.811609841465411</v>
+        <v>0.921763519209112</v>
       </c>
       <c r="I13">
-        <v>0.002159199916944283</v>
+        <v>0.3658257841077955</v>
       </c>
       <c r="J13">
-        <v>-8.849935288997564</v>
+        <v>-9.816183117763163</v>
       </c>
       <c r="K13">
-        <v>-2.446990999527293</v>
+        <v>25.66054330247018</v>
       </c>
       <c r="L13" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="N13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E14">
         <v>31</v>
       </c>
       <c r="F14">
-        <v>-0.2301138560694871</v>
+        <v>-3.234287117971579</v>
       </c>
       <c r="G14">
-        <v>1.198806158363297</v>
+        <v>4.680851127814104</v>
       </c>
       <c r="H14">
-        <v>-0.1919525141442853</v>
+        <v>-0.6909613293943722</v>
       </c>
       <c r="I14">
-        <v>0.8507452715434625</v>
+        <v>0.5017421224982936</v>
       </c>
       <c r="J14">
-        <v>-2.819977105772124</v>
+        <v>-13.34665118006968</v>
       </c>
       <c r="K14">
-        <v>2.35974939363315</v>
+        <v>6.878076944126519</v>
       </c>
       <c r="L14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E15">
         <v>31</v>
       </c>
       <c r="F15">
-        <v>2.255537876781865</v>
+        <v>0.9057264693775823</v>
       </c>
       <c r="G15">
-        <v>2.422323244309472</v>
+        <v>33.98975385954066</v>
       </c>
       <c r="H15">
-        <v>0.9311465272360245</v>
+        <v>0.02664704408041342</v>
       </c>
       <c r="I15">
-        <v>0.3687480622312649</v>
+        <v>0.9791459640503541</v>
       </c>
       <c r="J15">
-        <v>-2.97757333604558</v>
+        <v>-72.52467240965927</v>
       </c>
       <c r="K15">
-        <v>7.488649089609309</v>
+        <v>74.33612534841444</v>
       </c>
       <c r="L15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M15" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E16">
         <v>31</v>
       </c>
       <c r="F16">
-        <v>0.8137687499335803</v>
+        <v>53.24399409703744</v>
       </c>
       <c r="G16">
-        <v>1.208497585044787</v>
+        <v>50.81885719979571</v>
       </c>
       <c r="H16">
-        <v>0.6733722599068513</v>
+        <v>1.047721200964973</v>
       </c>
       <c r="I16">
-        <v>0.5125046997314113</v>
+        <v>0.3138565246061172</v>
       </c>
       <c r="J16">
-        <v>-1.797031554208154</v>
+        <v>-56.5434721546597</v>
       </c>
       <c r="K16">
-        <v>3.424569054075314</v>
+        <v>163.0314603487346</v>
       </c>
       <c r="L16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M16" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="N16" t="b">
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E17">
         <v>31</v>
       </c>
       <c r="F17">
-        <v>-0.031449541264781</v>
+        <v>1.666536266210316</v>
       </c>
       <c r="G17">
-        <v>0.05010462054939988</v>
+        <v>8.485020431287293</v>
       </c>
       <c r="H17">
-        <v>-0.6276774660686995</v>
+        <v>0.1964092225476798</v>
       </c>
       <c r="I17">
-        <v>0.5410844609470509</v>
+        <v>0.8473270090635971</v>
       </c>
       <c r="J17">
-        <v>-0.139693993043666</v>
+        <v>-16.66423592298915</v>
       </c>
       <c r="K17">
-        <v>0.07679491051410399</v>
+        <v>19.99730845540978</v>
       </c>
       <c r="L17" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E18">
         <v>31</v>
       </c>
       <c r="F18">
-        <v>-1.339537174858271</v>
+        <v>11.69747045481679</v>
       </c>
       <c r="G18">
-        <v>2.733722711313198</v>
+        <v>12.52919560366158</v>
       </c>
       <c r="H18">
-        <v>-0.4900047723621527</v>
+        <v>0.9336170353504805</v>
       </c>
       <c r="I18">
-        <v>0.6322960355903786</v>
+        <v>0.3675189358654612</v>
       </c>
       <c r="J18">
-        <v>-7.245386035839785</v>
+        <v>-15.37021101802509</v>
       </c>
       <c r="K18">
-        <v>4.566311686123243</v>
+        <v>38.76515192765867</v>
       </c>
       <c r="L18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M18" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E19">
         <v>31</v>
       </c>
       <c r="F19">
-        <v>0.1806036037475747</v>
+        <v>0.2562013601435249</v>
       </c>
       <c r="G19">
-        <v>0.1054191739278986</v>
+        <v>1.514519812481349</v>
       </c>
       <c r="H19">
-        <v>1.713195019637495</v>
+        <v>0.1691634259467173</v>
       </c>
       <c r="I19">
-        <v>0.1104070767983194</v>
+        <v>0.8682719415744495</v>
       </c>
       <c r="J19">
-        <v>-0.04714067539645689</v>
+        <v>-3.015719772333088</v>
       </c>
       <c r="K19">
-        <v>0.4083478828916063</v>
+        <v>3.528122492620137</v>
       </c>
       <c r="L19" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E20">
         <v>31</v>
       </c>
       <c r="F20">
-        <v>0.08632185663203309</v>
+        <v>-0.8585883127407358</v>
       </c>
       <c r="G20">
-        <v>0.1334266139661887</v>
+        <v>3.168911666660741</v>
       </c>
       <c r="H20">
-        <v>0.6469613075387473</v>
+        <v>-0.2709410684348542</v>
       </c>
       <c r="I20">
-        <v>0.5289154465490595</v>
+        <v>0.7906906588498602</v>
       </c>
       <c r="J20">
-        <v>-0.2019288181184815</v>
+        <v>-7.704605752493866</v>
       </c>
       <c r="K20">
-        <v>0.3745725313825476</v>
+        <v>5.987429127012395</v>
       </c>
       <c r="L20" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E21">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F21">
-        <v>-4.216317327769282</v>
+        <v>-0.05412327243670201</v>
       </c>
       <c r="G21">
-        <v>1.185247102294864</v>
+        <v>0.06027318568718423</v>
       </c>
       <c r="H21">
-        <v>-3.55733190117545</v>
+        <v>-0.8979660162248589</v>
       </c>
       <c r="I21">
-        <v>0.001974538926999698</v>
+        <v>0.385532919132147</v>
       </c>
       <c r="J21">
-        <v>-6.688699459134154</v>
+        <v>-0.1843355736204566</v>
       </c>
       <c r="K21">
-        <v>-1.74393519640441</v>
+        <v>0.07608902874705259</v>
       </c>
       <c r="L21" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="M21" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="N21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" t="s">
-        <v>155</v>
-      </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E22">
-        <v>36</v>
-      </c>
-      <c r="F22">
-        <v>-0.6851829439858779</v>
-      </c>
-      <c r="G22">
-        <v>1.194463325500999</v>
-      </c>
-      <c r="H22">
-        <v>-0.5736324668641363</v>
-      </c>
-      <c r="I22">
-        <v>0.5726113336302558</v>
-      </c>
-      <c r="J22">
-        <v>-3.176789780080591</v>
-      </c>
-      <c r="K22">
-        <v>1.806423892108835</v>
-      </c>
-      <c r="L22" t="s">
-        <v>67</v>
-      </c>
-      <c r="M22" t="s">
-        <v>23</v>
-      </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" t="s">
-        <v>158</v>
-      </c>
-      <c r="C23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" t="s">
-        <v>154</v>
-      </c>
-      <c r="E23">
-        <v>36</v>
-      </c>
-      <c r="F23">
-        <v>3.496583410312398</v>
-      </c>
-      <c r="G23">
-        <v>1.95133126171899</v>
-      </c>
-      <c r="H23">
-        <v>1.791896372957273</v>
-      </c>
-      <c r="I23">
-        <v>0.08829329153290767</v>
-      </c>
-      <c r="J23">
-        <v>-0.5738222751405955</v>
-      </c>
-      <c r="K23">
-        <v>7.566989095765391</v>
-      </c>
-      <c r="L23" t="s">
-        <v>67</v>
-      </c>
-      <c r="M23" t="s">
-        <v>30</v>
-      </c>
-      <c r="N23" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" t="s">
-        <v>154</v>
-      </c>
-      <c r="E24">
-        <v>36</v>
-      </c>
-      <c r="F24">
-        <v>0.8860029767134595</v>
-      </c>
-      <c r="G24">
-        <v>1.237943798162317</v>
-      </c>
-      <c r="H24">
-        <v>0.7157053317191776</v>
-      </c>
-      <c r="I24">
-        <v>0.482446372144523</v>
-      </c>
-      <c r="J24">
-        <v>-1.696302536022605</v>
-      </c>
-      <c r="K24">
-        <v>3.468308489449524</v>
-      </c>
-      <c r="L24" t="s">
-        <v>67</v>
-      </c>
-      <c r="M24" t="s">
-        <v>53</v>
-      </c>
-      <c r="N24" t="b">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" t="s">
-        <v>171</v>
-      </c>
-      <c r="C25" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" t="s">
-        <v>154</v>
-      </c>
-      <c r="E25">
-        <v>36</v>
-      </c>
-      <c r="F25">
-        <v>-0.03527719844182507</v>
-      </c>
-      <c r="G25">
-        <v>0.04234204535506891</v>
-      </c>
-      <c r="H25">
-        <v>-0.8331481898429812</v>
-      </c>
-      <c r="I25">
-        <v>0.414600482687798</v>
-      </c>
-      <c r="J25">
-        <v>-0.1236011573349722</v>
-      </c>
-      <c r="K25">
-        <v>0.05304676045132206</v>
-      </c>
-      <c r="L25" t="s">
-        <v>67</v>
-      </c>
-      <c r="M25" t="s">
-        <v>56</v>
-      </c>
-      <c r="N25" t="b">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" t="s">
-        <v>175</v>
-      </c>
-      <c r="C26" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" t="s">
-        <v>154</v>
-      </c>
-      <c r="E26">
-        <v>36</v>
-      </c>
-      <c r="F26">
-        <v>0.1161367673679964</v>
-      </c>
-      <c r="G26">
-        <v>0.08440229334259029</v>
-      </c>
-      <c r="H26">
-        <v>1.37599066054515</v>
-      </c>
-      <c r="I26">
-        <v>0.1840384186810669</v>
-      </c>
-      <c r="J26">
-        <v>-0.05992333141005803</v>
-      </c>
-      <c r="K26">
-        <v>0.2921968661460508</v>
-      </c>
-      <c r="L26" t="s">
-        <v>67</v>
-      </c>
-      <c r="M26" t="s">
-        <v>61</v>
-      </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" t="s">
-        <v>177</v>
-      </c>
-      <c r="C27" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" t="s">
-        <v>154</v>
-      </c>
-      <c r="E27">
-        <v>36</v>
-      </c>
-      <c r="F27">
-        <v>-0.08899523683077261</v>
-      </c>
-      <c r="G27">
-        <v>0.09072990900255458</v>
-      </c>
-      <c r="H27">
-        <v>-0.9808809223898469</v>
-      </c>
-      <c r="I27">
-        <v>0.3383688583958437</v>
-      </c>
-      <c r="J27">
-        <v>-0.2782545105838596</v>
-      </c>
-      <c r="K27">
-        <v>0.1002640369223144</v>
-      </c>
-      <c r="L27" t="s">
-        <v>67</v>
-      </c>
-      <c r="M27" t="s">
-        <v>64</v>
-      </c>
-      <c r="N27" t="b">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -6444,7 +5289,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -6452,16 +5297,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>8</v>
@@ -6490,7 +5335,7 @@
         <v>0.007386964173758466</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -6513,7 +5358,7 @@
         <v>0.001523027722757665</v>
       </c>
       <c r="G3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -6536,7 +5381,7 @@
         <v>0.0003324260727056167</v>
       </c>
       <c r="G4" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -6547,24 +5392,24 @@
         <v>36</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>5.902604088121402</v>
+        <v>5.417474966421664</v>
       </c>
       <c r="F5">
-        <v>0.001617143941436018</v>
+        <v>0.001788371524256679</v>
       </c>
       <c r="G5" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B6">
         <v>31</v>
@@ -6576,36 +5421,13 @@
         <v>13</v>
       </c>
       <c r="E6">
-        <v>4.953993496132533</v>
+        <v>3.45411170739337</v>
       </c>
       <c r="F6">
-        <v>0.005552603201377665</v>
+        <v>0.02330375464484713</v>
       </c>
       <c r="G6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7">
-        <v>36</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>20</v>
-      </c>
-      <c r="E7">
-        <v>4.12903431599249</v>
-      </c>
-      <c r="F7">
-        <v>0.005839546951602488</v>
-      </c>
-      <c r="G7" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -6615,7 +5437,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1">
@@ -6626,25 +5448,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6745,22 +5567,22 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>1.372949653581145</v>
+        <v>53.86518864767415</v>
       </c>
       <c r="E5">
-        <v>0.3219138496843572</v>
+        <v>0.5681977399499447</v>
       </c>
       <c r="F5">
-        <v>0.2229713177310755</v>
+        <v>0.2598850523000154</v>
       </c>
       <c r="G5">
-        <v>0.969416775756163</v>
+        <v>0.8794975187458534</v>
       </c>
       <c r="H5">
-        <v>1.595053176446366</v>
+        <v>1.650423269587353</v>
       </c>
       <c r="I5">
-        <v>1.36918579146961</v>
+        <v>1.365180932568826</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -6768,231 +5590,173 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>18</v>
       </c>
       <c r="D6">
-        <v>3.274875819626642</v>
+        <v>61.08070029911875</v>
       </c>
       <c r="E6">
-        <v>0.9564107679877191</v>
+        <v>0.4788638921806911</v>
       </c>
       <c r="F6">
-        <v>0.5997922517603256</v>
+        <v>0.9254893726900082</v>
       </c>
       <c r="G6">
-        <v>0.318606727007158</v>
+        <v>0.9793989291894669</v>
       </c>
       <c r="H6">
-        <v>0.9405400689304357</v>
+        <v>1.04308737387962</v>
       </c>
       <c r="I6">
-        <v>0.6650622607183739</v>
+        <v>0.7375741554403465</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>2.451268394797905</v>
+        <v>1.017681660032122</v>
       </c>
       <c r="E7">
-        <v>1.170373500273494</v>
+        <v>0.5018431757227956</v>
       </c>
       <c r="F7">
-        <v>0.7528928869508489</v>
+        <v>0.4220077889086216</v>
       </c>
       <c r="G7">
-        <v>0.3885499414135918</v>
+        <v>0.7979069126061417</v>
       </c>
       <c r="H7">
-        <v>0.8554494254447713</v>
+        <v>2.233996446339432</v>
       </c>
       <c r="I7">
-        <v>0.6508994147546787</v>
+        <v>2.027318740887332</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>17</v>
       </c>
       <c r="D8">
-        <v>1.017681660032122</v>
+        <v>1.051471993332928</v>
       </c>
       <c r="E8">
-        <v>0.5018431757227956</v>
+        <v>0.3119360618233111</v>
       </c>
       <c r="F8">
-        <v>0.4220077889086216</v>
+        <v>0.9476168913915635</v>
       </c>
       <c r="G8">
-        <v>0.7979069126061417</v>
+        <v>0.3919919610818148</v>
       </c>
       <c r="H8">
-        <v>2.233996446339432</v>
+        <v>1.642640090746519</v>
       </c>
       <c r="I8">
-        <v>2.027318740887332</v>
+        <v>1.490671592589143</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>17</v>
       </c>
       <c r="D9">
-        <v>1.051471993332928</v>
+        <v>1.287562935668985</v>
       </c>
       <c r="E9">
-        <v>0.3119360618233111</v>
+        <v>0.2867174620062506</v>
       </c>
       <c r="F9">
-        <v>0.9476168913915635</v>
+        <v>0.9537540652610096</v>
       </c>
       <c r="G9">
-        <v>0.3919919610818148</v>
+        <v>0.4973830488955234</v>
       </c>
       <c r="H9">
-        <v>1.642640090746519</v>
+        <v>1.655374913650029</v>
       </c>
       <c r="I9">
-        <v>1.490671592589143</v>
+        <v>1.44758336875928</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>17</v>
       </c>
       <c r="D10">
-        <v>1.287562935668985</v>
+        <v>1320.190136266348</v>
       </c>
       <c r="E10">
-        <v>0.2867174620062506</v>
+        <v>1.045986551806551</v>
       </c>
       <c r="F10">
-        <v>0.9537540652610096</v>
+        <v>0.912222834844275</v>
       </c>
       <c r="G10">
-        <v>0.4973830488955234</v>
+        <v>0.5275374953958908</v>
       </c>
       <c r="H10">
-        <v>1.655374913650029</v>
+        <v>1.576901905053064</v>
       </c>
       <c r="I10">
-        <v>1.44758336875928</v>
+        <v>1.268459366590729</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D11">
-        <v>4.083695181374016</v>
+        <v>1509.998127926904</v>
       </c>
       <c r="E11">
-        <v>0.7336674483744495</v>
+        <v>2.834843051323265</v>
       </c>
       <c r="F11">
-        <v>0.7900021679569911</v>
+        <v>0.5945294488259011</v>
       </c>
       <c r="G11">
-        <v>0.5366288571540381</v>
+        <v>0.4051937054050931</v>
       </c>
       <c r="H11">
-        <v>1.711172887772359</v>
+        <v>1.968568108570851</v>
       </c>
       <c r="I11">
-        <v>1.437672789045799</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12">
-        <v>13</v>
-      </c>
-      <c r="D12">
-        <v>3.699275739211368</v>
-      </c>
-      <c r="E12">
-        <v>26.82051809587888</v>
-      </c>
-      <c r="F12">
-        <v>0.9352860912391692</v>
-      </c>
-      <c r="G12">
-        <v>0.6480350161090446</v>
-      </c>
-      <c r="H12">
-        <v>1.330531050850008</v>
-      </c>
-      <c r="I12">
-        <v>0.7380458349902594</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13">
-        <v>17</v>
-      </c>
-      <c r="D13">
-        <v>2.222235394349132</v>
-      </c>
-      <c r="E13">
-        <v>0.926586624665542</v>
-      </c>
-      <c r="F13">
-        <v>0.7253227341197865</v>
-      </c>
-      <c r="G13">
-        <v>0.3874372043244655</v>
-      </c>
-      <c r="H13">
-        <v>1.463722447989537</v>
-      </c>
-      <c r="I13">
-        <v>1.065014516408562</v>
+        <v>1.091965116106979</v>
       </c>
     </row>
   </sheetData>
@@ -7007,23 +5771,23 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -7031,74 +5795,74 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="B5" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="B6" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="B8" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="B10" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="B11" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
@@ -598,7 +598,7 @@
     <t>output_dir</t>
   </si>
   <si>
-    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/nested-regression-models/New_Outputs/multiple_regression_HT4_HT6</t>
+    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/figure-weight-middle/New_Outputs/multiple_regression_HT4_HT6</t>
   </si>
 </sst>
 </file>

--- a/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
@@ -598,7 +598,7 @@
     <t>output_dir</t>
   </si>
   <si>
-    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/figure-weight-middle/New_Outputs/multiple_regression_HT4_HT6</t>
+    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/strip-stats-size/New_Outputs/multiple_regression_HT4_HT6</t>
   </si>
 </sst>
 </file>

--- a/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
@@ -598,7 +598,7 @@
     <t>output_dir</t>
   </si>
   <si>
-    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/strip-stats-size/New_Outputs/multiple_regression_HT4_HT6</t>
+    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/figure-weight-middle/New_Outputs/multiple_regression_HT4_HT6</t>
   </si>
 </sst>
 </file>

--- a/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
@@ -598,7 +598,7 @@
     <t>output_dir</t>
   </si>
   <si>
-    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/figure-weight-middle/New_Outputs/multiple_regression_HT4_HT6</t>
+    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/strip-stats-v2/New_Outputs/multiple_regression_HT4_HT6</t>
   </si>
 </sst>
 </file>

--- a/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
@@ -598,7 +598,7 @@
     <t>output_dir</t>
   </si>
   <si>
-    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/figure-weight-middle/New_Outputs/multiple_regression_HT4_HT6</t>
+    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/New_Outputs/multiple_regression_HT4_HT6</t>
   </si>
 </sst>
 </file>

--- a/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
@@ -10,17 +10,15 @@
     <sheet name="Coefficients" sheetId="1" r:id="rId1"/>
     <sheet name="Model_fit" sheetId="2" r:id="rId2"/>
     <sheet name="Nested_tests" sheetId="3" r:id="rId3"/>
-    <sheet name="Interaction_terms" sheetId="4" r:id="rId4"/>
-    <sheet name="Interaction_omnibus" sheetId="5" r:id="rId5"/>
-    <sheet name="Diagnostics" sheetId="6" r:id="rId6"/>
-    <sheet name="Config" sheetId="7" r:id="rId7"/>
+    <sheet name="Diagnostics" sheetId="4" r:id="rId4"/>
+    <sheet name="Config" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="160">
   <si>
     <t>group</t>
   </si>
@@ -431,105 +429,6 @@
   </si>
   <si>
     <t>0.234</t>
-  </si>
-  <si>
-    <t>predictor</t>
-  </si>
-  <si>
-    <t>comparison</t>
-  </si>
-  <si>
-    <t>sig</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:log_ROE</t>
-  </si>
-  <si>
-    <t>Tramadol group minus Hydrocodone group</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:R_5HT4</t>
-  </si>
-  <si>
-    <t>0.205</t>
-  </si>
-  <si>
-    <t>5.8e-04</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:R_5HT6</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>3.5e-04</t>
-  </si>
-  <si>
-    <t>0.018</t>
-  </si>
-  <si>
-    <t>0.015</t>
-  </si>
-  <si>
-    <t>0.137</t>
-  </si>
-  <si>
-    <t>0.881</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:R_5HT4_x_ROE</t>
-  </si>
-  <si>
-    <t>0.766</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:R_5HT6_x_ROE</t>
-  </si>
-  <si>
-    <t>0.366</t>
-  </si>
-  <si>
-    <t>0.502</t>
-  </si>
-  <si>
-    <t>0.979</t>
-  </si>
-  <si>
-    <t>0.314</t>
-  </si>
-  <si>
-    <t>0.847</t>
-  </si>
-  <si>
-    <t>0.368</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:sex_female</t>
-  </si>
-  <si>
-    <t>0.868</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:log_MME</t>
-  </si>
-  <si>
-    <t>0.791</t>
-  </si>
-  <si>
-    <t>.grpTramadol group:MQS_nonopioid</t>
-  </si>
-  <si>
-    <t>0.386</t>
-  </si>
-  <si>
-    <t>0.007</t>
-  </si>
-  <si>
-    <t>3.3e-04</t>
-  </si>
-  <si>
-    <t>0.023</t>
   </si>
   <si>
     <t>setting</t>
@@ -4292,994 +4191,326 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1">
+    <row r="1" spans="1:9" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C2">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>141</v>
+      <c r="D2">
+        <v>1.01163910023057</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>0.5795877175725123</v>
       </c>
       <c r="F2">
-        <v>-4.887134700262774</v>
+        <v>0.1691410039128372</v>
       </c>
       <c r="G2">
-        <v>1.644367348188758</v>
+        <v>0.6544893796276015</v>
       </c>
       <c r="H2">
-        <v>-2.972045574637484</v>
+        <v>1.531481188713505</v>
       </c>
       <c r="I2">
-        <v>0.005781869300953446</v>
-      </c>
-      <c r="J2">
-        <v>-8.245380843509782</v>
-      </c>
-      <c r="K2">
-        <v>-1.528888557015765</v>
-      </c>
-      <c r="L2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>1.405383523270676</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>1.007973823773254</v>
+      </c>
+      <c r="E3">
+        <v>0.2926251835358054</v>
+      </c>
+      <c r="F3">
+        <v>0.2602028007683616</v>
+      </c>
+      <c r="G3">
+        <v>0.8809803495022062</v>
+      </c>
+      <c r="H3">
+        <v>1.913271182809426</v>
+      </c>
+      <c r="I3">
+        <v>1.755738049990488</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>1.121305331718685</v>
+      </c>
+      <c r="E4">
+        <v>0.4273099001295377</v>
+      </c>
+      <c r="F4">
+        <v>0.1594268095201135</v>
+      </c>
+      <c r="G4">
+        <v>0.8917722169641169</v>
+      </c>
+      <c r="H4">
+        <v>1.5698579120013</v>
+      </c>
+      <c r="I4">
+        <v>1.394855358622803</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>53.86518864767415</v>
+      </c>
+      <c r="E5">
+        <v>0.5681977399499447</v>
+      </c>
+      <c r="F5">
+        <v>0.2598850523000154</v>
+      </c>
+      <c r="G5">
+        <v>0.8794975187458534</v>
+      </c>
+      <c r="H5">
+        <v>1.650423269587353</v>
+      </c>
+      <c r="I5">
+        <v>1.365180932568826</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>61.08070029911875</v>
+      </c>
+      <c r="E6">
+        <v>0.4788638921806911</v>
+      </c>
+      <c r="F6">
+        <v>0.9254893726900082</v>
+      </c>
+      <c r="G6">
+        <v>0.9793989291894669</v>
+      </c>
+      <c r="H6">
+        <v>1.04308737387962</v>
+      </c>
+      <c r="I6">
+        <v>0.7375741554403465</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E3">
-        <v>36</v>
-      </c>
-      <c r="F3">
-        <v>-1.906542506110529</v>
-      </c>
-      <c r="G3">
-        <v>1.470318719242319</v>
-      </c>
-      <c r="H3">
-        <v>-1.296686549085768</v>
-      </c>
-      <c r="I3">
-        <v>0.2046245320982059</v>
-      </c>
-      <c r="J3">
-        <v>-4.909333928403231</v>
-      </c>
-      <c r="K3">
-        <v>1.096248916182172</v>
-      </c>
-      <c r="L3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
+      <c r="C7">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>1.017681660032122</v>
+      </c>
+      <c r="E7">
+        <v>0.5018431757227956</v>
+      </c>
+      <c r="F7">
+        <v>0.4220077889086216</v>
+      </c>
+      <c r="G7">
+        <v>0.7979069126061417</v>
+      </c>
+      <c r="H7">
+        <v>2.233996446339432</v>
+      </c>
+      <c r="I7">
+        <v>2.027318740887332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4">
-        <v>36</v>
-      </c>
-      <c r="F4">
-        <v>-6.071416259789797</v>
-      </c>
-      <c r="G4">
-        <v>1.577859503894293</v>
-      </c>
-      <c r="H4">
-        <v>-3.847881414539773</v>
-      </c>
-      <c r="I4">
-        <v>0.00057900884939516</v>
-      </c>
-      <c r="J4">
-        <v>-9.293835264506248</v>
-      </c>
-      <c r="K4">
-        <v>-2.848997255073346</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>141</v>
-      </c>
-      <c r="E5">
-        <v>36</v>
-      </c>
-      <c r="F5">
-        <v>3.676698186670552</v>
-      </c>
-      <c r="G5">
-        <v>2.174611148707129</v>
-      </c>
-      <c r="H5">
-        <v>1.690738221799542</v>
-      </c>
-      <c r="I5">
-        <v>0.1012525841897636</v>
-      </c>
-      <c r="J5">
-        <v>-0.7644502654996144</v>
-      </c>
-      <c r="K5">
-        <v>8.117846638840717</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" t="s">
+      <c r="C8">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>1.051471993332928</v>
+      </c>
+      <c r="E8">
+        <v>0.3119360618233111</v>
+      </c>
+      <c r="F8">
+        <v>0.9476168913915635</v>
+      </c>
+      <c r="G8">
+        <v>0.3919919610818148</v>
+      </c>
+      <c r="H8">
+        <v>1.642640090746519</v>
+      </c>
+      <c r="I8">
+        <v>1.490671592589143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6">
-        <v>36</v>
-      </c>
-      <c r="F6">
-        <v>-5.778734418070625</v>
-      </c>
-      <c r="G6">
-        <v>1.421121084661567</v>
-      </c>
-      <c r="H6">
-        <v>-4.066320935240223</v>
-      </c>
-      <c r="I6">
-        <v>0.000351662226711714</v>
-      </c>
-      <c r="J6">
-        <v>-8.689768997247185</v>
-      </c>
-      <c r="K6">
-        <v>-2.867699838894066</v>
-      </c>
-      <c r="L6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>141</v>
-      </c>
-      <c r="E7">
-        <v>36</v>
-      </c>
-      <c r="F7">
-        <v>-3.424236830192158</v>
-      </c>
-      <c r="G7">
-        <v>1.356763227019878</v>
-      </c>
-      <c r="H7">
-        <v>-2.523827858832431</v>
-      </c>
-      <c r="I7">
-        <v>0.01756138370750144</v>
-      </c>
-      <c r="J7">
-        <v>-6.203440314144839</v>
-      </c>
-      <c r="K7">
-        <v>-0.6450333462394773</v>
-      </c>
-      <c r="L7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8">
-        <v>36</v>
-      </c>
-      <c r="F8">
-        <v>5.501499320232195</v>
-      </c>
-      <c r="G8">
-        <v>2.121023700020244</v>
-      </c>
-      <c r="H8">
-        <v>2.59379436457013</v>
-      </c>
-      <c r="I8">
-        <v>0.01493073044433937</v>
-      </c>
-      <c r="J8">
-        <v>1.156779225193753</v>
-      </c>
-      <c r="K8">
-        <v>9.846219415270639</v>
-      </c>
-      <c r="L8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N8" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" t="s">
+      <c r="C9">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>1.287562935668985</v>
+      </c>
+      <c r="E9">
+        <v>0.2867174620062506</v>
+      </c>
+      <c r="F9">
+        <v>0.9537540652610096</v>
+      </c>
+      <c r="G9">
+        <v>0.4973830488955234</v>
+      </c>
+      <c r="H9">
+        <v>1.655374913650029</v>
+      </c>
+      <c r="I9">
+        <v>1.44758336875928</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" t="s">
         <v>38</v>
       </c>
-      <c r="B9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9">
-        <v>36</v>
-      </c>
-      <c r="F9">
-        <v>-4.810789706071763</v>
-      </c>
-      <c r="G9">
-        <v>3.124924900168364</v>
-      </c>
-      <c r="H9">
-        <v>-1.539489702876561</v>
-      </c>
-      <c r="I9">
-        <v>0.1367668029302571</v>
-      </c>
-      <c r="J9">
-        <v>-11.26031771272485</v>
-      </c>
-      <c r="K9">
-        <v>1.638738300581324</v>
-      </c>
-      <c r="L9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" t="s">
-        <v>20</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>141</v>
+      <c r="C10">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>1320.190136266348</v>
       </c>
       <c r="E10">
-        <v>36</v>
+        <v>1.045986551806551</v>
       </c>
       <c r="F10">
-        <v>5.246812088337475</v>
+        <v>0.912222834844275</v>
       </c>
       <c r="G10">
-        <v>34.60602080118172</v>
+        <v>0.5275374953958908</v>
       </c>
       <c r="H10">
-        <v>0.1516155850012755</v>
+        <v>1.576901905053064</v>
       </c>
       <c r="I10">
-        <v>0.8807574184531457</v>
-      </c>
-      <c r="J10">
-        <v>-66.176504466891</v>
-      </c>
-      <c r="K10">
-        <v>76.67012864356596</v>
-      </c>
-      <c r="L10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N10" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>1.268459366590729</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>141</v>
+        <v>50</v>
+      </c>
+      <c r="C11">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>1509.998127926904</v>
       </c>
       <c r="E11">
-        <v>36</v>
+        <v>2.834843051323265</v>
       </c>
       <c r="F11">
-        <v>36.93763645779599</v>
+        <v>0.5945294488259011</v>
       </c>
       <c r="G11">
-        <v>34.06728847980239</v>
+        <v>0.4051937054050931</v>
       </c>
       <c r="H11">
-        <v>1.084255252063731</v>
+        <v>1.968568108570851</v>
       </c>
       <c r="I11">
-        <v>0.2890240288797525</v>
-      </c>
-      <c r="J11">
-        <v>-33.37379123423516</v>
-      </c>
-      <c r="K11">
-        <v>107.2490641498271</v>
-      </c>
-      <c r="L11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M11" t="s">
-        <v>30</v>
-      </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>152</v>
-      </c>
-      <c r="C12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s">
-        <v>141</v>
-      </c>
-      <c r="E12">
-        <v>36</v>
-      </c>
-      <c r="F12">
-        <v>2.598237833638032</v>
-      </c>
-      <c r="G12">
-        <v>8.638369475890512</v>
-      </c>
-      <c r="H12">
-        <v>0.3007787338675028</v>
-      </c>
-      <c r="I12">
-        <v>0.7661734859586893</v>
-      </c>
-      <c r="J12">
-        <v>-15.23048050246384</v>
-      </c>
-      <c r="K12">
-        <v>20.4269561697399</v>
-      </c>
-      <c r="L12" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12" t="s">
-        <v>45</v>
-      </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E13">
-        <v>36</v>
-      </c>
-      <c r="F13">
-        <v>7.922180092353511</v>
-      </c>
-      <c r="G13">
-        <v>8.5945906159867</v>
-      </c>
-      <c r="H13">
-        <v>0.921763519209112</v>
-      </c>
-      <c r="I13">
-        <v>0.3658257841077955</v>
-      </c>
-      <c r="J13">
-        <v>-9.816183117763163</v>
-      </c>
-      <c r="K13">
-        <v>25.66054330247018</v>
-      </c>
-      <c r="L13" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E14">
-        <v>31</v>
-      </c>
-      <c r="F14">
-        <v>-3.234287117971579</v>
-      </c>
-      <c r="G14">
-        <v>4.680851127814104</v>
-      </c>
-      <c r="H14">
-        <v>-0.6909613293943722</v>
-      </c>
-      <c r="I14">
-        <v>0.5017421224982936</v>
-      </c>
-      <c r="J14">
-        <v>-13.34665118006968</v>
-      </c>
-      <c r="K14">
-        <v>6.878076944126519</v>
-      </c>
-      <c r="L14" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14" t="s">
-        <v>20</v>
-      </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>141</v>
-      </c>
-      <c r="E15">
-        <v>31</v>
-      </c>
-      <c r="F15">
-        <v>0.9057264693775823</v>
-      </c>
-      <c r="G15">
-        <v>33.98975385954066</v>
-      </c>
-      <c r="H15">
-        <v>0.02664704408041342</v>
-      </c>
-      <c r="I15">
-        <v>0.9791459640503541</v>
-      </c>
-      <c r="J15">
-        <v>-72.52467240965927</v>
-      </c>
-      <c r="K15">
-        <v>74.33612534841444</v>
-      </c>
-      <c r="L15" t="s">
-        <v>51</v>
-      </c>
-      <c r="M15" t="s">
-        <v>23</v>
-      </c>
-      <c r="N15" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" t="s">
-        <v>145</v>
-      </c>
-      <c r="C16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16">
-        <v>31</v>
-      </c>
-      <c r="F16">
-        <v>53.24399409703744</v>
-      </c>
-      <c r="G16">
-        <v>50.81885719979571</v>
-      </c>
-      <c r="H16">
-        <v>1.047721200964973</v>
-      </c>
-      <c r="I16">
-        <v>0.3138565246061172</v>
-      </c>
-      <c r="J16">
-        <v>-56.5434721546597</v>
-      </c>
-      <c r="K16">
-        <v>163.0314603487346</v>
-      </c>
-      <c r="L16" t="s">
-        <v>51</v>
-      </c>
-      <c r="M16" t="s">
-        <v>30</v>
-      </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="A17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" t="s">
-        <v>141</v>
-      </c>
-      <c r="E17">
-        <v>31</v>
-      </c>
-      <c r="F17">
-        <v>1.666536266210316</v>
-      </c>
-      <c r="G17">
-        <v>8.485020431287293</v>
-      </c>
-      <c r="H17">
-        <v>0.1964092225476798</v>
-      </c>
-      <c r="I17">
-        <v>0.8473270090635971</v>
-      </c>
-      <c r="J17">
-        <v>-16.66423592298915</v>
-      </c>
-      <c r="K17">
-        <v>19.99730845540978</v>
-      </c>
-      <c r="L17" t="s">
-        <v>51</v>
-      </c>
-      <c r="M17" t="s">
-        <v>45</v>
-      </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" t="s">
-        <v>141</v>
-      </c>
-      <c r="E18">
-        <v>31</v>
-      </c>
-      <c r="F18">
-        <v>11.69747045481679</v>
-      </c>
-      <c r="G18">
-        <v>12.52919560366158</v>
-      </c>
-      <c r="H18">
-        <v>0.9336170353504805</v>
-      </c>
-      <c r="I18">
-        <v>0.3675189358654612</v>
-      </c>
-      <c r="J18">
-        <v>-15.37021101802509</v>
-      </c>
-      <c r="K18">
-        <v>38.76515192765867</v>
-      </c>
-      <c r="L18" t="s">
-        <v>51</v>
-      </c>
-      <c r="M18" t="s">
-        <v>48</v>
-      </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19">
-        <v>31</v>
-      </c>
-      <c r="F19">
-        <v>0.2562013601435249</v>
-      </c>
-      <c r="G19">
-        <v>1.514519812481349</v>
-      </c>
-      <c r="H19">
-        <v>0.1691634259467173</v>
-      </c>
-      <c r="I19">
-        <v>0.8682719415744495</v>
-      </c>
-      <c r="J19">
-        <v>-3.015719772333088</v>
-      </c>
-      <c r="K19">
-        <v>3.528122492620137</v>
-      </c>
-      <c r="L19" t="s">
-        <v>51</v>
-      </c>
-      <c r="M19" t="s">
-        <v>59</v>
-      </c>
-      <c r="N19" t="b">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" t="s">
-        <v>163</v>
-      </c>
-      <c r="C20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20">
-        <v>31</v>
-      </c>
-      <c r="F20">
-        <v>-0.8585883127407358</v>
-      </c>
-      <c r="G20">
-        <v>3.168911666660741</v>
-      </c>
-      <c r="H20">
-        <v>-0.2709410684348542</v>
-      </c>
-      <c r="I20">
-        <v>0.7906906588498602</v>
-      </c>
-      <c r="J20">
-        <v>-7.704605752493866</v>
-      </c>
-      <c r="K20">
-        <v>5.987429127012395</v>
-      </c>
-      <c r="L20" t="s">
-        <v>51</v>
-      </c>
-      <c r="M20" t="s">
-        <v>62</v>
-      </c>
-      <c r="N20" t="b">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" t="s">
-        <v>165</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" t="s">
-        <v>141</v>
-      </c>
-      <c r="E21">
-        <v>31</v>
-      </c>
-      <c r="F21">
-        <v>-0.05412327243670201</v>
-      </c>
-      <c r="G21">
-        <v>0.06027318568718423</v>
-      </c>
-      <c r="H21">
-        <v>-0.8979660162248589</v>
-      </c>
-      <c r="I21">
-        <v>0.385532919132147</v>
-      </c>
-      <c r="J21">
-        <v>-0.1843355736204566</v>
-      </c>
-      <c r="K21">
-        <v>0.07608902874705259</v>
-      </c>
-      <c r="L21" t="s">
-        <v>51</v>
-      </c>
-      <c r="M21" t="s">
-        <v>65</v>
-      </c>
-      <c r="N21" t="b">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>166</v>
+        <v>1.091965116106979</v>
       </c>
     </row>
   </sheetData>
@@ -5289,505 +4520,28 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2">
-        <v>36</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>30</v>
-      </c>
-      <c r="E2">
-        <v>5.806236284200734</v>
-      </c>
-      <c r="F2">
-        <v>0.007386964173758466</v>
-      </c>
-      <c r="G2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3">
-        <v>36</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>30</v>
-      </c>
-      <c r="E3">
-        <v>8.115896351486487</v>
-      </c>
-      <c r="F3">
-        <v>0.001523027722757665</v>
-      </c>
-      <c r="G3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4">
-        <v>36</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>28</v>
-      </c>
-      <c r="E4">
-        <v>8.599476119849234</v>
-      </c>
-      <c r="F4">
-        <v>0.0003324260727056167</v>
-      </c>
-      <c r="G4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5">
-        <v>36</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>24</v>
-      </c>
-      <c r="E5">
-        <v>5.417474966421664</v>
-      </c>
-      <c r="F5">
-        <v>0.001788371524256679</v>
-      </c>
-      <c r="G5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6">
-        <v>31</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>13</v>
-      </c>
-      <c r="E6">
-        <v>3.45411170739337</v>
-      </c>
-      <c r="F6">
-        <v>0.02330375464484713</v>
-      </c>
-      <c r="G6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2">
-        <v>19</v>
-      </c>
-      <c r="D2">
-        <v>1.01163910023057</v>
-      </c>
-      <c r="E2">
-        <v>0.5795877175725123</v>
-      </c>
-      <c r="F2">
-        <v>0.1691410039128372</v>
-      </c>
-      <c r="G2">
-        <v>0.6544893796276015</v>
-      </c>
-      <c r="H2">
-        <v>1.531481188713505</v>
-      </c>
-      <c r="I2">
-        <v>1.405383523270676</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3">
-        <v>19</v>
-      </c>
-      <c r="D3">
-        <v>1.007973823773254</v>
-      </c>
-      <c r="E3">
-        <v>0.2926251835358054</v>
-      </c>
-      <c r="F3">
-        <v>0.2602028007683616</v>
-      </c>
-      <c r="G3">
-        <v>0.8809803495022062</v>
-      </c>
-      <c r="H3">
-        <v>1.913271182809426</v>
-      </c>
-      <c r="I3">
-        <v>1.755738049990488</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>1.121305331718685</v>
-      </c>
-      <c r="E4">
-        <v>0.4273099001295377</v>
-      </c>
-      <c r="F4">
-        <v>0.1594268095201135</v>
-      </c>
-      <c r="G4">
-        <v>0.8917722169641169</v>
-      </c>
-      <c r="H4">
-        <v>1.5698579120013</v>
-      </c>
-      <c r="I4">
-        <v>1.394855358622803</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5">
-        <v>19</v>
-      </c>
-      <c r="D5">
-        <v>53.86518864767415</v>
-      </c>
-      <c r="E5">
-        <v>0.5681977399499447</v>
-      </c>
-      <c r="F5">
-        <v>0.2598850523000154</v>
-      </c>
-      <c r="G5">
-        <v>0.8794975187458534</v>
-      </c>
-      <c r="H5">
-        <v>1.650423269587353</v>
-      </c>
-      <c r="I5">
-        <v>1.365180932568826</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>61.08070029911875</v>
-      </c>
-      <c r="E6">
-        <v>0.4788638921806911</v>
-      </c>
-      <c r="F6">
-        <v>0.9254893726900082</v>
-      </c>
-      <c r="G6">
-        <v>0.9793989291894669</v>
-      </c>
-      <c r="H6">
-        <v>1.04308737387962</v>
-      </c>
-      <c r="I6">
-        <v>0.7375741554403465</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>17</v>
-      </c>
-      <c r="D7">
-        <v>1.017681660032122</v>
-      </c>
-      <c r="E7">
-        <v>0.5018431757227956</v>
-      </c>
-      <c r="F7">
-        <v>0.4220077889086216</v>
-      </c>
-      <c r="G7">
-        <v>0.7979069126061417</v>
-      </c>
-      <c r="H7">
-        <v>2.233996446339432</v>
-      </c>
-      <c r="I7">
-        <v>2.027318740887332</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8">
-        <v>17</v>
-      </c>
-      <c r="D8">
-        <v>1.051471993332928</v>
-      </c>
-      <c r="E8">
-        <v>0.3119360618233111</v>
-      </c>
-      <c r="F8">
-        <v>0.9476168913915635</v>
-      </c>
-      <c r="G8">
-        <v>0.3919919610818148</v>
-      </c>
-      <c r="H8">
-        <v>1.642640090746519</v>
-      </c>
-      <c r="I8">
-        <v>1.490671592589143</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9">
-        <v>17</v>
-      </c>
-      <c r="D9">
-        <v>1.287562935668985</v>
-      </c>
-      <c r="E9">
-        <v>0.2867174620062506</v>
-      </c>
-      <c r="F9">
-        <v>0.9537540652610096</v>
-      </c>
-      <c r="G9">
-        <v>0.4973830488955234</v>
-      </c>
-      <c r="H9">
-        <v>1.655374913650029</v>
-      </c>
-      <c r="I9">
-        <v>1.44758336875928</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10">
-        <v>17</v>
-      </c>
-      <c r="D10">
-        <v>1320.190136266348</v>
-      </c>
-      <c r="E10">
-        <v>1.045986551806551</v>
-      </c>
-      <c r="F10">
-        <v>0.912222834844275</v>
-      </c>
-      <c r="G10">
-        <v>0.5275374953958908</v>
-      </c>
-      <c r="H10">
-        <v>1.576901905053064</v>
-      </c>
-      <c r="I10">
-        <v>1.268459366590729</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11">
-        <v>13</v>
-      </c>
-      <c r="D11">
-        <v>1509.998127926904</v>
-      </c>
-      <c r="E11">
-        <v>2.834843051323265</v>
-      </c>
-      <c r="F11">
-        <v>0.5945294488259011</v>
-      </c>
-      <c r="G11">
-        <v>0.4051937054050931</v>
-      </c>
-      <c r="H11">
-        <v>1.968568108570851</v>
-      </c>
-      <c r="I11">
-        <v>1.091965116106979</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -5795,74 +4549,74 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6/Stats_Multiple_Regression_HT4_HT6_NRS.xlsx
@@ -74,7 +74,7 @@
     <t>(Intercept)</t>
   </si>
   <si>
-    <t>1.2e-05</t>
+    <t>&lt;10⁻⁵</t>
   </si>
   <si>
     <t>log_ROE</t>
@@ -83,7 +83,7 @@
     <t>log10 ROE</t>
   </si>
   <si>
-    <t>0.029</t>
+    <t>0.597</t>
   </si>
   <si>
     <t>R_5HT4</t>
@@ -92,7 +92,7 @@
     <t>5HT4</t>
   </si>
   <si>
-    <t>0.004</t>
+    <t>0.014</t>
   </si>
   <si>
     <t>HT6</t>
@@ -101,10 +101,7 @@
     <t>ROE + 5-HT6</t>
   </si>
   <si>
-    <t>7.8e-05</t>
-  </si>
-  <si>
-    <t>0.034</t>
+    <t>0.464</t>
   </si>
   <si>
     <t>R_5HT6</t>
@@ -113,7 +110,7 @@
     <t>5HT6</t>
   </si>
   <si>
-    <t>0.243</t>
+    <t>0.755</t>
   </si>
   <si>
     <t>HT4_HT6</t>
@@ -122,16 +119,10 @@
     <t>ROE + 5-HT4 + 5-HT6</t>
   </si>
   <si>
-    <t>2.1e-05</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>0.010</t>
-  </si>
-  <si>
-    <t>0.640</t>
+    <t>0.639</t>
+  </si>
+  <si>
+    <t>0.537</t>
   </si>
   <si>
     <t>HT4_HT6_ROEint</t>
@@ -140,16 +131,13 @@
     <t>ROE + 5-HT4 + 5-HT6 + ROEx5-HT4 + ROEx5-HT6</t>
   </si>
   <si>
-    <t>2.1e-04</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>0.846</t>
-  </si>
-  <si>
-    <t>0.894</t>
+    <t>0.532</t>
+  </si>
+  <si>
+    <t>0.436</t>
+  </si>
+  <si>
+    <t>0.185</t>
   </si>
   <si>
     <t>R_5HT4_x_ROE</t>
@@ -158,7 +146,7 @@
     <t>5-HT4 x log10 ROE</t>
   </si>
   <si>
-    <t>0.526</t>
+    <t>0.667</t>
   </si>
   <si>
     <t>R_5HT6_x_ROE</t>
@@ -167,7 +155,7 @@
     <t>5-HT6 x log10 ROE</t>
   </si>
   <si>
-    <t>0.871</t>
+    <t>0.119</t>
   </si>
   <si>
     <t>HT4_HT6_ROEint_Cov</t>
@@ -176,22 +164,22 @@
     <t>ROE + 5-HT4 + 5-HT6 + ROEx5-HT4 + ROEx5-HT6 + Sex + log MME + MQS non-opioid</t>
   </si>
   <si>
-    <t>0.540</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>0.218</t>
-  </si>
-  <si>
-    <t>0.411</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>0.503</t>
+    <t>0.974</t>
+  </si>
+  <si>
+    <t>0.186</t>
+  </si>
+  <si>
+    <t>0.861</t>
+  </si>
+  <si>
+    <t>0.463</t>
+  </si>
+  <si>
+    <t>0.309</t>
+  </si>
+  <si>
+    <t>0.170</t>
   </si>
   <si>
     <t>sex_female</t>
@@ -200,7 +188,7 @@
     <t>Sex (female)</t>
   </si>
   <si>
-    <t>0.073</t>
+    <t>0.207</t>
   </si>
   <si>
     <t>log_MME</t>
@@ -209,7 +197,7 @@
     <t>log10 MME</t>
   </si>
   <si>
-    <t>0.252</t>
+    <t>0.008</t>
   </si>
   <si>
     <t>MQS_nonopioid</t>
@@ -218,217 +206,229 @@
     <t>MQS non-opioid</t>
   </si>
   <si>
-    <t>0.009</t>
+    <t>0.022</t>
   </si>
   <si>
     <t>Tramadol group</t>
   </si>
   <si>
+    <t>0.012</t>
+  </si>
+  <si>
+    <t>0.520</t>
+  </si>
+  <si>
+    <t>0.701</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>0.657</t>
+  </si>
+  <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>0.603</t>
+  </si>
+  <si>
+    <t>0.459</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>0.287</t>
+  </si>
+  <si>
+    <t>0.424</t>
+  </si>
+  <si>
+    <t>0.251</t>
+  </si>
+  <si>
+    <t>0.453</t>
+  </si>
+  <si>
+    <t>0.355</t>
+  </si>
+  <si>
+    <t>0.995</t>
+  </si>
+  <si>
+    <t>0.927</t>
+  </si>
+  <si>
+    <t>0.649</t>
+  </si>
+  <si>
+    <t>0.499</t>
+  </si>
+  <si>
+    <t>0.663</t>
+  </si>
+  <si>
+    <t>0.643</t>
+  </si>
+  <si>
+    <t>0.891</t>
+  </si>
+  <si>
+    <t>0.266</t>
+  </si>
+  <si>
+    <t>0.203</t>
+  </si>
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>adj_R2</t>
+  </si>
+  <si>
+    <t>F_stat</t>
+  </si>
+  <si>
+    <t>df1</t>
+  </si>
+  <si>
+    <t>df2</t>
+  </si>
+  <si>
+    <t>F_p</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>AIC</t>
+  </si>
+  <si>
+    <t>BIC</t>
+  </si>
+  <si>
+    <t>max_VIF</t>
+  </si>
+  <si>
+    <t>max_cooksD</t>
+  </si>
+  <si>
+    <t>shapiro_p</t>
+  </si>
+  <si>
+    <t>bp_p</t>
+  </si>
+  <si>
+    <t>F_p_fmt</t>
+  </si>
+  <si>
+    <t>nrs ~ log_ROE + R_5HT4</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>nrs ~ log_ROE + R_5HT6</t>
+  </si>
+  <si>
+    <t>0.729</t>
+  </si>
+  <si>
+    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE +      sex_female + log_MME + MQS_nonopioid</t>
+  </si>
+  <si>
+    <t>7.8e-04</t>
+  </si>
+  <si>
+    <t>0.708</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>0.172</t>
+  </si>
+  <si>
+    <t>0.324</t>
+  </si>
+  <si>
+    <t>0.455</t>
+  </si>
+  <si>
+    <t>reduced</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>added_term</t>
+  </si>
+  <si>
+    <t>added_lab</t>
+  </si>
+  <si>
+    <t>df_num</t>
+  </si>
+  <si>
+    <t>df_den</t>
+  </si>
+  <si>
+    <t>R2_reduced</t>
+  </si>
+  <si>
+    <t>R2_full</t>
+  </si>
+  <si>
+    <t>delta_R2</t>
+  </si>
+  <si>
+    <t>adjR2_reduced</t>
+  </si>
+  <si>
+    <t>adjR2_full</t>
+  </si>
+  <si>
+    <t>delta_adjR2</t>
+  </si>
+  <si>
+    <t>delta_AIC</t>
+  </si>
+  <si>
+    <t>R_5HT4_x_ROE + R_5HT6_x_ROE</t>
+  </si>
+  <si>
+    <t>5-HT4 x log10 ROE + 5-HT6 x log10 ROE</t>
+  </si>
+  <si>
     <t>0.241</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>0.615</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>0.003</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>0.006</t>
-  </si>
-  <si>
-    <t>0.392</t>
-  </si>
-  <si>
-    <t>0.573</t>
-  </si>
-  <si>
-    <t>0.260</t>
-  </si>
-  <si>
-    <t>0.865</t>
-  </si>
-  <si>
-    <t>0.289</t>
-  </si>
-  <si>
-    <t>0.836</t>
-  </si>
-  <si>
-    <t>0.365</t>
-  </si>
-  <si>
-    <t>0.774</t>
-  </si>
-  <si>
-    <t>0.641</t>
-  </si>
-  <si>
-    <t>0.970</t>
-  </si>
-  <si>
-    <t>0.536</t>
-  </si>
-  <si>
-    <t>0.983</t>
-  </si>
-  <si>
-    <t>0.585</t>
-  </si>
-  <si>
-    <t>0.451</t>
-  </si>
-  <si>
-    <t>0.879</t>
-  </si>
-  <si>
-    <t>0.549</t>
-  </si>
-  <si>
-    <t>formula</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>adj_R2</t>
-  </si>
-  <si>
-    <t>F_stat</t>
-  </si>
-  <si>
-    <t>df1</t>
-  </si>
-  <si>
-    <t>df2</t>
-  </si>
-  <si>
-    <t>F_p</t>
-  </si>
-  <si>
-    <t>sigma</t>
-  </si>
-  <si>
-    <t>RMSE</t>
-  </si>
-  <si>
-    <t>AIC</t>
-  </si>
-  <si>
-    <t>BIC</t>
-  </si>
-  <si>
-    <t>max_VIF</t>
-  </si>
-  <si>
-    <t>max_cooksD</t>
-  </si>
-  <si>
-    <t>shapiro_p</t>
-  </si>
-  <si>
-    <t>bp_p</t>
-  </si>
-  <si>
-    <t>F_p_fmt</t>
-  </si>
-  <si>
-    <t>nrs ~ log_ROE + R_5HT4</t>
-  </si>
-  <si>
-    <t>0.002</t>
-  </si>
-  <si>
-    <t>nrs ~ log_ROE + R_5HT6</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6</t>
-  </si>
-  <si>
-    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE</t>
-  </si>
-  <si>
-    <t>nrs ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE +      sex_female + log_MME + MQS_nonopioid</t>
-  </si>
-  <si>
-    <t>0.167</t>
-  </si>
-  <si>
-    <t>0.012</t>
-  </si>
-  <si>
-    <t>0.222</t>
-  </si>
-  <si>
-    <t>reduced</t>
-  </si>
-  <si>
-    <t>full</t>
-  </si>
-  <si>
-    <t>added_term</t>
-  </si>
-  <si>
-    <t>added_lab</t>
-  </si>
-  <si>
-    <t>df_num</t>
-  </si>
-  <si>
-    <t>df_den</t>
-  </si>
-  <si>
-    <t>R2_reduced</t>
-  </si>
-  <si>
-    <t>R2_full</t>
-  </si>
-  <si>
-    <t>delta_R2</t>
-  </si>
-  <si>
-    <t>adjR2_reduced</t>
-  </si>
-  <si>
-    <t>adjR2_full</t>
-  </si>
-  <si>
-    <t>delta_adjR2</t>
-  </si>
-  <si>
-    <t>delta_AIC</t>
-  </si>
-  <si>
-    <t>R_5HT4_x_ROE + R_5HT6_x_ROE</t>
-  </si>
-  <si>
-    <t>5-HT4 x log10 ROE + 5-HT6 x log10 ROE</t>
-  </si>
-  <si>
-    <t>0.756</t>
-  </si>
-  <si>
-    <t>0.234</t>
   </si>
   <si>
     <t>setting</t>
@@ -904,28 +904,28 @@
         <v>17</v>
       </c>
       <c r="F2">
-        <v>10.10749021689429</v>
+        <v>6.794285389721852</v>
       </c>
       <c r="G2">
-        <v>1.61896309063729</v>
+        <v>0.9599225993324049</v>
       </c>
       <c r="H2">
-        <v>6.243187553408378</v>
+        <v>7.077951279037557</v>
       </c>
       <c r="I2">
-        <v>1.174421191918157E-05</v>
+        <v>7.322212117848059E-07</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
       </c>
       <c r="K2">
-        <v>6.675441781808676</v>
+        <v>4.791921935310018</v>
       </c>
       <c r="L2">
-        <v>13.5395386519799</v>
+        <v>8.796648844133685</v>
       </c>
       <c r="M2">
-        <v>6.117020341898763E-17</v>
+        <v>-9.186360889144584E-17</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -945,31 +945,31 @@
         <v>20</v>
       </c>
       <c r="F3">
-        <v>1.375844308585351</v>
+        <v>0.1397675755035537</v>
       </c>
       <c r="G3">
-        <v>0.5736027463473203</v>
+        <v>0.2598168538700222</v>
       </c>
       <c r="H3">
-        <v>2.398601327045021</v>
+        <v>0.5379465320347339</v>
       </c>
       <c r="I3">
-        <v>0.02899989459508434</v>
+        <v>0.5965501416413883</v>
       </c>
       <c r="J3" t="s">
         <v>21</v>
       </c>
       <c r="K3">
-        <v>0.1598608069558021</v>
+        <v>-0.4022008846529292</v>
       </c>
       <c r="L3">
-        <v>2.591827810214901</v>
+        <v>0.6817360356600366</v>
       </c>
       <c r="M3">
-        <v>0.4080145151788713</v>
+        <v>0.1024484219665803</v>
       </c>
       <c r="N3">
-        <v>1.01163910023057</v>
+        <v>1.01381011202702</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -989,31 +989,31 @@
         <v>23</v>
       </c>
       <c r="F4">
-        <v>2.58713861483516</v>
+        <v>2.397938528513136</v>
       </c>
       <c r="G4">
-        <v>0.7708836522997121</v>
+        <v>0.8925649406612035</v>
       </c>
       <c r="H4">
-        <v>3.356068853084597</v>
+        <v>2.686570376309836</v>
       </c>
       <c r="I4">
-        <v>0.004015571334531572</v>
+        <v>0.01418859194096281</v>
       </c>
       <c r="J4" t="s">
         <v>24</v>
       </c>
       <c r="K4">
-        <v>0.9529382752419655</v>
+        <v>0.5360806879828397</v>
       </c>
       <c r="L4">
-        <v>4.221338954428354</v>
+        <v>4.259796369043432</v>
       </c>
       <c r="M4">
-        <v>0.5708847029135828</v>
+        <v>0.5116398734165161</v>
       </c>
       <c r="N4">
-        <v>1.01163910023057</v>
+        <v>1.01381011202702</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1033,28 +1033,28 @@
         <v>17</v>
       </c>
       <c r="F5">
-        <v>10.72565127387594</v>
+        <v>6.799185237003141</v>
       </c>
       <c r="G5">
-        <v>2.040174230340469</v>
+        <v>1.126305379762461</v>
       </c>
       <c r="H5">
-        <v>5.257223189259682</v>
+        <v>6.036715582799665</v>
       </c>
       <c r="I5">
-        <v>7.819866788925478E-05</v>
+        <v>6.683426612954517E-06</v>
       </c>
       <c r="J5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K5">
-        <v>6.400675111642535</v>
+        <v>4.44975338435975</v>
       </c>
       <c r="L5">
-        <v>15.05062743610934</v>
+        <v>9.148617089646532</v>
       </c>
       <c r="M5">
-        <v>9.097704169396715E-17</v>
+        <v>-6.164743228857931E-17</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1074,31 +1074,31 @@
         <v>20</v>
       </c>
       <c r="F6">
-        <v>1.659416823273141</v>
+        <v>0.2245577670434684</v>
       </c>
       <c r="G6">
-        <v>0.7152994799819661</v>
+        <v>0.3004581876018346</v>
       </c>
       <c r="H6">
-        <v>2.319890996306858</v>
+        <v>0.7473844159009938</v>
       </c>
       <c r="I6">
-        <v>0.03389211693392566</v>
+        <v>0.4635288488096567</v>
       </c>
       <c r="J6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K6">
-        <v>0.1430496651291635</v>
+        <v>-0.4021870297257084</v>
       </c>
       <c r="L6">
-        <v>3.175783981417118</v>
+        <v>0.8513025638126452</v>
       </c>
       <c r="M6">
-        <v>0.492109569667527</v>
+        <v>0.1645988977848254</v>
       </c>
       <c r="N6">
-        <v>1.007973823773254</v>
+        <v>1.001226066313922</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1112,37 +1112,37 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7">
+        <v>0.4653703778267558</v>
+      </c>
+      <c r="G7">
+        <v>1.47271615585347</v>
+      </c>
+      <c r="H7">
+        <v>0.3159946171413214</v>
+      </c>
+      <c r="I7">
+        <v>0.7552806267536638</v>
+      </c>
+      <c r="J7" t="s">
         <v>30</v>
       </c>
-      <c r="F7">
-        <v>1.771794170495995</v>
-      </c>
-      <c r="G7">
-        <v>1.462268419973902</v>
-      </c>
-      <c r="H7">
-        <v>1.211675056572457</v>
-      </c>
-      <c r="I7">
-        <v>0.2432283212671872</v>
-      </c>
-      <c r="J7" t="s">
-        <v>31</v>
-      </c>
       <c r="K7">
-        <v>-1.32807640189057</v>
+        <v>-2.606661691481481</v>
       </c>
       <c r="L7">
-        <v>4.87166474288256</v>
+        <v>3.537402447134992</v>
       </c>
       <c r="M7">
-        <v>0.257027977442039</v>
+        <v>0.06959252103844972</v>
       </c>
       <c r="N7">
-        <v>1.007973823773254</v>
+        <v>1.001226066313922</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1150,10 +1150,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
         <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -1162,28 +1162,28 @@
         <v>17</v>
       </c>
       <c r="F8">
-        <v>10.23828795713792</v>
+        <v>6.712546745977011</v>
       </c>
       <c r="G8">
-        <v>1.682057087763823</v>
+        <v>0.9833758909014795</v>
       </c>
       <c r="H8">
-        <v>6.086766038808475</v>
+        <v>6.82602330205949</v>
       </c>
       <c r="I8">
-        <v>2.080842722461056E-05</v>
+        <v>1.625316452247182E-06</v>
       </c>
       <c r="J8" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K8">
-        <v>6.653068141818125</v>
+        <v>4.654317351795012</v>
       </c>
       <c r="L8">
-        <v>13.82350777245772</v>
+        <v>8.770776140159008</v>
       </c>
       <c r="M8">
-        <v>6.665869146464014E-17</v>
+        <v>-9.959694874388693E-17</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1191,10 +1191,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
         <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
@@ -1203,31 +1203,31 @@
         <v>20</v>
       </c>
       <c r="F9">
-        <v>1.411945101876969</v>
+        <v>0.1261341214908759</v>
       </c>
       <c r="G9">
-        <v>0.5928323484362782</v>
+        <v>0.264720326307401</v>
       </c>
       <c r="H9">
-        <v>2.381693754737364</v>
+        <v>0.476480681518975</v>
       </c>
       <c r="I9">
-        <v>0.03091031219680021</v>
+        <v>0.6391657017637534</v>
       </c>
       <c r="J9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K9">
-        <v>0.1483528622093293</v>
+        <v>-0.4279318891613313</v>
       </c>
       <c r="L9">
-        <v>2.675537341544608</v>
+        <v>0.6802001321430831</v>
       </c>
       <c r="M9">
-        <v>0.4187204123363754</v>
+        <v>0.09245521828882693</v>
       </c>
       <c r="N9">
-        <v>1.028417812864244</v>
+        <v>1.020648366032284</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1235,10 +1235,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
         <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -1247,31 +1247,31 @@
         <v>23</v>
       </c>
       <c r="F10">
-        <v>2.463101544153731</v>
+        <v>2.617184130207266</v>
       </c>
       <c r="G10">
-        <v>0.8319297511509806</v>
+        <v>0.9710338604250602</v>
       </c>
       <c r="H10">
-        <v>2.960708570340239</v>
+        <v>2.69525527056453</v>
       </c>
       <c r="I10">
-        <v>0.009719532889465282</v>
+        <v>0.01433522672757038</v>
       </c>
       <c r="J10" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="K10">
-        <v>0.6898852541253162</v>
+        <v>0.5847869026926538</v>
       </c>
       <c r="L10">
-        <v>4.236317834182145</v>
+        <v>4.649581357721878</v>
       </c>
       <c r="M10">
-        <v>0.5435143618579487</v>
+        <v>0.5584195512790122</v>
       </c>
       <c r="N10">
-        <v>1.121305331718685</v>
+        <v>1.163657854297254</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1279,43 +1279,43 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
       <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
         <v>29</v>
       </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
       <c r="F11">
-        <v>0.6022133601106154</v>
+        <v>-0.8663007856997285</v>
       </c>
       <c r="G11">
-        <v>1.263164922208297</v>
+        <v>1.376843701387318</v>
       </c>
       <c r="H11">
-        <v>0.4767495910651247</v>
+        <v>-0.6291932663285142</v>
       </c>
       <c r="I11">
-        <v>0.640411386456087</v>
+        <v>0.536715046277304</v>
       </c>
       <c r="J11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K11">
-        <v>-2.090158939297307</v>
+        <v>-3.748067771863957</v>
       </c>
       <c r="L11">
-        <v>3.294585659518538</v>
+        <v>2.015466200464501</v>
       </c>
       <c r="M11">
-        <v>0.0873609838633094</v>
+        <v>-0.1295485456895101</v>
       </c>
       <c r="N11">
-        <v>1.117242722797308</v>
+        <v>1.149213804608694</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1323,10 +1323,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -1335,28 +1335,28 @@
         <v>17</v>
       </c>
       <c r="F12">
-        <v>9.902340064556773</v>
+        <v>7.060342256434608</v>
       </c>
       <c r="G12">
-        <v>1.952111539446245</v>
+        <v>1.033009420329955</v>
       </c>
       <c r="H12">
-        <v>5.072630259316927</v>
+        <v>6.834731724110954</v>
       </c>
       <c r="I12">
-        <v>0.0002137698813614068</v>
+        <v>2.901229338516259E-06</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K12">
-        <v>5.685059480817777</v>
+        <v>4.880882889373906</v>
       </c>
       <c r="L12">
-        <v>14.11962064829577</v>
+        <v>9.23980162349531</v>
       </c>
       <c r="M12">
-        <v>5.368454873047635E-17</v>
+        <v>-1.397148285506614E-16</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1364,10 +1364,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
@@ -1376,31 +1376,31 @@
         <v>20</v>
       </c>
       <c r="F13">
-        <v>1.278045426650765</v>
+        <v>0.1887143857785156</v>
       </c>
       <c r="G13">
-        <v>0.6780795506097234</v>
+        <v>0.2956249153721954</v>
       </c>
       <c r="H13">
-        <v>1.884801606981891</v>
+        <v>0.6383575130699721</v>
       </c>
       <c r="I13">
-        <v>0.08200757702644451</v>
+        <v>0.531747213289538</v>
       </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K13">
-        <v>-0.1868563810748567</v>
+        <v>-0.4349996658693981</v>
       </c>
       <c r="L13">
-        <v>2.742947234376387</v>
+        <v>0.8124284374264293</v>
       </c>
       <c r="M13">
-        <v>0.3790116962199406</v>
+        <v>0.1383260098470396</v>
       </c>
       <c r="N13">
-        <v>1.217298576161407</v>
+        <v>1.346254426039904</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1408,10 +1408,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
@@ -1420,31 +1420,31 @@
         <v>23</v>
       </c>
       <c r="F14">
-        <v>0.5866724405731458</v>
+        <v>1.83976930139979</v>
       </c>
       <c r="G14">
-        <v>2.969857851793622</v>
+        <v>2.307240069351527</v>
       </c>
       <c r="H14">
-        <v>0.1975422629129639</v>
+        <v>0.7973896283436491</v>
       </c>
       <c r="I14">
-        <v>0.8464584846887609</v>
+        <v>0.4362213882792572</v>
       </c>
       <c r="J14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K14">
-        <v>-5.829315376591715</v>
+        <v>-3.028081738719284</v>
       </c>
       <c r="L14">
-        <v>7.002660257738007</v>
+        <v>6.707620341518863</v>
       </c>
       <c r="M14">
-        <v>0.1294566591923903</v>
+        <v>0.3925452305349316</v>
       </c>
       <c r="N14">
-        <v>12.92861246286382</v>
+        <v>6.948413229344522</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1452,43 +1452,43 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15">
+        <v>5.235724624971145</v>
+      </c>
+      <c r="G15">
+        <v>3.788639593108615</v>
+      </c>
+      <c r="H15">
+        <v>1.381953732018934</v>
+      </c>
+      <c r="I15">
+        <v>0.184876956032276</v>
+      </c>
+      <c r="J15" t="s">
         <v>39</v>
       </c>
-      <c r="D15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15">
-        <v>-1.238207904083448</v>
-      </c>
-      <c r="G15">
-        <v>9.082348762412622</v>
-      </c>
-      <c r="H15">
-        <v>-0.1363312438746883</v>
-      </c>
-      <c r="I15">
-        <v>0.8936480221241607</v>
-      </c>
-      <c r="J15" t="s">
-        <v>43</v>
-      </c>
       <c r="K15">
-        <v>-20.8594294974633</v>
+        <v>-2.757606207365488</v>
       </c>
       <c r="L15">
-        <v>18.3830136892964</v>
+        <v>13.22905545730778</v>
       </c>
       <c r="M15">
-        <v>-0.1796224858050113</v>
+        <v>0.7829619019078983</v>
       </c>
       <c r="N15">
-        <v>52.25812053263659</v>
+        <v>9.203259078112049</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1496,43 +1496,43 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F16">
-        <v>-0.834611263116579</v>
+        <v>-0.389249964863533</v>
       </c>
       <c r="G16">
-        <v>1.279701386227992</v>
+        <v>0.88935562560793</v>
       </c>
       <c r="H16">
-        <v>-0.6521922005387936</v>
+        <v>-0.4376763958708378</v>
       </c>
       <c r="I16">
-        <v>0.525641540877594</v>
+        <v>0.6671307754147855</v>
       </c>
       <c r="J16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K16">
-        <v>-3.599238027555519</v>
+        <v>-2.265626318004838</v>
       </c>
       <c r="L16">
-        <v>1.930015501322361</v>
+        <v>1.487126388277772</v>
       </c>
       <c r="M16">
-        <v>-0.4490746223254154</v>
+        <v>-0.2559490431463763</v>
       </c>
       <c r="N16">
-        <v>14.27279410864606</v>
+        <v>9.805012756907791</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1540,43 +1540,43 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F17">
-        <v>-0.5088683148202404</v>
+        <v>1.776922128456777</v>
       </c>
       <c r="G17">
-        <v>3.070790525600985</v>
+        <v>1.083817795638416</v>
       </c>
       <c r="H17">
-        <v>-0.1657124804110986</v>
+        <v>1.639502631906955</v>
       </c>
       <c r="I17">
-        <v>0.870932576241951</v>
+        <v>0.119480853958127</v>
       </c>
       <c r="J17" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K17">
-        <v>-7.142907916891511</v>
+        <v>-0.5097335403141181</v>
       </c>
       <c r="L17">
-        <v>6.12517128725103</v>
+        <v>4.063577797227671</v>
       </c>
       <c r="M17">
-        <v>-0.2216653048878749</v>
+        <v>1.04511857489558</v>
       </c>
       <c r="N17">
-        <v>53.86518864767415</v>
+        <v>11.6507609133532</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1584,10 +1584,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -1596,28 +1596,28 @@
         <v>17</v>
       </c>
       <c r="F18">
-        <v>1.828221291047192</v>
+        <v>-0.05348719281451544</v>
       </c>
       <c r="G18">
-        <v>2.867846524034585</v>
+        <v>1.624656229821602</v>
       </c>
       <c r="H18">
-        <v>0.637489236514368</v>
+        <v>-0.03292216029011177</v>
       </c>
       <c r="I18">
-        <v>0.5396831608311319</v>
+        <v>0.9742367724465317</v>
       </c>
       <c r="J18" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="K18">
-        <v>-4.659298265103578</v>
+        <v>-3.563343589248114</v>
       </c>
       <c r="L18">
-        <v>8.315740847197961</v>
+        <v>3.456369203619083</v>
       </c>
       <c r="M18">
-        <v>-1.748993587185722E-16</v>
+        <v>2.356822851929768E-16</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1625,10 +1625,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
         <v>19</v>
@@ -1637,31 +1637,31 @@
         <v>20</v>
       </c>
       <c r="F19">
-        <v>-0.05194554429486767</v>
+        <v>-0.2876924842647662</v>
       </c>
       <c r="G19">
-        <v>0.5701285613569899</v>
+        <v>0.2060308609959838</v>
       </c>
       <c r="H19">
-        <v>-0.09111198388523042</v>
+        <v>-1.396356268541606</v>
       </c>
       <c r="I19">
-        <v>0.9293992600759664</v>
+        <v>0.1859937537311021</v>
       </c>
       <c r="J19" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K19">
-        <v>-1.341665953084418</v>
+        <v>-0.7327950986245318</v>
       </c>
       <c r="L19">
-        <v>1.237774864494683</v>
+        <v>0.1574101300949995</v>
       </c>
       <c r="M19">
-        <v>-0.01548002713661297</v>
+        <v>-0.2115185523113217</v>
       </c>
       <c r="N19">
-        <v>2.147524359538006</v>
+        <v>1.691081219252941</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1669,10 +1669,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
@@ -1681,31 +1681,31 @@
         <v>23</v>
       </c>
       <c r="F20">
-        <v>-2.79181759345162</v>
+        <v>0.2671902449238823</v>
       </c>
       <c r="G20">
-        <v>2.108240965572673</v>
+        <v>1.493503153885728</v>
       </c>
       <c r="H20">
-        <v>-1.324240273783535</v>
+        <v>0.1789016944682835</v>
       </c>
       <c r="I20">
-        <v>0.2180657591054126</v>
+        <v>0.8607729664552745</v>
       </c>
       <c r="J20" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K20">
-        <v>-7.560989994626445</v>
+        <v>-2.95932715705917</v>
       </c>
       <c r="L20">
-        <v>1.977354807723205</v>
+        <v>3.493707646906934</v>
       </c>
       <c r="M20">
-        <v>-0.6079502216739275</v>
+        <v>0.05639911500886938</v>
       </c>
       <c r="N20">
-        <v>15.68007473575603</v>
+        <v>7.324461223577913</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1713,43 +1713,43 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21">
+        <v>1.927801414287574</v>
+      </c>
+      <c r="G21">
+        <v>2.551137162362826</v>
+      </c>
+      <c r="H21">
+        <v>0.7556635694578149</v>
+      </c>
+      <c r="I21">
+        <v>0.463323895457126</v>
+      </c>
+      <c r="J21" t="s">
         <v>51</v>
       </c>
-      <c r="D21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21">
-        <v>-5.495507284001475</v>
-      </c>
-      <c r="G21">
-        <v>6.380967108170462</v>
-      </c>
-      <c r="H21">
-        <v>-0.861234228423587</v>
-      </c>
-      <c r="I21">
-        <v>0.4114660252044843</v>
-      </c>
-      <c r="J21" t="s">
-        <v>55</v>
-      </c>
       <c r="K21">
-        <v>-19.93025773332903</v>
+        <v>-3.583595349618503</v>
       </c>
       <c r="L21">
-        <v>8.939243165326083</v>
+        <v>7.439198178193651</v>
       </c>
       <c r="M21">
-        <v>-0.7697879499094803</v>
+        <v>0.2804914759566485</v>
       </c>
       <c r="N21">
-        <v>59.43541820810998</v>
+        <v>10.15412202891363</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1757,43 +1757,43 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F22">
-        <v>-1.932213905458058</v>
+        <v>-0.5983796852183109</v>
       </c>
       <c r="G22">
-        <v>0.8733408625524705</v>
+        <v>0.5649714694158653</v>
       </c>
       <c r="H22">
-        <v>-2.212439596391805</v>
+        <v>-1.059132571485401</v>
       </c>
       <c r="I22">
-        <v>0.05422896907145851</v>
+        <v>0.3088225377918506</v>
       </c>
       <c r="J22" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K22">
-        <v>-3.907848193245492</v>
+        <v>-1.818926339540073</v>
       </c>
       <c r="L22">
-        <v>0.04342038232937506</v>
+        <v>0.6221669691034514</v>
       </c>
       <c r="M22">
-        <v>-1.017785101958202</v>
+        <v>-0.3913404210520974</v>
       </c>
       <c r="N22">
-        <v>15.74399719434322</v>
+        <v>10.06164015914702</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1801,43 +1801,43 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F23">
-        <v>-1.502017604888746</v>
+        <v>1.033736944061372</v>
       </c>
       <c r="G23">
-        <v>2.153554970164709</v>
+        <v>0.7112839510019571</v>
       </c>
       <c r="H23">
-        <v>-0.6974596078101819</v>
+        <v>1.453339334600743</v>
       </c>
       <c r="I23">
-        <v>0.5031329126524713</v>
+        <v>0.1698405864745297</v>
       </c>
       <c r="J23" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K23">
-        <v>-6.373697406126516</v>
+        <v>-0.5028986095282719</v>
       </c>
       <c r="L23">
-        <v>3.369662196349025</v>
+        <v>2.570372497651016</v>
       </c>
       <c r="M23">
-        <v>-0.6319725722756425</v>
+        <v>0.6009719302043309</v>
       </c>
       <c r="N23">
-        <v>61.08070029911875</v>
+        <v>12.60185079627546</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1845,43 +1845,43 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F24">
-        <v>1.242107842466939</v>
+        <v>0.7091830236768881</v>
       </c>
       <c r="G24">
-        <v>0.6128722921647237</v>
+        <v>0.5339281889876979</v>
       </c>
       <c r="H24">
-        <v>2.026699295019024</v>
+        <v>1.328236714793922</v>
       </c>
       <c r="I24">
-        <v>0.07332438590515773</v>
+        <v>0.2069477949327304</v>
       </c>
       <c r="J24" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K24">
-        <v>-0.1443056031340451</v>
+        <v>-0.4442987006140764</v>
       </c>
       <c r="L24">
-        <v>2.628521288067923</v>
+        <v>1.862664747967853</v>
       </c>
       <c r="M24">
-        <v>0.2910546361517289</v>
+        <v>0.1699729194894863</v>
       </c>
       <c r="N24">
-        <v>1.534320472076546</v>
+        <v>1.206892310244196</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1889,43 +1889,43 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E25" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F25">
-        <v>1.484329999294819</v>
+        <v>2.941140530498599</v>
       </c>
       <c r="G25">
-        <v>1.211537304524129</v>
+        <v>0.9397144932262405</v>
       </c>
       <c r="H25">
-        <v>1.225162439284392</v>
+        <v>3.129823527996292</v>
       </c>
       <c r="I25">
-        <v>0.2516095807119866</v>
+        <v>0.007975490246739424</v>
       </c>
       <c r="J25" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="K25">
-        <v>-1.256357792131669</v>
+        <v>0.911010793308813</v>
       </c>
       <c r="L25">
-        <v>4.225017790721308</v>
+        <v>4.971270267688386</v>
       </c>
       <c r="M25">
-        <v>0.2362361095267534</v>
+        <v>0.4939420932560564</v>
       </c>
       <c r="N25">
-        <v>2.765991782932822</v>
+        <v>1.835576070806632</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1933,48 +1933,48 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F26">
-        <v>0.09640589246893831</v>
+        <v>0.07121326762944705</v>
       </c>
       <c r="G26">
-        <v>0.02924678992963755</v>
+        <v>0.02749016894791665</v>
       </c>
       <c r="H26">
-        <v>3.296289702250172</v>
+        <v>2.590499453254322</v>
       </c>
       <c r="I26">
-        <v>0.009284696343749841</v>
+        <v>0.02240615481717743</v>
       </c>
       <c r="J26" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K26">
-        <v>0.03024505714075432</v>
+        <v>0.01182436827350119</v>
       </c>
       <c r="L26">
-        <v>0.1625667277971223</v>
+        <v>0.1306021669853929</v>
       </c>
       <c r="M26">
-        <v>0.5891230058109815</v>
+        <v>0.4091003520729791</v>
       </c>
       <c r="N26">
-        <v>2.376330748734058</v>
+        <v>1.838030485108268</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
@@ -1989,33 +1989,33 @@
         <v>17</v>
       </c>
       <c r="F27">
-        <v>-8.618603698098783</v>
+        <v>6.665179260997519</v>
       </c>
       <c r="G27">
-        <v>7.042351060199127</v>
+        <v>2.396103999645568</v>
       </c>
       <c r="H27">
-        <v>-1.223824774485907</v>
+        <v>2.781673609318892</v>
       </c>
       <c r="I27">
-        <v>0.2412163428046945</v>
+        <v>0.01231043096633879</v>
       </c>
       <c r="J27" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="K27">
-        <v>-23.7229445036577</v>
+        <v>1.631151557432441</v>
       </c>
       <c r="L27">
-        <v>6.485737107460135</v>
+        <v>11.6992069645626</v>
       </c>
       <c r="M27">
-        <v>2.549396886789191E-16</v>
+        <v>-2.143688242424856E-16</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
@@ -2030,36 +2030,36 @@
         <v>20</v>
       </c>
       <c r="F28">
-        <v>-3.511290391677422</v>
+        <v>0.3435335052957038</v>
       </c>
       <c r="G28">
-        <v>1.751985142324548</v>
+        <v>0.5230153656865397</v>
       </c>
       <c r="H28">
-        <v>-2.00417817871367</v>
+        <v>0.6568325288966648</v>
       </c>
       <c r="I28">
-        <v>0.06479240799018404</v>
+        <v>0.519598963624976</v>
       </c>
       <c r="J28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K28">
-        <v>-7.26892480236489</v>
+        <v>-0.7552810038598738</v>
       </c>
       <c r="L28">
-        <v>0.2463440190100465</v>
+        <v>1.442348014451281</v>
       </c>
       <c r="M28">
-        <v>-0.4754847166404753</v>
+        <v>0.1545811649279696</v>
       </c>
       <c r="N28">
-        <v>1.017681660032122</v>
+        <v>1.03589293707489</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
@@ -2074,36 +2074,36 @@
         <v>23</v>
       </c>
       <c r="F29">
-        <v>0.6805961087246314</v>
+        <v>0.5096642556860471</v>
       </c>
       <c r="G29">
-        <v>1.322614030297522</v>
+        <v>1.307696768564257</v>
       </c>
       <c r="H29">
-        <v>0.514584068468963</v>
+        <v>0.3897419248390561</v>
       </c>
       <c r="I29">
-        <v>0.6148709436016764</v>
+        <v>0.7013004356267195</v>
       </c>
       <c r="J29" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K29">
-        <v>-2.15612885671081</v>
+        <v>-2.237704707342584</v>
       </c>
       <c r="L29">
-        <v>3.517321074160073</v>
+        <v>3.257033218714678</v>
       </c>
       <c r="M29">
-        <v>0.1220833868876404</v>
+        <v>0.09172316855879835</v>
       </c>
       <c r="N29">
-        <v>1.017681660032122</v>
+        <v>1.03589293707489</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
@@ -2118,33 +2118,33 @@
         <v>17</v>
       </c>
       <c r="F30">
-        <v>-10.6127934040996</v>
+        <v>7.136076277481951</v>
       </c>
       <c r="G30">
-        <v>5.175514159846477</v>
+        <v>2.116160979292637</v>
       </c>
       <c r="H30">
-        <v>-2.050577599890946</v>
+        <v>3.372180258170768</v>
       </c>
       <c r="I30">
-        <v>0.05951621020672625</v>
+        <v>0.003394241034608621</v>
       </c>
       <c r="J30" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="K30">
-        <v>-21.71316727726842</v>
+        <v>2.69018703538799</v>
       </c>
       <c r="L30">
-        <v>0.4875804690692256</v>
+        <v>11.58196551957591</v>
       </c>
       <c r="M30">
-        <v>2.705530520589896E-16</v>
+        <v>-2.433589695300672E-16</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
@@ -2159,36 +2159,36 @@
         <v>20</v>
       </c>
       <c r="F31">
-        <v>-4.411999436516661</v>
+        <v>0.2116238289062774</v>
       </c>
       <c r="G31">
-        <v>1.309432873444871</v>
+        <v>0.4685443865017951</v>
       </c>
       <c r="H31">
-        <v>-3.369397184072156</v>
+        <v>0.4516622864405326</v>
       </c>
       <c r="I31">
-        <v>0.004583616726171178</v>
+        <v>0.6569071673660187</v>
       </c>
       <c r="J31" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K31">
-        <v>-7.22045363220318</v>
+        <v>-0.7727513995265595</v>
       </c>
       <c r="L31">
-        <v>-1.603545240830142</v>
+        <v>1.195999057339114</v>
       </c>
       <c r="M31">
-        <v>-0.597455085703657</v>
+        <v>0.09522523274896059</v>
       </c>
       <c r="N31">
-        <v>1.051471993332928</v>
+        <v>1.030136629964357</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
         <v>25</v>
@@ -2197,48 +2197,48 @@
         <v>26</v>
       </c>
       <c r="D32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" t="s">
         <v>29</v>
       </c>
-      <c r="E32" t="s">
-        <v>30</v>
-      </c>
       <c r="F32">
-        <v>5.448492357166543</v>
+        <v>3.420817910634935</v>
       </c>
       <c r="G32">
-        <v>1.5482478081329</v>
+        <v>1.614011677174695</v>
       </c>
       <c r="H32">
-        <v>3.519134552327976</v>
+        <v>2.119450533730356</v>
       </c>
       <c r="I32">
-        <v>0.00340331696787525</v>
+        <v>0.04821445347274762</v>
       </c>
       <c r="J32" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K32">
-        <v>2.127831068685181</v>
+        <v>0.0299052048522146</v>
       </c>
       <c r="L32">
-        <v>8.769153645647906</v>
+        <v>6.811730616417656</v>
       </c>
       <c r="M32">
-        <v>0.6240062304031372</v>
+        <v>0.446849729174709</v>
       </c>
       <c r="N32">
-        <v>1.051471993332927</v>
+        <v>1.030136629964357</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" t="s">
         <v>32</v>
-      </c>
-      <c r="C33" t="s">
-        <v>33</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -2247,39 +2247,39 @@
         <v>17</v>
       </c>
       <c r="F33">
-        <v>-10.19144750992142</v>
+        <v>7.572569114152238</v>
       </c>
       <c r="G33">
-        <v>5.237262160554294</v>
+        <v>2.217629079587136</v>
       </c>
       <c r="H33">
-        <v>-1.945949467009839</v>
+        <v>3.414714022221449</v>
       </c>
       <c r="I33">
-        <v>0.07360487493619533</v>
+        <v>0.003300953552315416</v>
       </c>
       <c r="J33" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="K33">
-        <v>-21.50586452726152</v>
+        <v>2.89378073618314</v>
       </c>
       <c r="L33">
-        <v>1.122969507418674</v>
+        <v>12.25135749212134</v>
       </c>
       <c r="M33">
-        <v>2.625400713087132E-16</v>
+        <v>-2.666303942927031E-16</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" t="s">
         <v>32</v>
-      </c>
-      <c r="C34" t="s">
-        <v>33</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
@@ -2288,42 +2288,42 @@
         <v>20</v>
       </c>
       <c r="F34">
-        <v>-4.366789316193658</v>
+        <v>0.2529679298636416</v>
       </c>
       <c r="G34">
-        <v>1.320570139566511</v>
+        <v>0.4773023716955067</v>
       </c>
       <c r="H34">
-        <v>-3.30674546194653</v>
+        <v>0.5299951244009775</v>
       </c>
       <c r="I34">
-        <v>0.005673610803694174</v>
+        <v>0.6029694926816085</v>
       </c>
       <c r="J34" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K34">
-        <v>-7.219707654373844</v>
+        <v>-0.7540520492763261</v>
       </c>
       <c r="L34">
-        <v>-1.513870978013472</v>
+        <v>1.259987909003609</v>
       </c>
       <c r="M34">
-        <v>-0.591332914406741</v>
+        <v>0.1138290055698611</v>
       </c>
       <c r="N34">
-        <v>1.053043406545435</v>
+        <v>1.043759348059124</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" t="s">
         <v>32</v>
-      </c>
-      <c r="C35" t="s">
-        <v>33</v>
       </c>
       <c r="D35" t="s">
         <v>22</v>
@@ -2332,86 +2332,86 @@
         <v>23</v>
       </c>
       <c r="F35">
-        <v>-0.9611352860384266</v>
+        <v>-1.051628436687748</v>
       </c>
       <c r="G35">
-        <v>1.084507089405542</v>
+        <v>1.38699232146856</v>
       </c>
       <c r="H35">
-        <v>-0.8862415888542138</v>
+        <v>-0.7582078288467191</v>
       </c>
       <c r="I35">
-        <v>0.3915870564538799</v>
+        <v>0.458709606010013</v>
       </c>
       <c r="J35" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K35">
-        <v>-3.304070409701851</v>
+        <v>-3.97792644285731</v>
       </c>
       <c r="L35">
-        <v>1.381799837624998</v>
+        <v>1.874669569481815</v>
       </c>
       <c r="M35">
-        <v>-0.17240570357752</v>
+        <v>-0.1892592844865975</v>
       </c>
       <c r="N35">
-        <v>1.246185532354503</v>
+        <v>1.409860367392662</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" t="s">
         <v>32</v>
       </c>
-      <c r="C36" t="s">
-        <v>33</v>
-      </c>
       <c r="D36" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" t="s">
         <v>29</v>
       </c>
-      <c r="E36" t="s">
-        <v>30</v>
-      </c>
       <c r="F36">
-        <v>6.103712680342809</v>
+        <v>4.164940468576444</v>
       </c>
       <c r="G36">
-        <v>1.726552559379775</v>
+        <v>1.905580793812701</v>
       </c>
       <c r="H36">
-        <v>3.535202358702262</v>
+        <v>2.185654096693114</v>
       </c>
       <c r="I36">
-        <v>0.003658663645030331</v>
+        <v>0.0431233419581149</v>
       </c>
       <c r="J36" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="K36">
-        <v>2.37372264732313</v>
+        <v>0.1445164249704325</v>
       </c>
       <c r="L36">
-        <v>9.83370271336249</v>
+        <v>8.185364512182456</v>
       </c>
       <c r="M36">
-        <v>0.6990474596362041</v>
+        <v>0.5440519106925317</v>
       </c>
       <c r="N36">
-        <v>1.287562935668985</v>
+        <v>1.402025977401938</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -2420,39 +2420,39 @@
         <v>17</v>
       </c>
       <c r="F37">
-        <v>-7.025807352399712</v>
+        <v>12.37887134325402</v>
       </c>
       <c r="G37">
-        <v>12.10172011153177</v>
+        <v>5.369266132363192</v>
       </c>
       <c r="H37">
-        <v>-0.5805627041154916</v>
+        <v>2.305505266099684</v>
       </c>
       <c r="I37">
-        <v>0.5732365592471065</v>
+        <v>0.03584077390969835</v>
       </c>
       <c r="J37" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K37">
-        <v>-33.66151372946366</v>
+        <v>0.9345514854390053</v>
       </c>
       <c r="L37">
-        <v>19.60989902466424</v>
+        <v>23.82319120106904</v>
       </c>
       <c r="M37">
-        <v>-5.082782219216875E-16</v>
+        <v>-6.464873210647709E-16</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D38" t="s">
         <v>19</v>
@@ -2461,42 +2461,42 @@
         <v>20</v>
       </c>
       <c r="F38">
-        <v>-3.532744279421006</v>
+        <v>1.362573334403291</v>
       </c>
       <c r="G38">
-        <v>2.977497728821761</v>
+        <v>1.234195138705521</v>
       </c>
       <c r="H38">
-        <v>-1.186480931697961</v>
+        <v>1.104017745388642</v>
       </c>
       <c r="I38">
-        <v>0.260426198282804</v>
+        <v>0.2869817083317103</v>
       </c>
       <c r="J38" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K38">
-        <v>-10.08617259476426</v>
+        <v>-1.268051333122675</v>
       </c>
       <c r="L38">
-        <v>3.020684035922248</v>
+        <v>3.993198001929257</v>
       </c>
       <c r="M38">
-        <v>-0.4783899151848027</v>
+        <v>0.613122650585555</v>
       </c>
       <c r="N38">
-        <v>5.89942369691529</v>
+        <v>6.596146876697277</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s">
         <v>22</v>
@@ -2505,174 +2505,174 @@
         <v>23</v>
       </c>
       <c r="F39">
-        <v>5.833484528910711</v>
+        <v>-16.55072442711214</v>
       </c>
       <c r="G39">
-        <v>33.62541035817681</v>
+        <v>20.14041462523017</v>
       </c>
       <c r="H39">
-        <v>0.1734844115439074</v>
+        <v>-0.8217668173712185</v>
       </c>
       <c r="I39">
-        <v>0.865421941006731</v>
+        <v>0.4240795867295765</v>
       </c>
       <c r="J39" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K39">
-        <v>-68.17554467142811</v>
+        <v>-59.47900202744442</v>
       </c>
       <c r="L39">
-        <v>79.84251372924955</v>
+        <v>26.37755317322015</v>
       </c>
       <c r="M39">
-        <v>1.046393800253498</v>
+        <v>-2.978597909234908</v>
       </c>
       <c r="N39">
-        <v>1320.190136266348</v>
+        <v>280.9792596993184</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D40" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" t="s">
         <v>29</v>
       </c>
-      <c r="E40" t="s">
-        <v>30</v>
-      </c>
       <c r="F40">
-        <v>35.69942855371251</v>
+        <v>21.62506003364044</v>
       </c>
       <c r="G40">
-        <v>32.06615363008937</v>
+        <v>18.1049342570722</v>
       </c>
       <c r="H40">
-        <v>1.113305604580334</v>
+        <v>1.194429083618086</v>
       </c>
       <c r="I40">
-        <v>0.2893137205361322</v>
+        <v>0.25085628571147</v>
       </c>
       <c r="J40" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K40">
-        <v>-34.87769972733284</v>
+        <v>-16.96469386098571</v>
       </c>
       <c r="L40">
-        <v>106.2765568347579</v>
+        <v>60.21481392826659</v>
       </c>
       <c r="M40">
-        <v>4.088592656287188</v>
+        <v>2.824807537804753</v>
       </c>
       <c r="N40">
-        <v>489.4248092751843</v>
+        <v>119.6202462527081</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E41" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F41">
-        <v>1.763626570521479</v>
+        <v>-3.817011212851301</v>
       </c>
       <c r="G41">
-        <v>8.33421038896889</v>
+        <v>4.949710464280141</v>
       </c>
       <c r="H41">
-        <v>0.2116129169064179</v>
+        <v>-0.7711584829854136</v>
       </c>
       <c r="I41">
-        <v>0.8362786983247414</v>
+        <v>0.4525902437098861</v>
       </c>
       <c r="J41" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K41">
-        <v>-16.57984681668061</v>
+        <v>-14.36706933259367</v>
       </c>
       <c r="L41">
-        <v>20.10709995772357</v>
+        <v>6.733046906891071</v>
       </c>
       <c r="M41">
-        <v>1.256225479341864</v>
+        <v>-2.972388327574307</v>
       </c>
       <c r="N41">
-        <v>1278.845061605036</v>
+        <v>317.7397271440617</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E42" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F42">
-        <v>7.413311777533256</v>
+        <v>4.053008619180903</v>
       </c>
       <c r="G42">
-        <v>7.850372629092067</v>
+        <v>4.246116826631245</v>
       </c>
       <c r="H42">
-        <v>0.9443261011663137</v>
+        <v>0.9545212213099777</v>
       </c>
       <c r="I42">
-        <v>0.3652831392486496</v>
+        <v>0.3549505491195191</v>
       </c>
       <c r="J42" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K42">
-        <v>-9.865241880287968</v>
+        <v>-4.99737516133598</v>
       </c>
       <c r="L42">
-        <v>24.69186543535448</v>
+        <v>13.10339239969779</v>
       </c>
       <c r="M42">
-        <v>3.432787595952272</v>
+        <v>2.741082865488492</v>
       </c>
       <c r="N42">
-        <v>479.5312997909448</v>
+        <v>176.3684335962053</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
@@ -2681,39 +2681,39 @@
         <v>17</v>
       </c>
       <c r="F43">
-        <v>-8.565392342781157</v>
+        <v>-0.06624307516693249</v>
       </c>
       <c r="G43">
-        <v>27.82231610331168</v>
+        <v>10.73991403094985</v>
       </c>
       <c r="H43">
-        <v>-0.3078605070467739</v>
+        <v>-0.006167933465392357</v>
       </c>
       <c r="I43">
-        <v>0.7735531303060883</v>
+        <v>0.9952297663618666</v>
       </c>
       <c r="J43" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K43">
-        <v>-85.81252570308662</v>
+        <v>-24.83252924227452</v>
       </c>
       <c r="L43">
-        <v>68.68174101752432</v>
+        <v>24.70004309194065</v>
       </c>
       <c r="M43">
-        <v>-3.479997159803594E-16</v>
+        <v>-6.47933489017708E-17</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C44" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D44" t="s">
         <v>19</v>
@@ -2722,42 +2722,42 @@
         <v>20</v>
       </c>
       <c r="F44">
-        <v>-3.28623266226647</v>
+        <v>0.1802247249480476</v>
       </c>
       <c r="G44">
-        <v>6.517868070138991</v>
+        <v>1.894954233794749</v>
       </c>
       <c r="H44">
-        <v>-0.5041882755071464</v>
+        <v>0.09510769269985889</v>
       </c>
       <c r="I44">
-        <v>0.6406338509391254</v>
+        <v>0.9265684174381512</v>
       </c>
       <c r="J44" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K44">
-        <v>-21.38273556192886</v>
+        <v>-4.189547574205285</v>
       </c>
       <c r="L44">
-        <v>14.81027023739592</v>
+        <v>4.54999702410138</v>
       </c>
       <c r="M44">
-        <v>-0.335075842545724</v>
+        <v>0.08014225177542152</v>
       </c>
       <c r="N44">
-        <v>9.83669863928314</v>
+        <v>11.84480760643306</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D45" t="s">
         <v>22</v>
@@ -2766,295 +2766,295 @@
         <v>23</v>
       </c>
       <c r="F45">
-        <v>-1.886091124073796</v>
+        <v>-12.25337597672485</v>
       </c>
       <c r="G45">
-        <v>47.80442939832684</v>
+        <v>25.89778856667206</v>
       </c>
       <c r="H45">
-        <v>-0.03945431726332475</v>
+        <v>-0.4731437182437176</v>
       </c>
       <c r="I45">
-        <v>0.9704188544286534</v>
+        <v>0.6487516195574812</v>
       </c>
       <c r="J45" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K45">
-        <v>-134.6124651338318</v>
+        <v>-71.97378350411377</v>
       </c>
       <c r="L45">
-        <v>130.8402828856842</v>
+        <v>47.46703155066406</v>
       </c>
       <c r="M45">
-        <v>-0.3248691183222625</v>
+        <v>-2.155116709997016</v>
       </c>
       <c r="N45">
-        <v>1509.998127926904</v>
+        <v>346.0920734595073</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C46" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D46" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" t="s">
         <v>29</v>
       </c>
-      <c r="E46" t="s">
-        <v>30</v>
-      </c>
       <c r="F46">
-        <v>47.74848681303564</v>
+        <v>17.94782027650155</v>
       </c>
       <c r="G46">
-        <v>70.70238063213495</v>
+        <v>25.32561182837809</v>
       </c>
       <c r="H46">
-        <v>0.6753448241222796</v>
+        <v>0.7086825936576383</v>
       </c>
       <c r="I46">
-        <v>0.5364845963625324</v>
+        <v>0.4986486994477883</v>
       </c>
       <c r="J46" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K46">
-        <v>-148.5527918188867</v>
+        <v>-40.45314532631384</v>
       </c>
       <c r="L46">
-        <v>244.049765444958</v>
+        <v>76.34878587931694</v>
       </c>
       <c r="M46">
-        <v>4.662763691735115</v>
+        <v>2.14389700244283</v>
       </c>
       <c r="N46">
-        <v>1061.657115641728</v>
+        <v>152.665366063833</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D47" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E47" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F47">
-        <v>-0.2656776392476792</v>
+        <v>-2.909631807266604</v>
       </c>
       <c r="G47">
-        <v>11.86093317114378</v>
+        <v>6.423828784572828</v>
       </c>
       <c r="H47">
-        <v>-0.02239938758731403</v>
+        <v>-0.4529435489087508</v>
       </c>
       <c r="I47">
-        <v>0.9832022150942343</v>
+        <v>0.662621212114537</v>
       </c>
       <c r="J47" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K47">
-        <v>-33.19690748534797</v>
+        <v>-17.72300754833509</v>
       </c>
       <c r="L47">
-        <v>32.66555220685262</v>
+        <v>11.90374393380188</v>
       </c>
       <c r="M47">
-        <v>-0.183286808004701</v>
+        <v>-2.247879473420355</v>
       </c>
       <c r="N47">
-        <v>1491.20977191473</v>
+        <v>410.8602321533518</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E48" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F48">
-        <v>10.19545284992796</v>
+        <v>2.899503669110876</v>
       </c>
       <c r="G48">
-        <v>17.20902092055179</v>
+        <v>6.013212678854174</v>
       </c>
       <c r="H48">
-        <v>0.5924481640760915</v>
+        <v>0.4821887772749425</v>
       </c>
       <c r="I48">
-        <v>0.5854191223842596</v>
+        <v>0.6425877304750094</v>
       </c>
       <c r="J48" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K48">
-        <v>-37.58444905018449</v>
+        <v>-10.96698963418897</v>
       </c>
       <c r="L48">
-        <v>57.9753547500404</v>
+        <v>16.76599697241072</v>
       </c>
       <c r="M48">
-        <v>4.088973628664985</v>
+        <v>1.866211684297022</v>
       </c>
       <c r="N48">
-        <v>1060.905052376005</v>
+        <v>249.8755904226072</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E49" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F49">
-        <v>1.498309202610451</v>
+        <v>0.2937057917039008</v>
       </c>
       <c r="G49">
-        <v>1.797450544274193</v>
+        <v>2.073220421618082</v>
       </c>
       <c r="H49">
-        <v>0.8335746468148116</v>
+        <v>0.1416664569967302</v>
       </c>
       <c r="I49">
-        <v>0.4514035274989894</v>
+        <v>0.8908460320506801</v>
       </c>
       <c r="J49" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K49">
-        <v>-3.492213562874741</v>
+        <v>-4.487149073737119</v>
       </c>
       <c r="L49">
-        <v>6.488831968095644</v>
+        <v>5.074560657144921</v>
       </c>
       <c r="M49">
-        <v>0.2098052536131294</v>
+        <v>0.04717478782673095</v>
       </c>
       <c r="N49">
-        <v>1.410887344908986</v>
+        <v>1.849788466128847</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D50" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E50" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F50">
-        <v>0.6257416865540727</v>
+        <v>4.571466125855214</v>
       </c>
       <c r="G50">
-        <v>3.84361133467724</v>
+        <v>3.822337929742566</v>
       </c>
       <c r="H50">
-        <v>0.1628004582327568</v>
+        <v>1.195986909028502</v>
       </c>
       <c r="I50">
-        <v>0.8785691959241584</v>
+        <v>0.265944204271084</v>
       </c>
       <c r="J50" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K50">
-        <v>-10.04583418989331</v>
+        <v>-4.242860946278872</v>
       </c>
       <c r="L50">
-        <v>11.29731756300145</v>
+        <v>13.3857931979893</v>
       </c>
       <c r="M50">
-        <v>0.0381518160393763</v>
+        <v>0.4004947722985648</v>
       </c>
       <c r="N50">
-        <v>1.223116427490704</v>
+        <v>1.870583384208452</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C51" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E51" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F51">
-        <v>0.04228262003223595</v>
+        <v>0.1020275684120469</v>
       </c>
       <c r="G51">
-        <v>0.06472401480274068</v>
+        <v>0.07354772703175166</v>
       </c>
       <c r="H51">
-        <v>0.653275606605997</v>
+        <v>1.387229388720606</v>
       </c>
       <c r="I51">
-        <v>0.5492260186729562</v>
+        <v>0.2027935210892635</v>
       </c>
       <c r="J51" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K51">
-        <v>-0.1374200540555829</v>
+        <v>-0.06757379425803965</v>
       </c>
       <c r="L51">
-        <v>0.2219852941200548</v>
+        <v>0.2716289310821334</v>
       </c>
       <c r="M51">
-        <v>0.1496423847524685</v>
+        <v>0.427032854735327</v>
       </c>
       <c r="N51">
-        <v>1.168597551198277</v>
+        <v>1.5807465367321</v>
       </c>
     </row>
   </sheetData>
@@ -3075,61 +3075,61 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -3140,61 +3140,61 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>0.5423542182666674</v>
+        <v>0.2845064891361842</v>
       </c>
       <c r="G2">
-        <v>0.4851484955500008</v>
+        <v>0.2129571380498025</v>
       </c>
       <c r="H2">
-        <v>9.480768575425332</v>
+        <v>3.976367148217729</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K2">
-        <v>0.001924135753232884</v>
+        <v>0.03516065792606456</v>
       </c>
       <c r="L2">
-        <v>1.531481188713505</v>
+        <v>1.85320502161696</v>
       </c>
       <c r="M2">
-        <v>1.405383523270676</v>
+        <v>1.72812259331291</v>
       </c>
       <c r="N2">
-        <v>74.8514532235269</v>
+        <v>98.43481072861663</v>
       </c>
       <c r="O2">
-        <v>78.62920914019267</v>
+        <v>102.9767875923332</v>
       </c>
       <c r="P2">
-        <v>1.01163910023057</v>
+        <v>1.01381011202702</v>
       </c>
       <c r="Q2">
-        <v>0.5795877175725123</v>
+        <v>0.6456134694995845</v>
       </c>
       <c r="R2">
-        <v>0.1691410039128372</v>
+        <v>0.8496237199841992</v>
       </c>
       <c r="S2">
-        <v>0.6544893796276015</v>
+        <v>0.2869294079853869</v>
       </c>
       <c r="T2" t="s">
         <v>16</v>
       </c>
       <c r="U2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -3205,61 +3205,61 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>0.2857352938597114</v>
+        <v>0.03113421888602168</v>
       </c>
       <c r="G3">
-        <v>0.1964522055921754</v>
+        <v>-0.06575235922537637</v>
       </c>
       <c r="H3">
-        <v>3.200329417408903</v>
+        <v>0.3213470791612055</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K3">
-        <v>0.06774441976825894</v>
+        <v>0.7288466726527358</v>
       </c>
       <c r="L3">
-        <v>1.913271182809426</v>
+        <v>2.156514722729037</v>
       </c>
       <c r="M3">
-        <v>1.755738049990488</v>
+        <v>2.010960347985854</v>
       </c>
       <c r="N3">
-        <v>83.30945803494667</v>
+        <v>105.407342607054</v>
       </c>
       <c r="O3">
-        <v>87.08721395161243</v>
+        <v>109.9493194707706</v>
       </c>
       <c r="P3">
-        <v>1.007973823773254</v>
+        <v>1.001226066313922</v>
       </c>
       <c r="Q3">
-        <v>0.2926251835358054</v>
+        <v>0.5286822215276535</v>
       </c>
       <c r="R3">
-        <v>0.2602028007683616</v>
+        <v>0.8262574420475279</v>
       </c>
       <c r="S3">
-        <v>0.8809803495022062</v>
+        <v>0.9196585177067426</v>
       </c>
       <c r="T3" t="s">
         <v>26</v>
       </c>
       <c r="U3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -3267,64 +3267,64 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>0.5491852688037044</v>
+        <v>0.2991102344296735</v>
       </c>
       <c r="G4">
-        <v>0.4590223225644453</v>
+        <v>0.1884434293396219</v>
       </c>
       <c r="H4">
-        <v>6.091030647405533</v>
+        <v>2.702799942460453</v>
       </c>
       <c r="I4">
         <v>3</v>
       </c>
       <c r="J4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K4">
-        <v>0.006387463856358749</v>
+        <v>0.07444733779744316</v>
       </c>
       <c r="L4">
-        <v>1.5698579120013</v>
+        <v>1.881844245117446</v>
       </c>
       <c r="M4">
-        <v>1.394855358622803</v>
+        <v>1.710395549150666</v>
       </c>
       <c r="N4">
-        <v>76.56571178603471</v>
+        <v>99.96050684408745</v>
       </c>
       <c r="O4">
-        <v>81.28790668186691</v>
+        <v>105.6379779237332</v>
       </c>
       <c r="P4">
-        <v>1.121305331718685</v>
+        <v>1.163657854297254</v>
       </c>
       <c r="Q4">
-        <v>0.4273099001295377</v>
+        <v>0.6996202726518953</v>
       </c>
       <c r="R4">
-        <v>0.1594268095201135</v>
+        <v>0.9326466220450975</v>
       </c>
       <c r="S4">
-        <v>0.8917722169641169</v>
+        <v>0.6072212868760981</v>
       </c>
       <c r="T4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U4" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -3332,64 +3332,64 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5">
-        <v>0.5681626756787765</v>
+        <v>0.4070725894038524</v>
       </c>
       <c r="G5">
-        <v>0.4020713970936907</v>
+        <v>0.2326821745226326</v>
       </c>
       <c r="H5">
-        <v>3.420785730105122</v>
+        <v>2.33426011218057</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="J5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K5">
-        <v>0.03427369420482255</v>
+        <v>0.08704163914451371</v>
       </c>
       <c r="L5">
-        <v>1.650423269587353</v>
+        <v>1.829834955868813</v>
       </c>
       <c r="M5">
-        <v>1.365180932568826</v>
+        <v>1.573158432238486</v>
       </c>
       <c r="N5">
-        <v>79.74856916681688</v>
+        <v>100.1130981122079</v>
       </c>
       <c r="O5">
-        <v>86.35964202098197</v>
+        <v>108.061557623712</v>
       </c>
       <c r="P5">
-        <v>53.86518864767415</v>
+        <v>11.6507609133532</v>
       </c>
       <c r="Q5">
-        <v>0.5681977399499447</v>
+        <v>4.764166958172268</v>
       </c>
       <c r="R5">
-        <v>0.2598850523000154</v>
+        <v>0.3113820582203898</v>
       </c>
       <c r="S5">
-        <v>0.8794975187458534</v>
+        <v>0.98143337827237</v>
       </c>
       <c r="T5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="U5" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -3397,389 +3397,389 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>8</v>
       </c>
       <c r="F6">
-        <v>0.8790246632349847</v>
+        <v>0.823606190872186</v>
       </c>
       <c r="G6">
-        <v>0.7714910305549711</v>
+        <v>0.7150561544858389</v>
       </c>
       <c r="H6">
-        <v>8.174416146162267</v>
+        <v>7.587341453676157</v>
       </c>
       <c r="I6">
         <v>8</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K6">
-        <v>0.002438185066128097</v>
+        <v>0.0007777012876700377</v>
       </c>
       <c r="L6">
-        <v>1.04308737387962</v>
+        <v>1.135083662342778</v>
       </c>
       <c r="M6">
-        <v>0.7375741554403465</v>
+        <v>0.8725457520363624</v>
       </c>
       <c r="N6">
-        <v>60.12379593672846</v>
+        <v>76.43432717068637</v>
       </c>
       <c r="O6">
-        <v>69.0275135156901</v>
+        <v>87.34475170426953</v>
       </c>
       <c r="P6">
-        <v>61.08070029911875</v>
+        <v>12.60185079627546</v>
       </c>
       <c r="Q6">
-        <v>0.4788638921806911</v>
+        <v>5.267903921499294</v>
       </c>
       <c r="R6">
-        <v>0.9254893726900082</v>
+        <v>0.3839029071968507</v>
       </c>
       <c r="S6">
-        <v>0.9793989291894669</v>
+        <v>0.1708790703642055</v>
       </c>
       <c r="T6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="U6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>0.2256869953733925</v>
+        <v>0.0375870024217027</v>
       </c>
       <c r="G7">
-        <v>0.1150708518553056</v>
+        <v>-0.06934777508699708</v>
       </c>
       <c r="H7">
-        <v>2.040271774042552</v>
+        <v>0.3514946521363904</v>
       </c>
       <c r="I7">
         <v>2</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K7">
-        <v>0.1668844505736521</v>
+        <v>0.7083588373351388</v>
       </c>
       <c r="L7">
-        <v>2.233996446339432</v>
+        <v>2.34184253239145</v>
       </c>
       <c r="M7">
-        <v>2.027318740887332</v>
+        <v>2.168124886990257</v>
       </c>
       <c r="N7">
-        <v>80.2721896210583</v>
+        <v>100.0976512325781</v>
       </c>
       <c r="O7">
-        <v>83.60504299728316</v>
+        <v>104.2757409834718</v>
       </c>
       <c r="P7">
-        <v>1.017681660032122</v>
+        <v>1.03589293707489</v>
       </c>
       <c r="Q7">
-        <v>0.5018431757227956</v>
+        <v>0.1823749204000267</v>
       </c>
       <c r="R7">
-        <v>0.4220077889086216</v>
+        <v>0.2010733948132116</v>
       </c>
       <c r="S7">
-        <v>0.7979069126061417</v>
+        <v>0.2573258684407913</v>
       </c>
       <c r="T7" t="s">
         <v>16</v>
       </c>
       <c r="U7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8">
-        <v>0.581364133429465</v>
+        <v>0.2232985729528257</v>
       </c>
       <c r="G8">
-        <v>0.5215590096336744</v>
+        <v>0.1369984143920285</v>
       </c>
       <c r="H8">
-        <v>9.720975336738347</v>
+        <v>2.587464225752439</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K8">
-        <v>0.002253486890922358</v>
+        <v>0.10286957079677</v>
       </c>
       <c r="L8">
-        <v>1.642640090746519</v>
+        <v>2.103797821740693</v>
       </c>
       <c r="M8">
-        <v>1.490671592589143</v>
+        <v>1.947738309225244</v>
       </c>
       <c r="N8">
-        <v>69.81761968638281</v>
+        <v>95.59551043127256</v>
       </c>
       <c r="O8">
-        <v>73.15047306260767</v>
+        <v>99.77360018216625</v>
       </c>
       <c r="P8">
-        <v>1.051471993332928</v>
+        <v>1.030136629964357</v>
       </c>
       <c r="Q8">
-        <v>0.3119360618233111</v>
+        <v>0.2456290742825697</v>
       </c>
       <c r="R8">
-        <v>0.9476168913915635</v>
+        <v>0.8137550751748333</v>
       </c>
       <c r="S8">
-        <v>0.3919919610818148</v>
+        <v>0.2143203191406846</v>
       </c>
       <c r="T8" t="s">
         <v>26</v>
       </c>
       <c r="U8" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D9">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>0.6052159001643111</v>
+        <v>0.2487046894681947</v>
       </c>
       <c r="G9">
-        <v>0.5141118771253059</v>
+        <v>0.116123164080229</v>
       </c>
       <c r="H9">
-        <v>6.643130346781668</v>
+        <v>1.875862332556701</v>
       </c>
       <c r="I9">
         <v>3</v>
       </c>
       <c r="J9">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K9">
-        <v>0.005860031563866003</v>
+        <v>0.1719847926856928</v>
       </c>
       <c r="L9">
-        <v>1.655374913650029</v>
+        <v>2.129090295660157</v>
       </c>
       <c r="M9">
-        <v>1.44758336875928</v>
+        <v>1.915617931886438</v>
       </c>
       <c r="N9">
-        <v>70.82035793830373</v>
+        <v>96.89710891219121</v>
       </c>
       <c r="O9">
-        <v>74.98642465858481</v>
+        <v>102.1197211008083</v>
       </c>
       <c r="P9">
-        <v>1.287562935668985</v>
+        <v>1.409860367392662</v>
       </c>
       <c r="Q9">
-        <v>0.2867174620062506</v>
+        <v>0.1630427025879717</v>
       </c>
       <c r="R9">
-        <v>0.9537540652610096</v>
+        <v>0.78185150196044</v>
       </c>
       <c r="S9">
-        <v>0.4973830488955234</v>
+        <v>0.3399393834114433</v>
       </c>
       <c r="T9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U9" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E10">
         <v>5</v>
       </c>
       <c r="F10">
-        <v>0.696872315126521</v>
+        <v>0.2986358641783577</v>
       </c>
       <c r="G10">
-        <v>0.5590870038203942</v>
+        <v>0.06484781890447699</v>
       </c>
       <c r="H10">
-        <v>5.057667675317242</v>
+        <v>1.27737867788966</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K10">
-        <v>0.01190990646581135</v>
+        <v>0.3242845389202932</v>
       </c>
       <c r="L10">
-        <v>1.576901905053064</v>
+        <v>2.189975971861964</v>
       </c>
       <c r="M10">
-        <v>1.268459366590729</v>
+        <v>1.850867510372357</v>
       </c>
       <c r="N10">
-        <v>70.32921440355418</v>
+        <v>99.45290545020981</v>
       </c>
       <c r="O10">
-        <v>76.16170781194769</v>
+        <v>106.7645625142738</v>
       </c>
       <c r="P10">
-        <v>1320.190136266348</v>
+        <v>317.7397271440617</v>
       </c>
       <c r="Q10">
-        <v>1.045986551806551</v>
+        <v>6.239174602978902</v>
       </c>
       <c r="R10">
-        <v>0.912222834844275</v>
+        <v>0.8381742606828063</v>
       </c>
       <c r="S10">
-        <v>0.5275374953958908</v>
+        <v>0.4007046320049603</v>
       </c>
       <c r="T10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="U10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="F11">
-        <v>0.8203979138143715</v>
+        <v>0.5204280584377704</v>
       </c>
       <c r="G11">
-        <v>0.4611937414431146</v>
+        <v>0.0408561168755408</v>
       </c>
       <c r="H11">
-        <v>2.283932027845283</v>
+        <v>1.085192884184279</v>
       </c>
       <c r="I11">
         <v>8</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>0.2215610425643967</v>
+        <v>0.4553881389889591</v>
       </c>
       <c r="L11">
-        <v>1.968568108570851</v>
+        <v>2.395987946889964</v>
       </c>
       <c r="M11">
-        <v>1.091965116106979</v>
+        <v>1.643634171640534</v>
       </c>
       <c r="N11">
-        <v>59.17985409156405</v>
+        <v>85.1388415792845</v>
       </c>
       <c r="O11">
-        <v>64.82934766617942</v>
+        <v>93.47097501984666</v>
       </c>
       <c r="P11">
-        <v>1509.998127926904</v>
+        <v>410.8602321533518</v>
       </c>
       <c r="Q11">
-        <v>2.834843051323265</v>
+        <v>4.221319101336776</v>
       </c>
       <c r="R11">
-        <v>0.5945294488259011</v>
+        <v>0.03225714142840883</v>
       </c>
       <c r="S11">
-        <v>0.4051937054050931</v>
+        <v>0.6020674406216109</v>
       </c>
       <c r="T11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="U11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3797,52 +3797,52 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>9</v>
@@ -3856,52 +3856,52 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
         <v>29</v>
       </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
       <c r="F2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>0.2272901725807632</v>
+        <v>0.3958841663931423</v>
       </c>
       <c r="J2">
-        <v>0.6404113864560872</v>
+        <v>0.5367150462773054</v>
       </c>
       <c r="K2">
-        <v>0.5423542182666674</v>
+        <v>0.2845064891361842</v>
       </c>
       <c r="L2">
-        <v>0.5491852688037044</v>
+        <v>0.2991102344296735</v>
       </c>
       <c r="M2">
-        <v>0.006831050537037031</v>
+        <v>0.01460374529348929</v>
       </c>
       <c r="N2">
-        <v>0.4851484955500008</v>
+        <v>0.2129571380498025</v>
       </c>
       <c r="O2">
-        <v>0.4590223225644453</v>
+        <v>0.1884434293396219</v>
       </c>
       <c r="P2">
-        <v>-0.02612617298555553</v>
+        <v>-0.02451370871018066</v>
       </c>
       <c r="Q2">
-        <v>1.714258562507808</v>
+        <v>1.525696115470822</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -3912,7 +3912,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -3921,43 +3921,43 @@
         <v>23</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I3">
-        <v>8.765795238486142</v>
+        <v>7.264400973505871</v>
       </c>
       <c r="J3">
-        <v>0.009719532889465282</v>
+        <v>0.0143352267275704</v>
       </c>
       <c r="K3">
-        <v>0.2857352938597114</v>
+        <v>0.03113421888602168</v>
       </c>
       <c r="L3">
-        <v>0.5491852688037044</v>
+        <v>0.2991102344296735</v>
       </c>
       <c r="M3">
-        <v>0.263449974943993</v>
+        <v>0.2679760155436518</v>
       </c>
       <c r="N3">
-        <v>0.1964522055921754</v>
+        <v>-0.06575235922537637</v>
       </c>
       <c r="O3">
-        <v>0.4590223225644453</v>
+        <v>0.1884434293396219</v>
       </c>
       <c r="P3">
-        <v>0.26257011697227</v>
+        <v>0.2541957885649982</v>
       </c>
       <c r="Q3">
-        <v>-6.743746248911961</v>
+        <v>-5.446835762966515</v>
       </c>
       <c r="R3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -3965,122 +3965,122 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
       <c r="H4">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I4">
-        <v>0.285647251269581</v>
+        <v>1.547710564363785</v>
       </c>
       <c r="J4">
-        <v>0.756124834990865</v>
+        <v>0.2412628093574826</v>
       </c>
       <c r="K4">
-        <v>0.5491852688037044</v>
+        <v>0.2991102344296735</v>
       </c>
       <c r="L4">
-        <v>0.5681626756787765</v>
+        <v>0.4070725894038524</v>
       </c>
       <c r="M4">
-        <v>0.0189774068750721</v>
+        <v>0.1079623549741789</v>
       </c>
       <c r="N4">
-        <v>0.4590223225644453</v>
+        <v>0.1884434293396219</v>
       </c>
       <c r="O4">
-        <v>0.4020713970936907</v>
+        <v>0.2326821745226326</v>
       </c>
       <c r="P4">
-        <v>-0.05695092547075464</v>
+        <v>0.04423874518301074</v>
       </c>
       <c r="Q4">
-        <v>3.182857380782167</v>
+        <v>0.1525912681204744</v>
       </c>
       <c r="R4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
       <c r="F5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I5">
-        <v>12.49765571697403</v>
+        <v>4.777083830391387</v>
       </c>
       <c r="J5">
-        <v>0.003658663645030331</v>
+        <v>0.04312334195811496</v>
       </c>
       <c r="K5">
-        <v>0.2256869953733925</v>
+        <v>0.0375870024217027</v>
       </c>
       <c r="L5">
-        <v>0.6052159001643111</v>
+        <v>0.2487046894681947</v>
       </c>
       <c r="M5">
-        <v>0.3795289047909187</v>
+        <v>0.2111176870464919</v>
       </c>
       <c r="N5">
-        <v>0.1150708518553056</v>
+        <v>-0.06934777508699708</v>
       </c>
       <c r="O5">
-        <v>0.5141118771253059</v>
+        <v>0.116123164080229</v>
       </c>
       <c r="P5">
-        <v>0.3990410252700003</v>
+        <v>0.1854709391672261</v>
       </c>
       <c r="Q5">
-        <v>-9.451831682754573</v>
+        <v>-3.200542320386916</v>
       </c>
       <c r="R5" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -4089,99 +4089,99 @@
         <v>23</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>0.7854241538148399</v>
+        <v>0.5748791117244582</v>
       </c>
       <c r="J6">
-        <v>0.3915870564538804</v>
+        <v>0.458709606010012</v>
       </c>
       <c r="K6">
-        <v>0.581364133429465</v>
+        <v>0.2232985729528257</v>
       </c>
       <c r="L6">
-        <v>0.6052159001643111</v>
+        <v>0.2487046894681947</v>
       </c>
       <c r="M6">
-        <v>0.02385176673484612</v>
+        <v>0.02540611651536895</v>
       </c>
       <c r="N6">
-        <v>0.5215590096336744</v>
+        <v>0.1369984143920285</v>
       </c>
       <c r="O6">
-        <v>0.5141118771253059</v>
+        <v>0.116123164080229</v>
       </c>
       <c r="P6">
-        <v>-0.007447132508368481</v>
+        <v>-0.02087525031179949</v>
       </c>
       <c r="Q6">
-        <v>1.002738251920917</v>
+        <v>1.301598480918656</v>
       </c>
       <c r="R6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>1.663029500266734</v>
+        <v>0.5339363551680865</v>
       </c>
       <c r="J7">
-        <v>0.2338636499567078</v>
+        <v>0.5970305760674619</v>
       </c>
       <c r="K7">
-        <v>0.6052159001643111</v>
+        <v>0.2487046894681947</v>
       </c>
       <c r="L7">
-        <v>0.696872315126521</v>
+        <v>0.2986358641783577</v>
       </c>
       <c r="M7">
-        <v>0.09165641496220989</v>
+        <v>0.04993117471016309</v>
       </c>
       <c r="N7">
-        <v>0.5141118771253059</v>
+        <v>0.116123164080229</v>
       </c>
       <c r="O7">
-        <v>0.5590870038203942</v>
+        <v>0.06484781890447699</v>
       </c>
       <c r="P7">
-        <v>0.0449751266950883</v>
+        <v>-0.05127534517575205</v>
       </c>
       <c r="Q7">
-        <v>-0.4911435347495541</v>
+        <v>2.555796538018598</v>
       </c>
       <c r="R7" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -4202,25 +4202,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4231,25 +4231,25 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2">
-        <v>1.01163910023057</v>
+        <v>1.01381011202702</v>
       </c>
       <c r="E2">
-        <v>0.5795877175725123</v>
+        <v>0.6456134694995845</v>
       </c>
       <c r="F2">
-        <v>0.1691410039128372</v>
+        <v>0.8496237199841992</v>
       </c>
       <c r="G2">
-        <v>0.6544893796276015</v>
+        <v>0.2869294079853869</v>
       </c>
       <c r="H2">
-        <v>1.531481188713505</v>
+        <v>1.85320502161696</v>
       </c>
       <c r="I2">
-        <v>1.405383523270676</v>
+        <v>1.72812259331291</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -4260,25 +4260,25 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>1.007973823773254</v>
+        <v>1.001226066313922</v>
       </c>
       <c r="E3">
-        <v>0.2926251835358054</v>
+        <v>0.5286822215276535</v>
       </c>
       <c r="F3">
-        <v>0.2602028007683616</v>
+        <v>0.8262574420475279</v>
       </c>
       <c r="G3">
-        <v>0.8809803495022062</v>
+        <v>0.9196585177067426</v>
       </c>
       <c r="H3">
-        <v>1.913271182809426</v>
+        <v>2.156514722729037</v>
       </c>
       <c r="I3">
-        <v>1.755738049990488</v>
+        <v>2.010960347985854</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4286,28 +4286,28 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D4">
-        <v>1.121305331718685</v>
+        <v>1.163657854297254</v>
       </c>
       <c r="E4">
-        <v>0.4273099001295377</v>
+        <v>0.6996202726518953</v>
       </c>
       <c r="F4">
-        <v>0.1594268095201135</v>
+        <v>0.9326466220450975</v>
       </c>
       <c r="G4">
-        <v>0.8917722169641169</v>
+        <v>0.6072212868760981</v>
       </c>
       <c r="H4">
-        <v>1.5698579120013</v>
+        <v>1.881844245117446</v>
       </c>
       <c r="I4">
-        <v>1.394855358622803</v>
+        <v>1.710395549150666</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -4315,28 +4315,28 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>53.86518864767415</v>
+        <v>11.6507609133532</v>
       </c>
       <c r="E5">
-        <v>0.5681977399499447</v>
+        <v>4.764166958172268</v>
       </c>
       <c r="F5">
-        <v>0.2598850523000154</v>
+        <v>0.3113820582203898</v>
       </c>
       <c r="G5">
-        <v>0.8794975187458534</v>
+        <v>0.98143337827237</v>
       </c>
       <c r="H5">
-        <v>1.650423269587353</v>
+        <v>1.829834955868813</v>
       </c>
       <c r="I5">
-        <v>1.365180932568826</v>
+        <v>1.573158432238486</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -4344,173 +4344,173 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>61.08070029911875</v>
+        <v>12.60185079627546</v>
       </c>
       <c r="E6">
-        <v>0.4788638921806911</v>
+        <v>5.267903921499294</v>
       </c>
       <c r="F6">
-        <v>0.9254893726900082</v>
+        <v>0.3839029071968507</v>
       </c>
       <c r="G6">
-        <v>0.9793989291894669</v>
+        <v>0.1708790703642055</v>
       </c>
       <c r="H6">
-        <v>1.04308737387962</v>
+        <v>1.135083662342778</v>
       </c>
       <c r="I6">
-        <v>0.7375741554403465</v>
+        <v>0.8725457520363624</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>1.017681660032122</v>
+        <v>1.03589293707489</v>
       </c>
       <c r="E7">
-        <v>0.5018431757227956</v>
+        <v>0.1823749204000267</v>
       </c>
       <c r="F7">
-        <v>0.4220077889086216</v>
+        <v>0.2010733948132116</v>
       </c>
       <c r="G7">
-        <v>0.7979069126061417</v>
+        <v>0.2573258684407913</v>
       </c>
       <c r="H7">
-        <v>2.233996446339432</v>
+        <v>2.34184253239145</v>
       </c>
       <c r="I7">
-        <v>2.027318740887332</v>
+        <v>2.168124886990257</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>1.051471993332928</v>
+        <v>1.030136629964357</v>
       </c>
       <c r="E8">
-        <v>0.3119360618233111</v>
+        <v>0.2456290742825697</v>
       </c>
       <c r="F8">
-        <v>0.9476168913915635</v>
+        <v>0.8137550751748333</v>
       </c>
       <c r="G8">
-        <v>0.3919919610818148</v>
+        <v>0.2143203191406846</v>
       </c>
       <c r="H8">
-        <v>1.642640090746519</v>
+        <v>2.103797821740693</v>
       </c>
       <c r="I8">
-        <v>1.490671592589143</v>
+        <v>1.947738309225244</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>1.287562935668985</v>
+        <v>1.409860367392662</v>
       </c>
       <c r="E9">
-        <v>0.2867174620062506</v>
+        <v>0.1630427025879717</v>
       </c>
       <c r="F9">
-        <v>0.9537540652610096</v>
+        <v>0.78185150196044</v>
       </c>
       <c r="G9">
-        <v>0.4973830488955234</v>
+        <v>0.3399393834114433</v>
       </c>
       <c r="H9">
-        <v>1.655374913650029</v>
+        <v>2.129090295660157</v>
       </c>
       <c r="I9">
-        <v>1.44758336875928</v>
+        <v>1.915617931886438</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D10">
-        <v>1320.190136266348</v>
+        <v>317.7397271440617</v>
       </c>
       <c r="E10">
-        <v>1.045986551806551</v>
+        <v>6.239174602978902</v>
       </c>
       <c r="F10">
-        <v>0.912222834844275</v>
+        <v>0.8381742606828063</v>
       </c>
       <c r="G10">
-        <v>0.5275374953958908</v>
+        <v>0.4007046320049603</v>
       </c>
       <c r="H10">
-        <v>1.576901905053064</v>
+        <v>2.189975971861964</v>
       </c>
       <c r="I10">
-        <v>1.268459366590729</v>
+        <v>1.850867510372357</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D11">
-        <v>1509.998127926904</v>
+        <v>410.8602321533518</v>
       </c>
       <c r="E11">
-        <v>2.834843051323265</v>
+        <v>4.221319101336776</v>
       </c>
       <c r="F11">
-        <v>0.5945294488259011</v>
+        <v>0.03225714142840883</v>
       </c>
       <c r="G11">
-        <v>0.4051937054050931</v>
+        <v>0.6020674406216109</v>
       </c>
       <c r="H11">
-        <v>1.968568108570851</v>
+        <v>2.395987946889964</v>
       </c>
       <c r="I11">
-        <v>1.091965116106979</v>
+        <v>1.643634171640534</v>
       </c>
     </row>
   </sheetData>
